--- a/templates/R80302書式/計画申請/03_人材開発支援助成金（事業展開等リスキリング支援コース）対象労働者一覧(様式第3-1号).xlsx
+++ b/templates/R80302書式/計画申請/03_人材開発支援助成金（事業展開等リスキリング支援コース）対象労働者一覧(様式第3-1号).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\12557000_人材開発統括官　企業内人材開発支援室\人開金島\15制度改正\令和７年度４月改正\05 支給要領・様式\02_様式\070328_助総最終登録版（再差替）\【溶け込み】様式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agri0001-my.sharepoint.com/personal/dxhr024_agri0001_onmicrosoft_com/Documents/デスクトップ/document_generator_new/templates/R80302書式/計画申請/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775AD4E6-CA05-4A32-90A4-6E26E30D9CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29445" yWindow="3420" windowWidth="26025" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="様式第３号" sheetId="3" r:id="rId1"/>
@@ -1409,11 +1409,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1423,13 +1420,13 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="5" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="24" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1468,7 +1465,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="37" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1">
@@ -1494,9 +1491,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="41" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1537,14 +1531,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -1552,16 +1552,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="18" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1581,6 +1581,66 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1606,10 +1666,10 @@
     <xf numFmtId="49" fontId="9" fillId="3" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1617,99 +1677,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="15" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="28" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1729,6 +1696,30 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1738,23 +1729,23 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="23" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -13418,1894 +13409,1875 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AM108"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35.625" style="3" customWidth="1"/>
-    <col min="3" max="4" width="4.5" style="3" customWidth="1"/>
-    <col min="5" max="5" width="2.625" style="3" customWidth="1"/>
-    <col min="6" max="7" width="6.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="2.625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="3.375" style="3" customWidth="1"/>
-    <col min="10" max="10" width="5.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="21.25" style="3" customWidth="1"/>
-    <col min="12" max="18" width="3.75" style="3" customWidth="1"/>
-    <col min="19" max="19" width="5.5" style="3" customWidth="1"/>
-    <col min="20" max="20" width="24" style="3" customWidth="1"/>
-    <col min="21" max="21" width="5" style="3" customWidth="1"/>
-    <col min="22" max="29" width="4.125" style="3" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="5.3984375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.59765625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="4.46484375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="2.59765625" style="2" customWidth="1"/>
+    <col min="6" max="7" width="6.46484375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="2.59765625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="3.3984375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="5.46484375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="21.265625" style="2" customWidth="1"/>
+    <col min="12" max="18" width="3.73046875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="5.46484375" style="2" customWidth="1"/>
+    <col min="20" max="20" width="24" style="2" customWidth="1"/>
+    <col min="21" max="21" width="5" style="2" customWidth="1"/>
+    <col min="22" max="29" width="4.1328125" style="2" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:28" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="115"/>
-      <c r="V1" s="115"/>
-      <c r="W1" s="115"/>
-      <c r="X1" s="115"/>
-      <c r="Y1" s="115"/>
-      <c r="Z1" s="115"/>
-      <c r="AA1" s="115"/>
-      <c r="AB1" s="115"/>
+      <c r="U1" s="96"/>
+      <c r="V1" s="96"/>
+      <c r="W1" s="96"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
+      <c r="Z1" s="96"/>
+      <c r="AA1" s="96"/>
+      <c r="AB1" s="96"/>
     </row>
-    <row r="2" spans="1:28" s="2" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="3" spans="1:28" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="U3" s="7" t="s">
+    <row r="2" spans="1:28" s="1" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:28" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="V3" s="4"/>
-      <c r="W3" s="112" t="s">
+      <c r="V3" s="3"/>
+      <c r="W3" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="X3" s="112"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="112" t="s">
+      <c r="X3" s="96"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="AA3" s="112"/>
-      <c r="AB3" s="7" t="s">
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="2" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:28" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="113" t="s">
+    <row r="4" spans="1:28" s="1" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:28" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="113"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="113"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="113"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
-      <c r="O5" s="113"/>
-      <c r="P5" s="113"/>
-      <c r="Q5" s="113"/>
-      <c r="R5" s="113"/>
-      <c r="S5" s="113"/>
-      <c r="T5" s="113"/>
-      <c r="U5" s="113"/>
-      <c r="V5" s="113"/>
-      <c r="W5" s="113"/>
-      <c r="X5" s="113"/>
-      <c r="Y5" s="113"/>
-      <c r="Z5" s="113"/>
-      <c r="AA5" s="113"/>
-      <c r="AB5" s="113"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="97"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="97"/>
+      <c r="P5" s="97"/>
+      <c r="Q5" s="97"/>
+      <c r="R5" s="97"/>
+      <c r="S5" s="97"/>
+      <c r="T5" s="97"/>
+      <c r="U5" s="97"/>
+      <c r="V5" s="97"/>
+      <c r="W5" s="97"/>
+      <c r="X5" s="97"/>
+      <c r="Y5" s="97"/>
+      <c r="Z5" s="97"/>
+      <c r="AA5" s="97"/>
+      <c r="AB5" s="97"/>
     </row>
-    <row r="6" spans="1:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="42"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
-      <c r="W6" s="42"/>
-      <c r="X6" s="42"/>
-      <c r="Y6" s="42"/>
-      <c r="Z6" s="42"/>
-      <c r="AA6" s="42"/>
-      <c r="AB6" s="42"/>
+    <row r="6" spans="1:28" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="40"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+      <c r="R6" s="40"/>
+      <c r="S6" s="40"/>
+      <c r="T6" s="40"/>
+      <c r="U6" s="40"/>
+      <c r="V6" s="40"/>
+      <c r="W6" s="40"/>
+      <c r="X6" s="40"/>
+      <c r="Y6" s="40"/>
+      <c r="Z6" s="40"/>
+      <c r="AA6" s="40"/>
+      <c r="AB6" s="40"/>
     </row>
-    <row r="7" spans="1:28" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="40"/>
-      <c r="AB7" s="41" t="s">
+    <row r="7" spans="1:28" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="12"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="12"/>
+      <c r="X7" s="12"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="38"/>
+      <c r="AB7" s="39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="11">
+    <row r="8" spans="1:28" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10">
         <v>1</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="101"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
-      <c r="N8" s="102"/>
-      <c r="O8" s="102"/>
-      <c r="P8" s="102"/>
-      <c r="Q8" s="102"/>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="102"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="102"/>
-      <c r="W8" s="102"/>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="103"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="91"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="91"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="91"/>
+      <c r="O8" s="91"/>
+      <c r="P8" s="91"/>
+      <c r="Q8" s="91"/>
+      <c r="R8" s="91"/>
+      <c r="S8" s="91"/>
+      <c r="T8" s="91"/>
+      <c r="U8" s="91"/>
+      <c r="V8" s="91"/>
+      <c r="W8" s="91"/>
+      <c r="X8" s="91"/>
+      <c r="Y8" s="91"/>
+      <c r="Z8" s="91"/>
+      <c r="AA8" s="91"/>
+      <c r="AB8" s="92"/>
     </row>
-    <row r="9" spans="1:28" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="12">
+    <row r="9" spans="1:28" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
         <v>2</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="104"/>
-      <c r="D9" s="105"/>
-      <c r="E9" s="105"/>
-      <c r="F9" s="105"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="105"/>
-      <c r="I9" s="105"/>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="105"/>
-      <c r="M9" s="105"/>
-      <c r="N9" s="105"/>
-      <c r="O9" s="105"/>
-      <c r="P9" s="105"/>
-      <c r="Q9" s="105"/>
-      <c r="R9" s="105"/>
-      <c r="S9" s="105"/>
-      <c r="T9" s="105"/>
-      <c r="U9" s="105"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="105"/>
-      <c r="X9" s="105"/>
-      <c r="Y9" s="105"/>
-      <c r="Z9" s="105"/>
-      <c r="AA9" s="105"/>
-      <c r="AB9" s="106"/>
+      <c r="C9" s="93"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="94"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="94"/>
+      <c r="T9" s="94"/>
+      <c r="U9" s="94"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="94"/>
+      <c r="X9" s="94"/>
+      <c r="Y9" s="94"/>
+      <c r="Z9" s="94"/>
+      <c r="AA9" s="94"/>
+      <c r="AB9" s="95"/>
     </row>
-    <row r="10" spans="1:28" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="14">
+    <row r="10" spans="1:28" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="13">
         <v>3</v>
       </c>
-      <c r="B10" s="107" t="s">
+      <c r="B10" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="107"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="107"/>
-      <c r="H10" s="107"/>
-      <c r="I10" s="107"/>
-      <c r="J10" s="107"/>
-      <c r="K10" s="107"/>
-      <c r="L10" s="108"/>
-      <c r="M10" s="108"/>
-      <c r="N10" s="108"/>
-      <c r="O10" s="108"/>
-      <c r="P10" s="108"/>
-      <c r="Q10" s="108"/>
-      <c r="R10" s="108"/>
-      <c r="S10" s="108"/>
-      <c r="T10" s="108"/>
-      <c r="U10" s="108"/>
-      <c r="V10" s="108"/>
-      <c r="W10" s="108"/>
-      <c r="X10" s="108"/>
-      <c r="Y10" s="108"/>
-      <c r="Z10" s="108"/>
-      <c r="AA10" s="108"/>
-      <c r="AB10" s="109"/>
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="104"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="105"/>
+      <c r="M10" s="105"/>
+      <c r="N10" s="105"/>
+      <c r="O10" s="105"/>
+      <c r="P10" s="105"/>
+      <c r="Q10" s="105"/>
+      <c r="R10" s="105"/>
+      <c r="S10" s="105"/>
+      <c r="T10" s="105"/>
+      <c r="U10" s="105"/>
+      <c r="V10" s="105"/>
+      <c r="W10" s="105"/>
+      <c r="X10" s="105"/>
+      <c r="Y10" s="105"/>
+      <c r="Z10" s="105"/>
+      <c r="AA10" s="105"/>
+      <c r="AB10" s="106"/>
     </row>
-    <row r="11" spans="1:28" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="19"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="94" t="s">
+    <row r="11" spans="1:28" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="M11" s="95"/>
-      <c r="N11" s="95"/>
-      <c r="O11" s="95"/>
-      <c r="P11" s="95"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="94" t="s">
+      <c r="M11" s="99"/>
+      <c r="N11" s="99"/>
+      <c r="O11" s="99"/>
+      <c r="P11" s="99"/>
+      <c r="Q11" s="99"/>
+      <c r="R11" s="109"/>
+      <c r="S11" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="T11" s="110"/>
-      <c r="U11" s="94" t="s">
+      <c r="T11" s="108"/>
+      <c r="U11" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="V11" s="95"/>
-      <c r="W11" s="95"/>
-      <c r="X11" s="95"/>
-      <c r="Y11" s="95"/>
-      <c r="Z11" s="95"/>
-      <c r="AA11" s="95"/>
-      <c r="AB11" s="111"/>
+      <c r="V11" s="99"/>
+      <c r="W11" s="99"/>
+      <c r="X11" s="99"/>
+      <c r="Y11" s="99"/>
+      <c r="Z11" s="99"/>
+      <c r="AA11" s="99"/>
+      <c r="AB11" s="100"/>
     </row>
-    <row r="12" spans="1:28" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:28" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="95"/>
-      <c r="E12" s="95"/>
-      <c r="F12" s="95"/>
-      <c r="G12" s="95"/>
-      <c r="H12" s="95"/>
-      <c r="I12" s="96"/>
-      <c r="J12" s="94" t="s">
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="K12" s="96"/>
-      <c r="L12" s="97" t="s">
+      <c r="K12" s="109"/>
+      <c r="L12" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="M12" s="98"/>
-      <c r="N12" s="98"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="99"/>
-      <c r="S12" s="97" t="s">
+      <c r="M12" s="102"/>
+      <c r="N12" s="102"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="102"/>
+      <c r="Q12" s="102"/>
+      <c r="R12" s="107"/>
+      <c r="S12" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="T12" s="99"/>
-      <c r="U12" s="97" t="s">
+      <c r="T12" s="107"/>
+      <c r="U12" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="V12" s="98"/>
-      <c r="W12" s="98"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="98"/>
-      <c r="AB12" s="100"/>
+      <c r="V12" s="102"/>
+      <c r="W12" s="102"/>
+      <c r="X12" s="102"/>
+      <c r="Y12" s="102"/>
+      <c r="Z12" s="102"/>
+      <c r="AA12" s="102"/>
+      <c r="AB12" s="103"/>
     </row>
-    <row r="13" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="84">
+    <row r="13" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="74">
         <v>1</v>
       </c>
-      <c r="B13" s="85"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="87"/>
-      <c r="E13" s="90" t="s">
+      <c r="B13" s="75"/>
+      <c r="C13" s="76"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="90" t="s">
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I13" s="87"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="32" t="s">
+      <c r="I13" s="58"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L13" s="70"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="74" t="s">
+      <c r="L13" s="62"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O13" s="71"/>
-      <c r="P13" s="74" t="s">
+      <c r="O13" s="44"/>
+      <c r="P13" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q13" s="71"/>
-      <c r="R13" s="76" t="s">
+      <c r="Q13" s="44"/>
+      <c r="R13" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S13" s="8"/>
-      <c r="T13" s="36" t="s">
+      <c r="S13" s="7"/>
+      <c r="T13" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U13" s="78"/>
-      <c r="V13" s="79"/>
-      <c r="W13" s="79"/>
-      <c r="X13" s="79"/>
-      <c r="Y13" s="79"/>
-      <c r="Z13" s="79"/>
-      <c r="AA13" s="79"/>
-      <c r="AB13" s="80"/>
+      <c r="U13" s="68"/>
+      <c r="V13" s="69"/>
+      <c r="W13" s="69"/>
+      <c r="X13" s="69"/>
+      <c r="Y13" s="69"/>
+      <c r="Z13" s="69"/>
+      <c r="AA13" s="69"/>
+      <c r="AB13" s="70"/>
     </row>
-    <row r="14" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="84"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="88"/>
-      <c r="D14" s="89"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="33" t="s">
+    <row r="14" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="74"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="77"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L14" s="72"/>
-      <c r="M14" s="73"/>
-      <c r="N14" s="75"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="75"/>
-      <c r="Q14" s="73"/>
-      <c r="R14" s="77"/>
-      <c r="S14" s="26"/>
-      <c r="T14" s="37" t="s">
+      <c r="L14" s="63"/>
+      <c r="M14" s="45"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="45"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U14" s="81"/>
-      <c r="V14" s="82"/>
-      <c r="W14" s="82"/>
-      <c r="X14" s="82"/>
-      <c r="Y14" s="82"/>
-      <c r="Z14" s="82"/>
-      <c r="AA14" s="82"/>
-      <c r="AB14" s="83"/>
+      <c r="U14" s="71"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="72"/>
+      <c r="X14" s="72"/>
+      <c r="Y14" s="72"/>
+      <c r="Z14" s="72"/>
+      <c r="AA14" s="72"/>
+      <c r="AB14" s="73"/>
     </row>
-    <row r="15" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="84">
+    <row r="15" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="74">
         <v>2</v>
       </c>
-      <c r="B15" s="85"/>
-      <c r="C15" s="86"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="90" t="s">
+      <c r="B15" s="75"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="87"/>
-      <c r="G15" s="87"/>
-      <c r="H15" s="90" t="s">
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I15" s="87"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="32" t="s">
+      <c r="I15" s="58"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L15" s="70"/>
-      <c r="M15" s="71"/>
-      <c r="N15" s="74" t="s">
+      <c r="L15" s="62"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O15" s="71"/>
-      <c r="P15" s="74" t="s">
+      <c r="O15" s="44"/>
+      <c r="P15" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q15" s="71"/>
-      <c r="R15" s="76" t="s">
+      <c r="Q15" s="44"/>
+      <c r="R15" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S15" s="8"/>
-      <c r="T15" s="36" t="s">
+      <c r="S15" s="7"/>
+      <c r="T15" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U15" s="78"/>
-      <c r="V15" s="79"/>
-      <c r="W15" s="79"/>
-      <c r="X15" s="79"/>
-      <c r="Y15" s="79"/>
-      <c r="Z15" s="79"/>
-      <c r="AA15" s="79"/>
-      <c r="AB15" s="80"/>
+      <c r="U15" s="68"/>
+      <c r="V15" s="69"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="69"/>
+      <c r="Y15" s="69"/>
+      <c r="Z15" s="69"/>
+      <c r="AA15" s="69"/>
+      <c r="AB15" s="70"/>
     </row>
-    <row r="16" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="84"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="89"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="89"/>
-      <c r="G16" s="89"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="33" t="s">
+    <row r="16" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="74"/>
+      <c r="B16" s="75"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="59"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L16" s="72"/>
-      <c r="M16" s="73"/>
-      <c r="N16" s="75"/>
-      <c r="O16" s="73"/>
-      <c r="P16" s="75"/>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="77"/>
-      <c r="S16" s="26"/>
-      <c r="T16" s="37" t="s">
+      <c r="L16" s="63"/>
+      <c r="M16" s="45"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="45"/>
+      <c r="P16" s="65"/>
+      <c r="Q16" s="45"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U16" s="81"/>
-      <c r="V16" s="82"/>
-      <c r="W16" s="82"/>
-      <c r="X16" s="82"/>
-      <c r="Y16" s="82"/>
-      <c r="Z16" s="82"/>
-      <c r="AA16" s="82"/>
-      <c r="AB16" s="83"/>
+      <c r="U16" s="71"/>
+      <c r="V16" s="72"/>
+      <c r="W16" s="72"/>
+      <c r="X16" s="72"/>
+      <c r="Y16" s="72"/>
+      <c r="Z16" s="72"/>
+      <c r="AA16" s="72"/>
+      <c r="AB16" s="73"/>
     </row>
-    <row r="17" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="84">
+    <row r="17" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="74">
         <v>3</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="87"/>
-      <c r="E17" s="90" t="s">
+      <c r="B17" s="75"/>
+      <c r="C17" s="76"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F17" s="87"/>
-      <c r="G17" s="87"/>
-      <c r="H17" s="90" t="s">
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I17" s="87"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="32" t="s">
+      <c r="I17" s="58"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L17" s="70"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="74" t="s">
+      <c r="L17" s="62"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O17" s="71"/>
-      <c r="P17" s="74" t="s">
+      <c r="O17" s="44"/>
+      <c r="P17" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q17" s="71"/>
-      <c r="R17" s="76" t="s">
+      <c r="Q17" s="44"/>
+      <c r="R17" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S17" s="8"/>
-      <c r="T17" s="36" t="s">
+      <c r="S17" s="7"/>
+      <c r="T17" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U17" s="78"/>
-      <c r="V17" s="79"/>
-      <c r="W17" s="79"/>
-      <c r="X17" s="79"/>
-      <c r="Y17" s="79"/>
-      <c r="Z17" s="79"/>
-      <c r="AA17" s="79"/>
-      <c r="AB17" s="80"/>
+      <c r="U17" s="68"/>
+      <c r="V17" s="69"/>
+      <c r="W17" s="69"/>
+      <c r="X17" s="69"/>
+      <c r="Y17" s="69"/>
+      <c r="Z17" s="69"/>
+      <c r="AA17" s="69"/>
+      <c r="AB17" s="70"/>
     </row>
-    <row r="18" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="84"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="88"/>
-      <c r="D18" s="89"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="89"/>
-      <c r="G18" s="89"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="33" t="s">
+    <row r="18" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="74"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L18" s="72"/>
-      <c r="M18" s="73"/>
-      <c r="N18" s="75"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="75"/>
-      <c r="Q18" s="73"/>
-      <c r="R18" s="77"/>
-      <c r="S18" s="26"/>
-      <c r="T18" s="37" t="s">
+      <c r="L18" s="63"/>
+      <c r="M18" s="45"/>
+      <c r="N18" s="65"/>
+      <c r="O18" s="45"/>
+      <c r="P18" s="65"/>
+      <c r="Q18" s="45"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U18" s="81"/>
-      <c r="V18" s="82"/>
-      <c r="W18" s="82"/>
-      <c r="X18" s="82"/>
-      <c r="Y18" s="82"/>
-      <c r="Z18" s="82"/>
-      <c r="AA18" s="82"/>
-      <c r="AB18" s="83"/>
+      <c r="U18" s="71"/>
+      <c r="V18" s="72"/>
+      <c r="W18" s="72"/>
+      <c r="X18" s="72"/>
+      <c r="Y18" s="72"/>
+      <c r="Z18" s="72"/>
+      <c r="AA18" s="72"/>
+      <c r="AB18" s="73"/>
     </row>
-    <row r="19" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="84">
+    <row r="19" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="74">
         <v>4</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="90" t="s">
+      <c r="B19" s="75"/>
+      <c r="C19" s="76"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="90" t="s">
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I19" s="87"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="32" t="s">
+      <c r="I19" s="58"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L19" s="70"/>
-      <c r="M19" s="71"/>
-      <c r="N19" s="74" t="s">
+      <c r="L19" s="62"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O19" s="71"/>
-      <c r="P19" s="74" t="s">
+      <c r="O19" s="44"/>
+      <c r="P19" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q19" s="71"/>
-      <c r="R19" s="76" t="s">
+      <c r="Q19" s="44"/>
+      <c r="R19" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S19" s="8"/>
-      <c r="T19" s="36" t="s">
+      <c r="S19" s="7"/>
+      <c r="T19" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U19" s="78"/>
-      <c r="V19" s="79"/>
-      <c r="W19" s="79"/>
-      <c r="X19" s="79"/>
-      <c r="Y19" s="79"/>
-      <c r="Z19" s="79"/>
-      <c r="AA19" s="79"/>
-      <c r="AB19" s="80"/>
+      <c r="U19" s="68"/>
+      <c r="V19" s="69"/>
+      <c r="W19" s="69"/>
+      <c r="X19" s="69"/>
+      <c r="Y19" s="69"/>
+      <c r="Z19" s="69"/>
+      <c r="AA19" s="69"/>
+      <c r="AB19" s="70"/>
     </row>
-    <row r="20" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="84"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="26"/>
-      <c r="K20" s="33" t="s">
+    <row r="20" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="74"/>
+      <c r="B20" s="75"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="59"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="72"/>
-      <c r="M20" s="73"/>
-      <c r="N20" s="75"/>
-      <c r="O20" s="73"/>
-      <c r="P20" s="75"/>
-      <c r="Q20" s="73"/>
-      <c r="R20" s="77"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="37" t="s">
+      <c r="L20" s="63"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="65"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U20" s="81"/>
-      <c r="V20" s="82"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="82"/>
-      <c r="Y20" s="82"/>
-      <c r="Z20" s="82"/>
-      <c r="AA20" s="82"/>
-      <c r="AB20" s="83"/>
+      <c r="U20" s="71"/>
+      <c r="V20" s="72"/>
+      <c r="W20" s="72"/>
+      <c r="X20" s="72"/>
+      <c r="Y20" s="72"/>
+      <c r="Z20" s="72"/>
+      <c r="AA20" s="72"/>
+      <c r="AB20" s="73"/>
     </row>
-    <row r="21" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="84">
+    <row r="21" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="74">
         <v>5</v>
       </c>
-      <c r="B21" s="85"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="87"/>
-      <c r="E21" s="90" t="s">
+      <c r="B21" s="75"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F21" s="87"/>
-      <c r="G21" s="87"/>
-      <c r="H21" s="90" t="s">
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I21" s="87"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="32" t="s">
+      <c r="I21" s="58"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L21" s="70"/>
-      <c r="M21" s="71"/>
-      <c r="N21" s="74" t="s">
+      <c r="L21" s="62"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="71"/>
-      <c r="P21" s="74" t="s">
+      <c r="O21" s="44"/>
+      <c r="P21" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q21" s="71"/>
-      <c r="R21" s="76" t="s">
+      <c r="Q21" s="44"/>
+      <c r="R21" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="8"/>
-      <c r="T21" s="36" t="s">
+      <c r="S21" s="7"/>
+      <c r="T21" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U21" s="78"/>
-      <c r="V21" s="79"/>
-      <c r="W21" s="79"/>
-      <c r="X21" s="79"/>
-      <c r="Y21" s="79"/>
-      <c r="Z21" s="79"/>
-      <c r="AA21" s="79"/>
-      <c r="AB21" s="80"/>
+      <c r="U21" s="68"/>
+      <c r="V21" s="69"/>
+      <c r="W21" s="69"/>
+      <c r="X21" s="69"/>
+      <c r="Y21" s="69"/>
+      <c r="Z21" s="69"/>
+      <c r="AA21" s="69"/>
+      <c r="AB21" s="70"/>
     </row>
-    <row r="22" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="84"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="88"/>
-      <c r="D22" s="89"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="89"/>
-      <c r="G22" s="89"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="33" t="s">
+    <row r="22" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="74"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="77"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="59"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L22" s="72"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="75"/>
-      <c r="O22" s="73"/>
-      <c r="P22" s="75"/>
-      <c r="Q22" s="73"/>
-      <c r="R22" s="77"/>
-      <c r="S22" s="26"/>
-      <c r="T22" s="37" t="s">
+      <c r="L22" s="63"/>
+      <c r="M22" s="45"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="45"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="45"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U22" s="81"/>
-      <c r="V22" s="82"/>
-      <c r="W22" s="82"/>
-      <c r="X22" s="82"/>
-      <c r="Y22" s="82"/>
-      <c r="Z22" s="82"/>
-      <c r="AA22" s="82"/>
-      <c r="AB22" s="83"/>
+      <c r="U22" s="71"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="72"/>
+      <c r="X22" s="72"/>
+      <c r="Y22" s="72"/>
+      <c r="Z22" s="72"/>
+      <c r="AA22" s="72"/>
+      <c r="AB22" s="73"/>
     </row>
-    <row r="23" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="84">
+    <row r="23" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="74">
         <v>6</v>
       </c>
-      <c r="B23" s="85"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="87"/>
-      <c r="E23" s="90" t="s">
+      <c r="B23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F23" s="87"/>
-      <c r="G23" s="87"/>
-      <c r="H23" s="90" t="s">
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I23" s="87"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="32" t="s">
+      <c r="I23" s="58"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L23" s="70"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="74" t="s">
+      <c r="L23" s="62"/>
+      <c r="M23" s="44"/>
+      <c r="N23" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O23" s="71"/>
-      <c r="P23" s="74" t="s">
+      <c r="O23" s="44"/>
+      <c r="P23" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q23" s="71"/>
-      <c r="R23" s="76" t="s">
+      <c r="Q23" s="44"/>
+      <c r="R23" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S23" s="8"/>
-      <c r="T23" s="36" t="s">
+      <c r="S23" s="7"/>
+      <c r="T23" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U23" s="78"/>
-      <c r="V23" s="79"/>
-      <c r="W23" s="79"/>
-      <c r="X23" s="79"/>
-      <c r="Y23" s="79"/>
-      <c r="Z23" s="79"/>
-      <c r="AA23" s="79"/>
-      <c r="AB23" s="80"/>
+      <c r="U23" s="68"/>
+      <c r="V23" s="69"/>
+      <c r="W23" s="69"/>
+      <c r="X23" s="69"/>
+      <c r="Y23" s="69"/>
+      <c r="Z23" s="69"/>
+      <c r="AA23" s="69"/>
+      <c r="AB23" s="70"/>
     </row>
-    <row r="24" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="84"/>
-      <c r="B24" s="85"/>
-      <c r="C24" s="88"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="33" t="s">
+    <row r="24" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="74"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="77"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L24" s="72"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="75"/>
-      <c r="O24" s="73"/>
-      <c r="P24" s="75"/>
-      <c r="Q24" s="73"/>
-      <c r="R24" s="77"/>
-      <c r="S24" s="26"/>
-      <c r="T24" s="37" t="s">
+      <c r="L24" s="63"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="45"/>
+      <c r="P24" s="65"/>
+      <c r="Q24" s="45"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U24" s="81"/>
-      <c r="V24" s="82"/>
-      <c r="W24" s="82"/>
-      <c r="X24" s="82"/>
-      <c r="Y24" s="82"/>
-      <c r="Z24" s="82"/>
-      <c r="AA24" s="82"/>
-      <c r="AB24" s="83"/>
+      <c r="U24" s="71"/>
+      <c r="V24" s="72"/>
+      <c r="W24" s="72"/>
+      <c r="X24" s="72"/>
+      <c r="Y24" s="72"/>
+      <c r="Z24" s="72"/>
+      <c r="AA24" s="72"/>
+      <c r="AB24" s="73"/>
     </row>
-    <row r="25" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="84">
+    <row r="25" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="74">
         <v>7</v>
       </c>
-      <c r="B25" s="85"/>
-      <c r="C25" s="86"/>
-      <c r="D25" s="87"/>
-      <c r="E25" s="90" t="s">
+      <c r="B25" s="75"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="87"/>
-      <c r="G25" s="87"/>
-      <c r="H25" s="90" t="s">
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I25" s="87"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="32" t="s">
+      <c r="I25" s="58"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L25" s="70"/>
-      <c r="M25" s="71"/>
-      <c r="N25" s="74" t="s">
+      <c r="L25" s="62"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O25" s="71"/>
-      <c r="P25" s="74" t="s">
+      <c r="O25" s="44"/>
+      <c r="P25" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="71"/>
-      <c r="R25" s="76" t="s">
+      <c r="Q25" s="44"/>
+      <c r="R25" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S25" s="8"/>
-      <c r="T25" s="36" t="s">
+      <c r="S25" s="7"/>
+      <c r="T25" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U25" s="78"/>
-      <c r="V25" s="79"/>
-      <c r="W25" s="79"/>
-      <c r="X25" s="79"/>
-      <c r="Y25" s="79"/>
-      <c r="Z25" s="79"/>
-      <c r="AA25" s="79"/>
-      <c r="AB25" s="80"/>
+      <c r="U25" s="68"/>
+      <c r="V25" s="69"/>
+      <c r="W25" s="69"/>
+      <c r="X25" s="69"/>
+      <c r="Y25" s="69"/>
+      <c r="Z25" s="69"/>
+      <c r="AA25" s="69"/>
+      <c r="AB25" s="70"/>
     </row>
-    <row r="26" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="84"/>
-      <c r="B26" s="85"/>
-      <c r="C26" s="88"/>
-      <c r="D26" s="89"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="89"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="91"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="33" t="s">
+    <row r="26" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="74"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="59"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L26" s="72"/>
-      <c r="M26" s="73"/>
-      <c r="N26" s="75"/>
-      <c r="O26" s="73"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="73"/>
-      <c r="R26" s="77"/>
-      <c r="S26" s="26"/>
-      <c r="T26" s="37" t="s">
+      <c r="L26" s="63"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="45"/>
+      <c r="P26" s="65"/>
+      <c r="Q26" s="45"/>
+      <c r="R26" s="67"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U26" s="81"/>
-      <c r="V26" s="82"/>
-      <c r="W26" s="82"/>
-      <c r="X26" s="82"/>
-      <c r="Y26" s="82"/>
-      <c r="Z26" s="82"/>
-      <c r="AA26" s="82"/>
-      <c r="AB26" s="83"/>
+      <c r="U26" s="71"/>
+      <c r="V26" s="72"/>
+      <c r="W26" s="72"/>
+      <c r="X26" s="72"/>
+      <c r="Y26" s="72"/>
+      <c r="Z26" s="72"/>
+      <c r="AA26" s="72"/>
+      <c r="AB26" s="73"/>
     </row>
-    <row r="27" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="84">
+    <row r="27" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="74">
         <v>8</v>
       </c>
-      <c r="B27" s="85"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="87"/>
-      <c r="E27" s="90" t="s">
+      <c r="B27" s="75"/>
+      <c r="C27" s="76"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F27" s="87"/>
-      <c r="G27" s="87"/>
-      <c r="H27" s="90" t="s">
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I27" s="87"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="32" t="s">
+      <c r="I27" s="58"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L27" s="70"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="74" t="s">
+      <c r="L27" s="62"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O27" s="71"/>
-      <c r="P27" s="74" t="s">
+      <c r="O27" s="44"/>
+      <c r="P27" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="76" t="s">
+      <c r="Q27" s="44"/>
+      <c r="R27" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S27" s="8"/>
-      <c r="T27" s="36" t="s">
+      <c r="S27" s="7"/>
+      <c r="T27" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U27" s="78"/>
-      <c r="V27" s="79"/>
-      <c r="W27" s="79"/>
-      <c r="X27" s="79"/>
-      <c r="Y27" s="79"/>
-      <c r="Z27" s="79"/>
-      <c r="AA27" s="79"/>
-      <c r="AB27" s="80"/>
+      <c r="U27" s="68"/>
+      <c r="V27" s="69"/>
+      <c r="W27" s="69"/>
+      <c r="X27" s="69"/>
+      <c r="Y27" s="69"/>
+      <c r="Z27" s="69"/>
+      <c r="AA27" s="69"/>
+      <c r="AB27" s="70"/>
     </row>
-    <row r="28" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="84"/>
-      <c r="B28" s="85"/>
-      <c r="C28" s="88"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="33" t="s">
+    <row r="28" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="74"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="61"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L28" s="72"/>
-      <c r="M28" s="73"/>
-      <c r="N28" s="75"/>
-      <c r="O28" s="73"/>
-      <c r="P28" s="75"/>
-      <c r="Q28" s="73"/>
-      <c r="R28" s="77"/>
-      <c r="S28" s="26"/>
-      <c r="T28" s="37" t="s">
+      <c r="L28" s="63"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="65"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="65"/>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U28" s="81"/>
-      <c r="V28" s="82"/>
-      <c r="W28" s="82"/>
-      <c r="X28" s="82"/>
-      <c r="Y28" s="82"/>
-      <c r="Z28" s="82"/>
-      <c r="AA28" s="82"/>
-      <c r="AB28" s="83"/>
+      <c r="U28" s="71"/>
+      <c r="V28" s="72"/>
+      <c r="W28" s="72"/>
+      <c r="X28" s="72"/>
+      <c r="Y28" s="72"/>
+      <c r="Z28" s="72"/>
+      <c r="AA28" s="72"/>
+      <c r="AB28" s="73"/>
     </row>
-    <row r="29" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="84">
+    <row r="29" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="74">
         <v>9</v>
       </c>
-      <c r="B29" s="85"/>
-      <c r="C29" s="86"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="90" t="s">
+      <c r="B29" s="75"/>
+      <c r="C29" s="76"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F29" s="87"/>
-      <c r="G29" s="87"/>
-      <c r="H29" s="90" t="s">
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I29" s="87"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="32" t="s">
+      <c r="I29" s="58"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L29" s="70"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="74" t="s">
+      <c r="L29" s="62"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O29" s="71"/>
-      <c r="P29" s="74" t="s">
+      <c r="O29" s="44"/>
+      <c r="P29" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="71"/>
-      <c r="R29" s="76" t="s">
+      <c r="Q29" s="44"/>
+      <c r="R29" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S29" s="8"/>
-      <c r="T29" s="36" t="s">
+      <c r="S29" s="7"/>
+      <c r="T29" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U29" s="78"/>
-      <c r="V29" s="79"/>
-      <c r="W29" s="79"/>
-      <c r="X29" s="79"/>
-      <c r="Y29" s="79"/>
-      <c r="Z29" s="79"/>
-      <c r="AA29" s="79"/>
-      <c r="AB29" s="80"/>
+      <c r="U29" s="68"/>
+      <c r="V29" s="69"/>
+      <c r="W29" s="69"/>
+      <c r="X29" s="69"/>
+      <c r="Y29" s="69"/>
+      <c r="Z29" s="69"/>
+      <c r="AA29" s="69"/>
+      <c r="AB29" s="70"/>
     </row>
-    <row r="30" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="84"/>
-      <c r="B30" s="85"/>
-      <c r="C30" s="88"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="91"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="33" t="s">
+    <row r="30" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="74"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="59"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L30" s="72"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="75"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="75"/>
-      <c r="Q30" s="73"/>
-      <c r="R30" s="77"/>
-      <c r="S30" s="26"/>
-      <c r="T30" s="37" t="s">
+      <c r="L30" s="63"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="45"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U30" s="81"/>
-      <c r="V30" s="82"/>
-      <c r="W30" s="82"/>
-      <c r="X30" s="82"/>
-      <c r="Y30" s="82"/>
-      <c r="Z30" s="82"/>
-      <c r="AA30" s="82"/>
-      <c r="AB30" s="83"/>
+      <c r="U30" s="71"/>
+      <c r="V30" s="72"/>
+      <c r="W30" s="72"/>
+      <c r="X30" s="72"/>
+      <c r="Y30" s="72"/>
+      <c r="Z30" s="72"/>
+      <c r="AA30" s="72"/>
+      <c r="AB30" s="73"/>
     </row>
-    <row r="31" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="84">
+    <row r="31" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="74">
         <v>10</v>
       </c>
-      <c r="B31" s="85"/>
-      <c r="C31" s="86"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="90" t="s">
+      <c r="B31" s="75"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F31" s="87"/>
-      <c r="G31" s="87"/>
-      <c r="H31" s="90" t="s">
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I31" s="87"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="32" t="s">
+      <c r="I31" s="58"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L31" s="70"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="74" t="s">
+      <c r="L31" s="62"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O31" s="71"/>
-      <c r="P31" s="74" t="s">
+      <c r="O31" s="44"/>
+      <c r="P31" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="76" t="s">
+      <c r="Q31" s="44"/>
+      <c r="R31" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S31" s="8"/>
-      <c r="T31" s="36" t="s">
+      <c r="S31" s="7"/>
+      <c r="T31" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U31" s="78"/>
-      <c r="V31" s="79"/>
-      <c r="W31" s="79"/>
-      <c r="X31" s="79"/>
-      <c r="Y31" s="79"/>
-      <c r="Z31" s="79"/>
-      <c r="AA31" s="79"/>
-      <c r="AB31" s="80"/>
+      <c r="U31" s="68"/>
+      <c r="V31" s="69"/>
+      <c r="W31" s="69"/>
+      <c r="X31" s="69"/>
+      <c r="Y31" s="69"/>
+      <c r="Z31" s="69"/>
+      <c r="AA31" s="69"/>
+      <c r="AB31" s="70"/>
     </row>
-    <row r="32" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="84"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="88"/>
-      <c r="D32" s="89"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="89"/>
-      <c r="G32" s="89"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="33" t="s">
+    <row r="32" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="74"/>
+      <c r="B32" s="75"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L32" s="72"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="75"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="75"/>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="77"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="37" t="s">
+      <c r="L32" s="63"/>
+      <c r="M32" s="45"/>
+      <c r="N32" s="65"/>
+      <c r="O32" s="45"/>
+      <c r="P32" s="65"/>
+      <c r="Q32" s="45"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U32" s="81"/>
-      <c r="V32" s="82"/>
-      <c r="W32" s="82"/>
-      <c r="X32" s="82"/>
-      <c r="Y32" s="82"/>
-      <c r="Z32" s="82"/>
-      <c r="AA32" s="82"/>
-      <c r="AB32" s="83"/>
+      <c r="U32" s="71"/>
+      <c r="V32" s="72"/>
+      <c r="W32" s="72"/>
+      <c r="X32" s="72"/>
+      <c r="Y32" s="72"/>
+      <c r="Z32" s="72"/>
+      <c r="AA32" s="72"/>
+      <c r="AB32" s="73"/>
     </row>
-    <row r="33" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="84">
+    <row r="33" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="74">
         <v>11</v>
       </c>
-      <c r="B33" s="85"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="87"/>
-      <c r="E33" s="90" t="s">
+      <c r="B33" s="75"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F33" s="87"/>
-      <c r="G33" s="87"/>
-      <c r="H33" s="90" t="s">
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I33" s="87"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="32" t="s">
+      <c r="I33" s="58"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L33" s="70"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="74" t="s">
+      <c r="L33" s="62"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O33" s="71"/>
-      <c r="P33" s="74" t="s">
+      <c r="O33" s="44"/>
+      <c r="P33" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q33" s="71"/>
-      <c r="R33" s="76" t="s">
+      <c r="Q33" s="44"/>
+      <c r="R33" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S33" s="8"/>
-      <c r="T33" s="36" t="s">
+      <c r="S33" s="7"/>
+      <c r="T33" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U33" s="78"/>
-      <c r="V33" s="79"/>
-      <c r="W33" s="79"/>
-      <c r="X33" s="79"/>
-      <c r="Y33" s="79"/>
-      <c r="Z33" s="79"/>
-      <c r="AA33" s="79"/>
-      <c r="AB33" s="80"/>
+      <c r="U33" s="68"/>
+      <c r="V33" s="69"/>
+      <c r="W33" s="69"/>
+      <c r="X33" s="69"/>
+      <c r="Y33" s="69"/>
+      <c r="Z33" s="69"/>
+      <c r="AA33" s="69"/>
+      <c r="AB33" s="70"/>
     </row>
-    <row r="34" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="84"/>
-      <c r="B34" s="85"/>
-      <c r="C34" s="88"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="89"/>
-      <c r="G34" s="89"/>
-      <c r="H34" s="91"/>
-      <c r="I34" s="89"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="33" t="s">
+    <row r="34" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="74"/>
+      <c r="B34" s="75"/>
+      <c r="C34" s="77"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="61"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L34" s="72"/>
-      <c r="M34" s="73"/>
-      <c r="N34" s="75"/>
-      <c r="O34" s="73"/>
-      <c r="P34" s="75"/>
-      <c r="Q34" s="73"/>
-      <c r="R34" s="77"/>
-      <c r="S34" s="26"/>
-      <c r="T34" s="37" t="s">
+      <c r="L34" s="63"/>
+      <c r="M34" s="45"/>
+      <c r="N34" s="65"/>
+      <c r="O34" s="45"/>
+      <c r="P34" s="65"/>
+      <c r="Q34" s="45"/>
+      <c r="R34" s="67"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U34" s="81"/>
-      <c r="V34" s="82"/>
-      <c r="W34" s="82"/>
-      <c r="X34" s="82"/>
-      <c r="Y34" s="82"/>
-      <c r="Z34" s="82"/>
-      <c r="AA34" s="82"/>
-      <c r="AB34" s="83"/>
+      <c r="U34" s="71"/>
+      <c r="V34" s="72"/>
+      <c r="W34" s="72"/>
+      <c r="X34" s="72"/>
+      <c r="Y34" s="72"/>
+      <c r="Z34" s="72"/>
+      <c r="AA34" s="72"/>
+      <c r="AB34" s="73"/>
     </row>
-    <row r="35" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="84">
+    <row r="35" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="74">
         <v>12</v>
       </c>
-      <c r="B35" s="85"/>
-      <c r="C35" s="86"/>
-      <c r="D35" s="87"/>
-      <c r="E35" s="90" t="s">
+      <c r="B35" s="75"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="87"/>
-      <c r="G35" s="87"/>
-      <c r="H35" s="90" t="s">
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I35" s="87"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="32" t="s">
+      <c r="I35" s="58"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L35" s="70"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="74" t="s">
+      <c r="L35" s="62"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O35" s="71"/>
-      <c r="P35" s="74" t="s">
+      <c r="O35" s="44"/>
+      <c r="P35" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q35" s="71"/>
-      <c r="R35" s="76" t="s">
+      <c r="Q35" s="44"/>
+      <c r="R35" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S35" s="8"/>
-      <c r="T35" s="36" t="s">
+      <c r="S35" s="7"/>
+      <c r="T35" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U35" s="78"/>
-      <c r="V35" s="79"/>
-      <c r="W35" s="79"/>
-      <c r="X35" s="79"/>
-      <c r="Y35" s="79"/>
-      <c r="Z35" s="79"/>
-      <c r="AA35" s="79"/>
-      <c r="AB35" s="80"/>
+      <c r="U35" s="68"/>
+      <c r="V35" s="69"/>
+      <c r="W35" s="69"/>
+      <c r="X35" s="69"/>
+      <c r="Y35" s="69"/>
+      <c r="Z35" s="69"/>
+      <c r="AA35" s="69"/>
+      <c r="AB35" s="70"/>
     </row>
-    <row r="36" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="84"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="88"/>
-      <c r="D36" s="89"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="91"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="33" t="s">
+    <row r="36" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="74"/>
+      <c r="B36" s="75"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L36" s="72"/>
-      <c r="M36" s="73"/>
-      <c r="N36" s="75"/>
-      <c r="O36" s="73"/>
-      <c r="P36" s="75"/>
-      <c r="Q36" s="73"/>
-      <c r="R36" s="77"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="37" t="s">
+      <c r="L36" s="63"/>
+      <c r="M36" s="45"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="45"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="45"/>
+      <c r="R36" s="67"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U36" s="81"/>
-      <c r="V36" s="82"/>
-      <c r="W36" s="82"/>
-      <c r="X36" s="82"/>
-      <c r="Y36" s="82"/>
-      <c r="Z36" s="82"/>
-      <c r="AA36" s="82"/>
-      <c r="AB36" s="83"/>
+      <c r="U36" s="71"/>
+      <c r="V36" s="72"/>
+      <c r="W36" s="72"/>
+      <c r="X36" s="72"/>
+      <c r="Y36" s="72"/>
+      <c r="Z36" s="72"/>
+      <c r="AA36" s="72"/>
+      <c r="AB36" s="73"/>
     </row>
-    <row r="37" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="84">
+    <row r="37" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="74">
         <v>13</v>
       </c>
-      <c r="B37" s="85"/>
-      <c r="C37" s="86"/>
-      <c r="D37" s="87"/>
-      <c r="E37" s="90" t="s">
+      <c r="B37" s="75"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F37" s="87"/>
-      <c r="G37" s="87"/>
-      <c r="H37" s="90" t="s">
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I37" s="87"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="32" t="s">
+      <c r="I37" s="58"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L37" s="70"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="74" t="s">
+      <c r="L37" s="62"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O37" s="71"/>
-      <c r="P37" s="74" t="s">
+      <c r="O37" s="44"/>
+      <c r="P37" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q37" s="71"/>
-      <c r="R37" s="76" t="s">
+      <c r="Q37" s="44"/>
+      <c r="R37" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S37" s="8"/>
-      <c r="T37" s="36" t="s">
+      <c r="S37" s="7"/>
+      <c r="T37" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U37" s="78"/>
-      <c r="V37" s="79"/>
-      <c r="W37" s="79"/>
-      <c r="X37" s="79"/>
-      <c r="Y37" s="79"/>
-      <c r="Z37" s="79"/>
-      <c r="AA37" s="79"/>
-      <c r="AB37" s="80"/>
+      <c r="U37" s="68"/>
+      <c r="V37" s="69"/>
+      <c r="W37" s="69"/>
+      <c r="X37" s="69"/>
+      <c r="Y37" s="69"/>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="69"/>
+      <c r="AB37" s="70"/>
     </row>
-    <row r="38" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="84"/>
-      <c r="B38" s="85"/>
-      <c r="C38" s="88"/>
-      <c r="D38" s="89"/>
-      <c r="E38" s="91"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="91"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="33" t="s">
+    <row r="38" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="74"/>
+      <c r="B38" s="75"/>
+      <c r="C38" s="77"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="61"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L38" s="72"/>
-      <c r="M38" s="73"/>
-      <c r="N38" s="75"/>
-      <c r="O38" s="73"/>
-      <c r="P38" s="75"/>
-      <c r="Q38" s="73"/>
-      <c r="R38" s="77"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="37" t="s">
+      <c r="L38" s="63"/>
+      <c r="M38" s="45"/>
+      <c r="N38" s="65"/>
+      <c r="O38" s="45"/>
+      <c r="P38" s="65"/>
+      <c r="Q38" s="45"/>
+      <c r="R38" s="67"/>
+      <c r="S38" s="25"/>
+      <c r="T38" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U38" s="81"/>
-      <c r="V38" s="82"/>
-      <c r="W38" s="82"/>
-      <c r="X38" s="82"/>
-      <c r="Y38" s="82"/>
-      <c r="Z38" s="82"/>
-      <c r="AA38" s="82"/>
-      <c r="AB38" s="83"/>
+      <c r="U38" s="71"/>
+      <c r="V38" s="72"/>
+      <c r="W38" s="72"/>
+      <c r="X38" s="72"/>
+      <c r="Y38" s="72"/>
+      <c r="Z38" s="72"/>
+      <c r="AA38" s="72"/>
+      <c r="AB38" s="73"/>
     </row>
-    <row r="39" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="84">
+    <row r="39" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="74">
         <v>14</v>
       </c>
-      <c r="B39" s="85"/>
-      <c r="C39" s="86"/>
-      <c r="D39" s="87"/>
-      <c r="E39" s="90" t="s">
+      <c r="B39" s="75"/>
+      <c r="C39" s="76"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F39" s="87"/>
-      <c r="G39" s="87"/>
-      <c r="H39" s="90" t="s">
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I39" s="87"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="32" t="s">
+      <c r="I39" s="58"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="70"/>
-      <c r="M39" s="71"/>
-      <c r="N39" s="74" t="s">
+      <c r="L39" s="62"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O39" s="71"/>
-      <c r="P39" s="74" t="s">
+      <c r="O39" s="44"/>
+      <c r="P39" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q39" s="71"/>
-      <c r="R39" s="76" t="s">
+      <c r="Q39" s="44"/>
+      <c r="R39" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S39" s="8"/>
-      <c r="T39" s="36" t="s">
+      <c r="S39" s="7"/>
+      <c r="T39" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U39" s="78"/>
-      <c r="V39" s="79"/>
-      <c r="W39" s="79"/>
-      <c r="X39" s="79"/>
-      <c r="Y39" s="79"/>
-      <c r="Z39" s="79"/>
-      <c r="AA39" s="79"/>
-      <c r="AB39" s="80"/>
+      <c r="U39" s="68"/>
+      <c r="V39" s="69"/>
+      <c r="W39" s="69"/>
+      <c r="X39" s="69"/>
+      <c r="Y39" s="69"/>
+      <c r="Z39" s="69"/>
+      <c r="AA39" s="69"/>
+      <c r="AB39" s="70"/>
     </row>
-    <row r="40" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="84"/>
-      <c r="B40" s="85"/>
-      <c r="C40" s="88"/>
-      <c r="D40" s="89"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="91"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="33" t="s">
+    <row r="40" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="74"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="77"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="61"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="61"/>
+      <c r="I40" s="59"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L40" s="72"/>
-      <c r="M40" s="73"/>
-      <c r="N40" s="75"/>
-      <c r="O40" s="73"/>
-      <c r="P40" s="75"/>
-      <c r="Q40" s="73"/>
-      <c r="R40" s="77"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="37" t="s">
+      <c r="L40" s="63"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="65"/>
+      <c r="O40" s="45"/>
+      <c r="P40" s="65"/>
+      <c r="Q40" s="45"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="25"/>
+      <c r="T40" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U40" s="81"/>
-      <c r="V40" s="82"/>
-      <c r="W40" s="82"/>
-      <c r="X40" s="82"/>
-      <c r="Y40" s="82"/>
-      <c r="Z40" s="82"/>
-      <c r="AA40" s="82"/>
-      <c r="AB40" s="83"/>
+      <c r="U40" s="71"/>
+      <c r="V40" s="72"/>
+      <c r="W40" s="72"/>
+      <c r="X40" s="72"/>
+      <c r="Y40" s="72"/>
+      <c r="Z40" s="72"/>
+      <c r="AA40" s="72"/>
+      <c r="AB40" s="73"/>
     </row>
-    <row r="41" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="84">
+    <row r="41" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="74">
         <v>15</v>
       </c>
-      <c r="B41" s="85"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="87"/>
-      <c r="E41" s="90" t="s">
+      <c r="B41" s="75"/>
+      <c r="C41" s="76"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F41" s="87"/>
-      <c r="G41" s="87"/>
-      <c r="H41" s="90" t="s">
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I41" s="87"/>
-      <c r="J41" s="8"/>
-      <c r="K41" s="32" t="s">
+      <c r="I41" s="58"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L41" s="70"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="74" t="s">
+      <c r="L41" s="62"/>
+      <c r="M41" s="44"/>
+      <c r="N41" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O41" s="71"/>
-      <c r="P41" s="74" t="s">
+      <c r="O41" s="44"/>
+      <c r="P41" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="76" t="s">
+      <c r="Q41" s="44"/>
+      <c r="R41" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S41" s="8"/>
-      <c r="T41" s="36" t="s">
+      <c r="S41" s="7"/>
+      <c r="T41" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U41" s="78"/>
-      <c r="V41" s="79"/>
-      <c r="W41" s="79"/>
-      <c r="X41" s="79"/>
-      <c r="Y41" s="79"/>
-      <c r="Z41" s="79"/>
-      <c r="AA41" s="79"/>
-      <c r="AB41" s="80"/>
+      <c r="U41" s="68"/>
+      <c r="V41" s="69"/>
+      <c r="W41" s="69"/>
+      <c r="X41" s="69"/>
+      <c r="Y41" s="69"/>
+      <c r="Z41" s="69"/>
+      <c r="AA41" s="69"/>
+      <c r="AB41" s="70"/>
     </row>
-    <row r="42" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="84"/>
-      <c r="B42" s="85"/>
-      <c r="C42" s="88"/>
-      <c r="D42" s="89"/>
-      <c r="E42" s="91"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="91"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="33" t="s">
+    <row r="42" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="74"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="61"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="61"/>
+      <c r="I42" s="59"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L42" s="72"/>
-      <c r="M42" s="73"/>
-      <c r="N42" s="75"/>
-      <c r="O42" s="73"/>
-      <c r="P42" s="75"/>
-      <c r="Q42" s="73"/>
-      <c r="R42" s="77"/>
-      <c r="S42" s="26"/>
-      <c r="T42" s="37" t="s">
+      <c r="L42" s="63"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="65"/>
+      <c r="O42" s="45"/>
+      <c r="P42" s="65"/>
+      <c r="Q42" s="45"/>
+      <c r="R42" s="67"/>
+      <c r="S42" s="25"/>
+      <c r="T42" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U42" s="81"/>
-      <c r="V42" s="82"/>
-      <c r="W42" s="82"/>
-      <c r="X42" s="82"/>
-      <c r="Y42" s="82"/>
-      <c r="Z42" s="82"/>
-      <c r="AA42" s="82"/>
-      <c r="AB42" s="83"/>
+      <c r="U42" s="71"/>
+      <c r="V42" s="72"/>
+      <c r="W42" s="72"/>
+      <c r="X42" s="72"/>
+      <c r="Y42" s="72"/>
+      <c r="Z42" s="72"/>
+      <c r="AA42" s="72"/>
+      <c r="AB42" s="73"/>
     </row>
-    <row r="43" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="84">
+    <row r="43" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="74">
         <v>16</v>
       </c>
-      <c r="B43" s="85"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="87"/>
-      <c r="E43" s="90" t="s">
+      <c r="B43" s="75"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F43" s="87"/>
-      <c r="G43" s="87"/>
-      <c r="H43" s="90" t="s">
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I43" s="87"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="32" t="s">
+      <c r="I43" s="58"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L43" s="70"/>
-      <c r="M43" s="71"/>
-      <c r="N43" s="74" t="s">
+      <c r="L43" s="62"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="71"/>
-      <c r="P43" s="74" t="s">
+      <c r="O43" s="44"/>
+      <c r="P43" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q43" s="71"/>
-      <c r="R43" s="76" t="s">
+      <c r="Q43" s="44"/>
+      <c r="R43" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S43" s="8"/>
-      <c r="T43" s="36" t="s">
+      <c r="S43" s="7"/>
+      <c r="T43" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U43" s="78"/>
-      <c r="V43" s="79"/>
-      <c r="W43" s="79"/>
-      <c r="X43" s="79"/>
-      <c r="Y43" s="79"/>
-      <c r="Z43" s="79"/>
-      <c r="AA43" s="79"/>
-      <c r="AB43" s="80"/>
+      <c r="U43" s="68"/>
+      <c r="V43" s="69"/>
+      <c r="W43" s="69"/>
+      <c r="X43" s="69"/>
+      <c r="Y43" s="69"/>
+      <c r="Z43" s="69"/>
+      <c r="AA43" s="69"/>
+      <c r="AB43" s="70"/>
     </row>
-    <row r="44" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="84"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="88"/>
-      <c r="D44" s="89"/>
-      <c r="E44" s="91"/>
-      <c r="F44" s="89"/>
-      <c r="G44" s="89"/>
-      <c r="H44" s="91"/>
-      <c r="I44" s="89"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="33" t="s">
+    <row r="44" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="74"/>
+      <c r="B44" s="75"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="61"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="61"/>
+      <c r="I44" s="59"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L44" s="72"/>
-      <c r="M44" s="73"/>
-      <c r="N44" s="75"/>
-      <c r="O44" s="73"/>
-      <c r="P44" s="75"/>
-      <c r="Q44" s="73"/>
-      <c r="R44" s="77"/>
-      <c r="S44" s="26"/>
-      <c r="T44" s="37" t="s">
+      <c r="L44" s="63"/>
+      <c r="M44" s="45"/>
+      <c r="N44" s="65"/>
+      <c r="O44" s="45"/>
+      <c r="P44" s="65"/>
+      <c r="Q44" s="45"/>
+      <c r="R44" s="67"/>
+      <c r="S44" s="25"/>
+      <c r="T44" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U44" s="81"/>
-      <c r="V44" s="82"/>
-      <c r="W44" s="82"/>
-      <c r="X44" s="82"/>
-      <c r="Y44" s="82"/>
-      <c r="Z44" s="82"/>
-      <c r="AA44" s="82"/>
-      <c r="AB44" s="83"/>
+      <c r="U44" s="71"/>
+      <c r="V44" s="72"/>
+      <c r="W44" s="72"/>
+      <c r="X44" s="72"/>
+      <c r="Y44" s="72"/>
+      <c r="Z44" s="72"/>
+      <c r="AA44" s="72"/>
+      <c r="AB44" s="73"/>
     </row>
-    <row r="45" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="84">
+    <row r="45" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="74">
         <v>17</v>
       </c>
-      <c r="B45" s="85"/>
-      <c r="C45" s="86"/>
-      <c r="D45" s="87"/>
-      <c r="E45" s="90" t="s">
+      <c r="B45" s="75"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F45" s="87"/>
-      <c r="G45" s="87"/>
-      <c r="H45" s="90" t="s">
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I45" s="87"/>
-      <c r="J45" s="8"/>
-      <c r="K45" s="32" t="s">
+      <c r="I45" s="58"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L45" s="70"/>
-      <c r="M45" s="71"/>
-      <c r="N45" s="74" t="s">
+      <c r="L45" s="62"/>
+      <c r="M45" s="44"/>
+      <c r="N45" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="71"/>
-      <c r="P45" s="74" t="s">
+      <c r="O45" s="44"/>
+      <c r="P45" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q45" s="71"/>
-      <c r="R45" s="76" t="s">
+      <c r="Q45" s="44"/>
+      <c r="R45" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S45" s="8"/>
-      <c r="T45" s="36" t="s">
+      <c r="S45" s="7"/>
+      <c r="T45" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U45" s="78"/>
-      <c r="V45" s="79"/>
-      <c r="W45" s="79"/>
-      <c r="X45" s="79"/>
-      <c r="Y45" s="79"/>
-      <c r="Z45" s="79"/>
-      <c r="AA45" s="79"/>
-      <c r="AB45" s="80"/>
+      <c r="U45" s="68"/>
+      <c r="V45" s="69"/>
+      <c r="W45" s="69"/>
+      <c r="X45" s="69"/>
+      <c r="Y45" s="69"/>
+      <c r="Z45" s="69"/>
+      <c r="AA45" s="69"/>
+      <c r="AB45" s="70"/>
     </row>
-    <row r="46" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="84"/>
-      <c r="B46" s="85"/>
-      <c r="C46" s="88"/>
-      <c r="D46" s="89"/>
-      <c r="E46" s="91"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
-      <c r="H46" s="91"/>
-      <c r="I46" s="89"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="33" t="s">
+    <row r="46" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="74"/>
+      <c r="B46" s="75"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="61"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="61"/>
+      <c r="I46" s="59"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L46" s="72"/>
-      <c r="M46" s="73"/>
-      <c r="N46" s="75"/>
-      <c r="O46" s="73"/>
-      <c r="P46" s="75"/>
-      <c r="Q46" s="73"/>
-      <c r="R46" s="77"/>
-      <c r="S46" s="26"/>
-      <c r="T46" s="37" t="s">
+      <c r="L46" s="63"/>
+      <c r="M46" s="45"/>
+      <c r="N46" s="65"/>
+      <c r="O46" s="45"/>
+      <c r="P46" s="65"/>
+      <c r="Q46" s="45"/>
+      <c r="R46" s="67"/>
+      <c r="S46" s="25"/>
+      <c r="T46" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U46" s="81"/>
-      <c r="V46" s="82"/>
-      <c r="W46" s="82"/>
-      <c r="X46" s="82"/>
-      <c r="Y46" s="82"/>
-      <c r="Z46" s="82"/>
-      <c r="AA46" s="82"/>
-      <c r="AB46" s="83"/>
+      <c r="U46" s="71"/>
+      <c r="V46" s="72"/>
+      <c r="W46" s="72"/>
+      <c r="X46" s="72"/>
+      <c r="Y46" s="72"/>
+      <c r="Z46" s="72"/>
+      <c r="AA46" s="72"/>
+      <c r="AB46" s="73"/>
     </row>
-    <row r="47" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="84">
+    <row r="47" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="74">
         <v>18</v>
       </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="86"/>
-      <c r="D47" s="87"/>
-      <c r="E47" s="90" t="s">
+      <c r="B47" s="75"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="87"/>
-      <c r="G47" s="87"/>
-      <c r="H47" s="90" t="s">
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I47" s="87"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="32" t="s">
+      <c r="I47" s="58"/>
+      <c r="J47" s="7"/>
+      <c r="K47" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L47" s="70"/>
-      <c r="M47" s="71"/>
-      <c r="N47" s="74" t="s">
+      <c r="L47" s="62"/>
+      <c r="M47" s="44"/>
+      <c r="N47" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="71"/>
-      <c r="P47" s="74" t="s">
+      <c r="O47" s="44"/>
+      <c r="P47" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q47" s="71"/>
-      <c r="R47" s="76" t="s">
+      <c r="Q47" s="44"/>
+      <c r="R47" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S47" s="8"/>
-      <c r="T47" s="36" t="s">
+      <c r="S47" s="7"/>
+      <c r="T47" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U47" s="78"/>
-      <c r="V47" s="79"/>
-      <c r="W47" s="79"/>
-      <c r="X47" s="79"/>
-      <c r="Y47" s="79"/>
-      <c r="Z47" s="79"/>
-      <c r="AA47" s="79"/>
-      <c r="AB47" s="80"/>
+      <c r="U47" s="68"/>
+      <c r="V47" s="69"/>
+      <c r="W47" s="69"/>
+      <c r="X47" s="69"/>
+      <c r="Y47" s="69"/>
+      <c r="Z47" s="69"/>
+      <c r="AA47" s="69"/>
+      <c r="AB47" s="70"/>
     </row>
-    <row r="48" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="84"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="88"/>
-      <c r="D48" s="89"/>
-      <c r="E48" s="91"/>
-      <c r="F48" s="89"/>
-      <c r="G48" s="89"/>
-      <c r="H48" s="91"/>
-      <c r="I48" s="89"/>
-      <c r="J48" s="26"/>
-      <c r="K48" s="33" t="s">
+    <row r="48" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="74"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="61"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="61"/>
+      <c r="I48" s="59"/>
+      <c r="J48" s="25"/>
+      <c r="K48" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L48" s="72"/>
-      <c r="M48" s="73"/>
-      <c r="N48" s="75"/>
-      <c r="O48" s="73"/>
-      <c r="P48" s="75"/>
-      <c r="Q48" s="73"/>
-      <c r="R48" s="77"/>
-      <c r="S48" s="26"/>
-      <c r="T48" s="37" t="s">
+      <c r="L48" s="63"/>
+      <c r="M48" s="45"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="45"/>
+      <c r="P48" s="65"/>
+      <c r="Q48" s="45"/>
+      <c r="R48" s="67"/>
+      <c r="S48" s="25"/>
+      <c r="T48" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U48" s="81"/>
-      <c r="V48" s="82"/>
-      <c r="W48" s="82"/>
-      <c r="X48" s="82"/>
-      <c r="Y48" s="82"/>
-      <c r="Z48" s="82"/>
-      <c r="AA48" s="82"/>
-      <c r="AB48" s="83"/>
+      <c r="U48" s="71"/>
+      <c r="V48" s="72"/>
+      <c r="W48" s="72"/>
+      <c r="X48" s="72"/>
+      <c r="Y48" s="72"/>
+      <c r="Z48" s="72"/>
+      <c r="AA48" s="72"/>
+      <c r="AB48" s="73"/>
     </row>
-    <row r="49" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="84">
+    <row r="49" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="74">
         <v>19</v>
       </c>
-      <c r="B49" s="85"/>
-      <c r="C49" s="86"/>
-      <c r="D49" s="87"/>
-      <c r="E49" s="90" t="s">
+      <c r="B49" s="75"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F49" s="87"/>
-      <c r="G49" s="87"/>
-      <c r="H49" s="90" t="s">
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I49" s="87"/>
-      <c r="J49" s="8"/>
-      <c r="K49" s="32" t="s">
+      <c r="I49" s="58"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L49" s="70"/>
-      <c r="M49" s="71"/>
-      <c r="N49" s="74" t="s">
+      <c r="L49" s="62"/>
+      <c r="M49" s="44"/>
+      <c r="N49" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="71"/>
-      <c r="P49" s="74" t="s">
+      <c r="O49" s="44"/>
+      <c r="P49" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q49" s="71"/>
-      <c r="R49" s="76" t="s">
+      <c r="Q49" s="44"/>
+      <c r="R49" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S49" s="8"/>
-      <c r="T49" s="36" t="s">
+      <c r="S49" s="7"/>
+      <c r="T49" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U49" s="78"/>
-      <c r="V49" s="79"/>
-      <c r="W49" s="79"/>
-      <c r="X49" s="79"/>
-      <c r="Y49" s="79"/>
-      <c r="Z49" s="79"/>
-      <c r="AA49" s="79"/>
-      <c r="AB49" s="80"/>
+      <c r="U49" s="68"/>
+      <c r="V49" s="69"/>
+      <c r="W49" s="69"/>
+      <c r="X49" s="69"/>
+      <c r="Y49" s="69"/>
+      <c r="Z49" s="69"/>
+      <c r="AA49" s="69"/>
+      <c r="AB49" s="70"/>
     </row>
-    <row r="50" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="84"/>
-      <c r="B50" s="85"/>
-      <c r="C50" s="88"/>
-      <c r="D50" s="89"/>
-      <c r="E50" s="91"/>
-      <c r="F50" s="89"/>
-      <c r="G50" s="89"/>
-      <c r="H50" s="91"/>
-      <c r="I50" s="89"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="33" t="s">
+    <row r="50" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="74"/>
+      <c r="B50" s="75"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="61"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="61"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="25"/>
+      <c r="K50" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L50" s="72"/>
-      <c r="M50" s="73"/>
-      <c r="N50" s="75"/>
-      <c r="O50" s="73"/>
-      <c r="P50" s="75"/>
-      <c r="Q50" s="73"/>
-      <c r="R50" s="77"/>
-      <c r="S50" s="26"/>
-      <c r="T50" s="37" t="s">
+      <c r="L50" s="63"/>
+      <c r="M50" s="45"/>
+      <c r="N50" s="65"/>
+      <c r="O50" s="45"/>
+      <c r="P50" s="65"/>
+      <c r="Q50" s="45"/>
+      <c r="R50" s="67"/>
+      <c r="S50" s="25"/>
+      <c r="T50" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U50" s="81"/>
-      <c r="V50" s="82"/>
-      <c r="W50" s="82"/>
-      <c r="X50" s="82"/>
-      <c r="Y50" s="82"/>
-      <c r="Z50" s="82"/>
-      <c r="AA50" s="82"/>
-      <c r="AB50" s="83"/>
+      <c r="U50" s="71"/>
+      <c r="V50" s="72"/>
+      <c r="W50" s="72"/>
+      <c r="X50" s="72"/>
+      <c r="Y50" s="72"/>
+      <c r="Z50" s="72"/>
+      <c r="AA50" s="72"/>
+      <c r="AB50" s="73"/>
     </row>
-    <row r="51" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="58">
+    <row r="51" spans="1:39" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="78">
         <v>20</v>
       </c>
-      <c r="B51" s="60"/>
-      <c r="C51" s="62"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="66" t="s">
+      <c r="B51" s="80"/>
+      <c r="C51" s="82"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F51" s="63"/>
-      <c r="G51" s="63"/>
-      <c r="H51" s="66" t="s">
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="I51" s="63"/>
-      <c r="J51" s="27"/>
-      <c r="K51" s="34" t="s">
+      <c r="I51" s="83"/>
+      <c r="J51" s="26"/>
+      <c r="K51" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="L51" s="68"/>
+      <c r="L51" s="88"/>
       <c r="M51" s="46"/>
       <c r="N51" s="48" t="s">
         <v>3</v>
@@ -15318,8 +15290,8 @@
       <c r="R51" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="S51" s="27"/>
-      <c r="T51" s="38" t="s">
+      <c r="S51" s="26"/>
+      <c r="T51" s="36" t="s">
         <v>14</v>
       </c>
       <c r="U51" s="52"/>
@@ -15331,29 +15303,29 @@
       <c r="AA51" s="53"/>
       <c r="AB51" s="54"/>
     </row>
-    <row r="52" spans="1:39" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="59"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="64"/>
-      <c r="D52" s="65"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="67"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="35" t="s">
+    <row r="52" spans="1:39" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="79"/>
+      <c r="B52" s="81"/>
+      <c r="C52" s="84"/>
+      <c r="D52" s="85"/>
+      <c r="E52" s="87"/>
+      <c r="F52" s="85"/>
+      <c r="G52" s="85"/>
+      <c r="H52" s="87"/>
+      <c r="I52" s="85"/>
+      <c r="J52" s="27"/>
+      <c r="K52" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="L52" s="69"/>
+      <c r="L52" s="89"/>
       <c r="M52" s="47"/>
       <c r="N52" s="49"/>
       <c r="O52" s="47"/>
       <c r="P52" s="49"/>
       <c r="Q52" s="47"/>
       <c r="R52" s="51"/>
-      <c r="S52" s="28"/>
-      <c r="T52" s="39" t="s">
+      <c r="S52" s="27"/>
+      <c r="T52" s="37" t="s">
         <v>13</v>
       </c>
       <c r="U52" s="55"/>
@@ -15365,2085 +15337,2085 @@
       <c r="AA52" s="56"/>
       <c r="AB52" s="57"/>
     </row>
-    <row r="53" spans="1:39" s="24" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="114" t="s">
+    <row r="53" spans="1:39" s="23" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="B53" s="114"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="23"/>
-      <c r="I53" s="23"/>
-      <c r="J53" s="23"/>
-      <c r="K53" s="23"/>
-      <c r="L53" s="23"/>
-      <c r="M53" s="23"/>
-      <c r="N53" s="23"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="23"/>
-      <c r="Q53" s="23"/>
-      <c r="R53" s="23"/>
-      <c r="S53" s="23"/>
-      <c r="T53" s="23"/>
-      <c r="U53" s="21"/>
-      <c r="V53" s="21"/>
-      <c r="W53" s="21"/>
-      <c r="X53" s="21"/>
-      <c r="Y53" s="21"/>
-      <c r="Z53" s="21"/>
-      <c r="AA53" s="21"/>
-      <c r="AB53" s="21"/>
+      <c r="B53" s="110"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="22"/>
+      <c r="O53" s="22"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22"/>
+      <c r="R53" s="22"/>
+      <c r="S53" s="22"/>
+      <c r="T53" s="22"/>
+      <c r="U53" s="20"/>
+      <c r="V53" s="20"/>
+      <c r="W53" s="20"/>
+      <c r="X53" s="20"/>
+      <c r="Y53" s="20"/>
+      <c r="Z53" s="20"/>
+      <c r="AA53" s="20"/>
+      <c r="AB53" s="20"/>
     </row>
-    <row r="54" spans="1:39" s="21" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="43">
+    <row r="54" spans="1:39" s="20" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="41">
         <v>1</v>
       </c>
-      <c r="B54" s="92" t="s">
+      <c r="B54" s="111" t="s">
         <v>25</v>
       </c>
-      <c r="C54" s="92"/>
-      <c r="D54" s="92"/>
-      <c r="E54" s="92"/>
-      <c r="F54" s="92"/>
-      <c r="G54" s="92"/>
-      <c r="H54" s="92"/>
-      <c r="I54" s="92"/>
-      <c r="J54" s="92"/>
-      <c r="K54" s="92"/>
-      <c r="L54" s="92"/>
-      <c r="M54" s="92"/>
-      <c r="N54" s="92"/>
-      <c r="O54" s="92"/>
-      <c r="P54" s="92"/>
-      <c r="Q54" s="92"/>
-      <c r="R54" s="92"/>
-      <c r="S54" s="92"/>
-      <c r="T54" s="92"/>
-      <c r="U54" s="92"/>
-      <c r="V54" s="92"/>
-      <c r="W54" s="92"/>
-      <c r="X54" s="92"/>
-      <c r="Y54" s="92"/>
-      <c r="Z54" s="92"/>
-      <c r="AA54" s="92"/>
-      <c r="AB54" s="92"/>
+      <c r="C54" s="111"/>
+      <c r="D54" s="111"/>
+      <c r="E54" s="111"/>
+      <c r="F54" s="111"/>
+      <c r="G54" s="111"/>
+      <c r="H54" s="111"/>
+      <c r="I54" s="111"/>
+      <c r="J54" s="111"/>
+      <c r="K54" s="111"/>
+      <c r="L54" s="111"/>
+      <c r="M54" s="111"/>
+      <c r="N54" s="111"/>
+      <c r="O54" s="111"/>
+      <c r="P54" s="111"/>
+      <c r="Q54" s="111"/>
+      <c r="R54" s="111"/>
+      <c r="S54" s="111"/>
+      <c r="T54" s="111"/>
+      <c r="U54" s="111"/>
+      <c r="V54" s="111"/>
+      <c r="W54" s="111"/>
+      <c r="X54" s="111"/>
+      <c r="Y54" s="111"/>
+      <c r="Z54" s="111"/>
+      <c r="AA54" s="111"/>
+      <c r="AB54" s="111"/>
     </row>
-    <row r="55" spans="1:39" s="25" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="44">
+    <row r="55" spans="1:39" s="24" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="42">
         <v>2</v>
       </c>
-      <c r="B55" s="93" t="s">
+      <c r="B55" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="93"/>
-      <c r="D55" s="93"/>
-      <c r="E55" s="93"/>
-      <c r="F55" s="93"/>
-      <c r="G55" s="93"/>
-      <c r="H55" s="93"/>
-      <c r="I55" s="93"/>
-      <c r="J55" s="93"/>
-      <c r="K55" s="93"/>
-      <c r="L55" s="93"/>
-      <c r="M55" s="93"/>
-      <c r="N55" s="93"/>
-      <c r="O55" s="93"/>
-      <c r="P55" s="93"/>
-      <c r="Q55" s="93"/>
-      <c r="R55" s="93"/>
-      <c r="S55" s="93"/>
-      <c r="T55" s="93"/>
-      <c r="U55" s="93"/>
-      <c r="V55" s="93"/>
-      <c r="W55" s="93"/>
-      <c r="X55" s="93"/>
-      <c r="Y55" s="93"/>
-      <c r="Z55" s="93"/>
-      <c r="AA55" s="93"/>
-      <c r="AB55" s="93"/>
+      <c r="C55" s="112"/>
+      <c r="D55" s="112"/>
+      <c r="E55" s="112"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="112"/>
+      <c r="H55" s="112"/>
+      <c r="I55" s="112"/>
+      <c r="J55" s="112"/>
+      <c r="K55" s="112"/>
+      <c r="L55" s="112"/>
+      <c r="M55" s="112"/>
+      <c r="N55" s="112"/>
+      <c r="O55" s="112"/>
+      <c r="P55" s="112"/>
+      <c r="Q55" s="112"/>
+      <c r="R55" s="112"/>
+      <c r="S55" s="112"/>
+      <c r="T55" s="112"/>
+      <c r="U55" s="112"/>
+      <c r="V55" s="112"/>
+      <c r="W55" s="112"/>
+      <c r="X55" s="112"/>
+      <c r="Y55" s="112"/>
+      <c r="Z55" s="112"/>
+      <c r="AA55" s="112"/>
+      <c r="AB55" s="112"/>
     </row>
-    <row r="56" spans="1:39" s="25" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="45">
+    <row r="56" spans="1:39" s="24" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="43">
         <v>3</v>
       </c>
-      <c r="B56" s="92" t="s">
+      <c r="B56" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="C56" s="92"/>
-      <c r="D56" s="92"/>
-      <c r="E56" s="92"/>
-      <c r="F56" s="92"/>
-      <c r="G56" s="92"/>
-      <c r="H56" s="92"/>
-      <c r="I56" s="92"/>
-      <c r="J56" s="92"/>
-      <c r="K56" s="92"/>
-      <c r="L56" s="92"/>
-      <c r="M56" s="92"/>
-      <c r="N56" s="92"/>
-      <c r="O56" s="92"/>
-      <c r="P56" s="92"/>
-      <c r="Q56" s="92"/>
-      <c r="R56" s="92"/>
-      <c r="S56" s="92"/>
-      <c r="T56" s="92"/>
-      <c r="U56" s="92"/>
-      <c r="V56" s="43"/>
-      <c r="W56" s="43"/>
-      <c r="X56" s="43"/>
-      <c r="Y56" s="43"/>
-      <c r="Z56" s="43"/>
-      <c r="AA56" s="43"/>
-      <c r="AB56" s="43"/>
+      <c r="C56" s="111"/>
+      <c r="D56" s="111"/>
+      <c r="E56" s="111"/>
+      <c r="F56" s="111"/>
+      <c r="G56" s="111"/>
+      <c r="H56" s="111"/>
+      <c r="I56" s="111"/>
+      <c r="J56" s="111"/>
+      <c r="K56" s="111"/>
+      <c r="L56" s="111"/>
+      <c r="M56" s="111"/>
+      <c r="N56" s="111"/>
+      <c r="O56" s="111"/>
+      <c r="P56" s="111"/>
+      <c r="Q56" s="111"/>
+      <c r="R56" s="111"/>
+      <c r="S56" s="111"/>
+      <c r="T56" s="111"/>
+      <c r="U56" s="111"/>
+      <c r="V56" s="41"/>
+      <c r="W56" s="41"/>
+      <c r="X56" s="41"/>
+      <c r="Y56" s="41"/>
+      <c r="Z56" s="41"/>
+      <c r="AA56" s="41"/>
+      <c r="AB56" s="41"/>
     </row>
-    <row r="57" spans="1:39" s="25" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="45">
+    <row r="57" spans="1:39" s="24" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="43">
         <v>4</v>
       </c>
-      <c r="B57" s="43" t="s">
+      <c r="B57" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="C57" s="43"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="43"/>
-      <c r="I57" s="43"/>
-      <c r="J57" s="43"/>
-      <c r="K57" s="43"/>
-      <c r="L57" s="43"/>
-      <c r="M57" s="43"/>
-      <c r="N57" s="43"/>
-      <c r="O57" s="43"/>
-      <c r="P57" s="43"/>
-      <c r="Q57" s="43"/>
-      <c r="R57" s="43"/>
-      <c r="S57" s="43"/>
-      <c r="T57" s="43"/>
-      <c r="U57" s="43"/>
-      <c r="V57" s="43"/>
-      <c r="W57" s="43"/>
-      <c r="X57" s="43"/>
-      <c r="Y57" s="43"/>
-      <c r="Z57" s="43"/>
-      <c r="AA57" s="43"/>
-      <c r="AB57" s="43"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41"/>
+      <c r="J57" s="41"/>
+      <c r="K57" s="41"/>
+      <c r="L57" s="41"/>
+      <c r="M57" s="41"/>
+      <c r="N57" s="41"/>
+      <c r="O57" s="41"/>
+      <c r="P57" s="41"/>
+      <c r="Q57" s="41"/>
+      <c r="R57" s="41"/>
+      <c r="S57" s="41"/>
+      <c r="T57" s="41"/>
+      <c r="U57" s="41"/>
+      <c r="V57" s="41"/>
+      <c r="W57" s="41"/>
+      <c r="X57" s="41"/>
+      <c r="Y57" s="41"/>
+      <c r="Z57" s="41"/>
+      <c r="AA57" s="41"/>
+      <c r="AB57" s="41"/>
     </row>
-    <row r="58" spans="1:39" s="25" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="44">
+    <row r="58" spans="1:39" s="24" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="42">
         <v>5</v>
       </c>
-      <c r="B58" s="93" t="s">
+      <c r="B58" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="C58" s="93"/>
-      <c r="D58" s="93"/>
-      <c r="E58" s="93"/>
-      <c r="F58" s="93"/>
-      <c r="G58" s="93"/>
-      <c r="H58" s="93"/>
-      <c r="I58" s="93"/>
-      <c r="J58" s="93"/>
-      <c r="K58" s="93"/>
-      <c r="L58" s="93"/>
-      <c r="M58" s="93"/>
-      <c r="N58" s="93"/>
-      <c r="O58" s="93"/>
-      <c r="P58" s="93"/>
-      <c r="Q58" s="93"/>
-      <c r="R58" s="93"/>
-      <c r="S58" s="93"/>
-      <c r="T58" s="93"/>
-      <c r="U58" s="93"/>
-      <c r="V58" s="44"/>
-      <c r="W58" s="44"/>
-      <c r="X58" s="44"/>
-      <c r="Y58" s="44"/>
-      <c r="Z58" s="44"/>
-      <c r="AA58" s="44"/>
-      <c r="AB58" s="44"/>
+      <c r="C58" s="112"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="112"/>
+      <c r="G58" s="112"/>
+      <c r="H58" s="112"/>
+      <c r="I58" s="112"/>
+      <c r="J58" s="112"/>
+      <c r="K58" s="112"/>
+      <c r="L58" s="112"/>
+      <c r="M58" s="112"/>
+      <c r="N58" s="112"/>
+      <c r="O58" s="112"/>
+      <c r="P58" s="112"/>
+      <c r="Q58" s="112"/>
+      <c r="R58" s="112"/>
+      <c r="S58" s="112"/>
+      <c r="T58" s="112"/>
+      <c r="U58" s="112"/>
+      <c r="V58" s="42"/>
+      <c r="W58" s="42"/>
+      <c r="X58" s="42"/>
+      <c r="Y58" s="42"/>
+      <c r="Z58" s="42"/>
+      <c r="AA58" s="42"/>
+      <c r="AB58" s="42"/>
     </row>
-    <row r="59" spans="1:39" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="29" t="s">
+    <row r="59" spans="1:39" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
-      <c r="L59" s="30"/>
-      <c r="M59" s="30"/>
-      <c r="N59" s="30"/>
-      <c r="O59" s="30"/>
-      <c r="P59" s="30"/>
-      <c r="Q59" s="30"/>
-      <c r="R59" s="30"/>
-      <c r="S59" s="31"/>
-      <c r="T59" s="31"/>
-      <c r="U59" s="31"/>
-      <c r="V59" s="30"/>
-      <c r="W59" s="30"/>
-      <c r="X59" s="31"/>
-      <c r="Y59" s="31"/>
-      <c r="Z59" s="31"/>
-      <c r="AA59" s="31"/>
-      <c r="AB59" s="31"/>
-      <c r="AC59" s="31"/>
-      <c r="AD59" s="31"/>
-      <c r="AE59" s="2"/>
-      <c r="AF59" s="22"/>
-      <c r="AG59" s="22"/>
-      <c r="AH59" s="20"/>
-      <c r="AI59" s="20"/>
-      <c r="AJ59" s="22"/>
-      <c r="AK59" s="20"/>
-      <c r="AL59" s="20"/>
-      <c r="AM59" s="22"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="28"/>
+      <c r="O59" s="28"/>
+      <c r="P59" s="28"/>
+      <c r="Q59" s="28"/>
+      <c r="R59" s="28"/>
+      <c r="S59" s="29"/>
+      <c r="T59" s="29"/>
+      <c r="U59" s="29"/>
+      <c r="V59" s="28"/>
+      <c r="W59" s="28"/>
+      <c r="X59" s="29"/>
+      <c r="Y59" s="29"/>
+      <c r="Z59" s="29"/>
+      <c r="AA59" s="29"/>
+      <c r="AB59" s="29"/>
+      <c r="AC59" s="29"/>
+      <c r="AD59" s="29"/>
+      <c r="AE59" s="1"/>
+      <c r="AF59" s="21"/>
+      <c r="AG59" s="21"/>
+      <c r="AH59" s="19"/>
+      <c r="AI59" s="19"/>
+      <c r="AJ59" s="21"/>
+      <c r="AK59" s="19"/>
+      <c r="AL59" s="19"/>
+      <c r="AM59" s="21"/>
     </row>
-    <row r="60" spans="1:39" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-      <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" s="2"/>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="2"/>
-      <c r="T60" s="2"/>
-      <c r="U60" s="7" t="s">
+    <row r="60" spans="1:39" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="Q60" s="1"/>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="V60" s="4"/>
-      <c r="W60" s="112" t="s">
+      <c r="V60" s="3"/>
+      <c r="W60" s="96" t="s">
         <v>8</v>
       </c>
-      <c r="X60" s="112"/>
-      <c r="Y60" s="4"/>
-      <c r="Z60" s="112" t="s">
+      <c r="X60" s="96"/>
+      <c r="Y60" s="3"/>
+      <c r="Z60" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="AA60" s="112"/>
-      <c r="AB60" s="7" t="s">
+      <c r="AA60" s="96"/>
+      <c r="AB60" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AC60" s="2"/>
-      <c r="AD60" s="2"/>
-      <c r="AE60" s="2"/>
-      <c r="AF60" s="2"/>
-      <c r="AG60" s="2"/>
-      <c r="AH60" s="2"/>
-      <c r="AI60" s="2"/>
-      <c r="AJ60" s="2"/>
-      <c r="AK60" s="2"/>
-      <c r="AL60" s="2"/>
-      <c r="AM60" s="2"/>
+      <c r="AC60" s="1"/>
+      <c r="AD60" s="1"/>
+      <c r="AE60" s="1"/>
+      <c r="AF60" s="1"/>
+      <c r="AG60" s="1"/>
+      <c r="AH60" s="1"/>
+      <c r="AI60" s="1"/>
+      <c r="AJ60" s="1"/>
+      <c r="AK60" s="1"/>
+      <c r="AL60" s="1"/>
+      <c r="AM60" s="1"/>
     </row>
-    <row r="61" spans="1:39" ht="33" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="113" t="s">
+    <row r="61" spans="1:39" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="B61" s="113"/>
-      <c r="C61" s="113"/>
-      <c r="D61" s="113"/>
-      <c r="E61" s="113"/>
-      <c r="F61" s="113"/>
-      <c r="G61" s="113"/>
-      <c r="H61" s="113"/>
-      <c r="I61" s="113"/>
-      <c r="J61" s="113"/>
-      <c r="K61" s="113"/>
-      <c r="L61" s="113"/>
-      <c r="M61" s="113"/>
-      <c r="N61" s="113"/>
-      <c r="O61" s="113"/>
-      <c r="P61" s="113"/>
-      <c r="Q61" s="113"/>
-      <c r="R61" s="113"/>
-      <c r="S61" s="113"/>
-      <c r="T61" s="113"/>
-      <c r="U61" s="113"/>
-      <c r="V61" s="113"/>
-      <c r="W61" s="113"/>
-      <c r="X61" s="113"/>
-      <c r="Y61" s="113"/>
-      <c r="Z61" s="113"/>
-      <c r="AA61" s="113"/>
-      <c r="AB61" s="113"/>
+      <c r="B61" s="97"/>
+      <c r="C61" s="97"/>
+      <c r="D61" s="97"/>
+      <c r="E61" s="97"/>
+      <c r="F61" s="97"/>
+      <c r="G61" s="97"/>
+      <c r="H61" s="97"/>
+      <c r="I61" s="97"/>
+      <c r="J61" s="97"/>
+      <c r="K61" s="97"/>
+      <c r="L61" s="97"/>
+      <c r="M61" s="97"/>
+      <c r="N61" s="97"/>
+      <c r="O61" s="97"/>
+      <c r="P61" s="97"/>
+      <c r="Q61" s="97"/>
+      <c r="R61" s="97"/>
+      <c r="S61" s="97"/>
+      <c r="T61" s="97"/>
+      <c r="U61" s="97"/>
+      <c r="V61" s="97"/>
+      <c r="W61" s="97"/>
+      <c r="X61" s="97"/>
+      <c r="Y61" s="97"/>
+      <c r="Z61" s="97"/>
+      <c r="AA61" s="97"/>
+      <c r="AB61" s="97"/>
     </row>
-    <row r="62" spans="1:39" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="13"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
-      <c r="L62" s="13"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
-      <c r="Q62" s="13"/>
-      <c r="R62" s="13"/>
-      <c r="S62" s="13"/>
-      <c r="T62" s="13"/>
-      <c r="U62" s="13"/>
-      <c r="V62" s="13"/>
-      <c r="W62" s="13"/>
-      <c r="X62" s="13"/>
-      <c r="Y62" s="13"/>
-      <c r="Z62" s="13"/>
-      <c r="AA62" s="13"/>
-      <c r="AB62" s="13"/>
+    <row r="62" spans="1:39" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="12"/>
+      <c r="H62" s="12"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="12"/>
+      <c r="S62" s="12"/>
+      <c r="T62" s="12"/>
+      <c r="U62" s="12"/>
+      <c r="V62" s="12"/>
+      <c r="W62" s="12"/>
+      <c r="X62" s="12"/>
+      <c r="Y62" s="12"/>
+      <c r="Z62" s="12"/>
+      <c r="AA62" s="12"/>
+      <c r="AB62" s="12"/>
     </row>
-    <row r="63" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="11">
+    <row r="63" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
         <v>1</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="101"/>
-      <c r="D63" s="102"/>
-      <c r="E63" s="102"/>
-      <c r="F63" s="102"/>
-      <c r="G63" s="102"/>
-      <c r="H63" s="102"/>
-      <c r="I63" s="102"/>
-      <c r="J63" s="102"/>
-      <c r="K63" s="102"/>
-      <c r="L63" s="102"/>
-      <c r="M63" s="102"/>
-      <c r="N63" s="102"/>
-      <c r="O63" s="102"/>
-      <c r="P63" s="102"/>
-      <c r="Q63" s="102"/>
-      <c r="R63" s="102"/>
-      <c r="S63" s="102"/>
-      <c r="T63" s="102"/>
-      <c r="U63" s="102"/>
-      <c r="V63" s="102"/>
-      <c r="W63" s="102"/>
-      <c r="X63" s="102"/>
-      <c r="Y63" s="102"/>
-      <c r="Z63" s="102"/>
-      <c r="AA63" s="102"/>
-      <c r="AB63" s="103"/>
+      <c r="C63" s="90"/>
+      <c r="D63" s="91"/>
+      <c r="E63" s="91"/>
+      <c r="F63" s="91"/>
+      <c r="G63" s="91"/>
+      <c r="H63" s="91"/>
+      <c r="I63" s="91"/>
+      <c r="J63" s="91"/>
+      <c r="K63" s="91"/>
+      <c r="L63" s="91"/>
+      <c r="M63" s="91"/>
+      <c r="N63" s="91"/>
+      <c r="O63" s="91"/>
+      <c r="P63" s="91"/>
+      <c r="Q63" s="91"/>
+      <c r="R63" s="91"/>
+      <c r="S63" s="91"/>
+      <c r="T63" s="91"/>
+      <c r="U63" s="91"/>
+      <c r="V63" s="91"/>
+      <c r="W63" s="91"/>
+      <c r="X63" s="91"/>
+      <c r="Y63" s="91"/>
+      <c r="Z63" s="91"/>
+      <c r="AA63" s="91"/>
+      <c r="AB63" s="92"/>
     </row>
-    <row r="64" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="12">
+    <row r="64" spans="1:39" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="11">
         <v>2</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C64" s="104"/>
-      <c r="D64" s="105"/>
-      <c r="E64" s="105"/>
-      <c r="F64" s="105"/>
-      <c r="G64" s="105"/>
-      <c r="H64" s="105"/>
-      <c r="I64" s="105"/>
-      <c r="J64" s="105"/>
-      <c r="K64" s="105"/>
-      <c r="L64" s="105"/>
-      <c r="M64" s="105"/>
-      <c r="N64" s="105"/>
-      <c r="O64" s="105"/>
-      <c r="P64" s="105"/>
-      <c r="Q64" s="105"/>
-      <c r="R64" s="105"/>
-      <c r="S64" s="105"/>
-      <c r="T64" s="105"/>
-      <c r="U64" s="105"/>
-      <c r="V64" s="105"/>
-      <c r="W64" s="105"/>
-      <c r="X64" s="105"/>
-      <c r="Y64" s="105"/>
-      <c r="Z64" s="105"/>
-      <c r="AA64" s="105"/>
-      <c r="AB64" s="106"/>
+      <c r="C64" s="93"/>
+      <c r="D64" s="94"/>
+      <c r="E64" s="94"/>
+      <c r="F64" s="94"/>
+      <c r="G64" s="94"/>
+      <c r="H64" s="94"/>
+      <c r="I64" s="94"/>
+      <c r="J64" s="94"/>
+      <c r="K64" s="94"/>
+      <c r="L64" s="94"/>
+      <c r="M64" s="94"/>
+      <c r="N64" s="94"/>
+      <c r="O64" s="94"/>
+      <c r="P64" s="94"/>
+      <c r="Q64" s="94"/>
+      <c r="R64" s="94"/>
+      <c r="S64" s="94"/>
+      <c r="T64" s="94"/>
+      <c r="U64" s="94"/>
+      <c r="V64" s="94"/>
+      <c r="W64" s="94"/>
+      <c r="X64" s="94"/>
+      <c r="Y64" s="94"/>
+      <c r="Z64" s="94"/>
+      <c r="AA64" s="94"/>
+      <c r="AB64" s="95"/>
     </row>
-    <row r="65" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="14">
+    <row r="65" spans="1:28" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="13">
         <v>3</v>
       </c>
-      <c r="B65" s="107" t="s">
+      <c r="B65" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="C65" s="107"/>
-      <c r="D65" s="107"/>
-      <c r="E65" s="107"/>
-      <c r="F65" s="107"/>
-      <c r="G65" s="107"/>
-      <c r="H65" s="107"/>
-      <c r="I65" s="107"/>
-      <c r="J65" s="107"/>
-      <c r="K65" s="107"/>
-      <c r="L65" s="108"/>
-      <c r="M65" s="108"/>
-      <c r="N65" s="108"/>
-      <c r="O65" s="108"/>
-      <c r="P65" s="108"/>
-      <c r="Q65" s="108"/>
-      <c r="R65" s="108"/>
-      <c r="S65" s="108"/>
-      <c r="T65" s="108"/>
-      <c r="U65" s="108"/>
-      <c r="V65" s="108"/>
-      <c r="W65" s="108"/>
-      <c r="X65" s="108"/>
-      <c r="Y65" s="108"/>
-      <c r="Z65" s="108"/>
-      <c r="AA65" s="108"/>
-      <c r="AB65" s="109"/>
+      <c r="C65" s="104"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="104"/>
+      <c r="F65" s="104"/>
+      <c r="G65" s="104"/>
+      <c r="H65" s="104"/>
+      <c r="I65" s="104"/>
+      <c r="J65" s="104"/>
+      <c r="K65" s="104"/>
+      <c r="L65" s="105"/>
+      <c r="M65" s="105"/>
+      <c r="N65" s="105"/>
+      <c r="O65" s="105"/>
+      <c r="P65" s="105"/>
+      <c r="Q65" s="105"/>
+      <c r="R65" s="105"/>
+      <c r="S65" s="105"/>
+      <c r="T65" s="105"/>
+      <c r="U65" s="105"/>
+      <c r="V65" s="105"/>
+      <c r="W65" s="105"/>
+      <c r="X65" s="105"/>
+      <c r="Y65" s="105"/>
+      <c r="Z65" s="105"/>
+      <c r="AA65" s="105"/>
+      <c r="AB65" s="106"/>
     </row>
-    <row r="66" spans="1:28" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="19"/>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="16"/>
-      <c r="L66" s="94" t="s">
+    <row r="66" spans="1:28" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="18"/>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="M66" s="95"/>
-      <c r="N66" s="95"/>
-      <c r="O66" s="95"/>
-      <c r="P66" s="95"/>
-      <c r="Q66" s="95"/>
-      <c r="R66" s="96"/>
-      <c r="S66" s="94" t="s">
+      <c r="M66" s="99"/>
+      <c r="N66" s="99"/>
+      <c r="O66" s="99"/>
+      <c r="P66" s="99"/>
+      <c r="Q66" s="99"/>
+      <c r="R66" s="109"/>
+      <c r="S66" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="T66" s="110"/>
-      <c r="U66" s="94" t="s">
+      <c r="T66" s="108"/>
+      <c r="U66" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="V66" s="95"/>
-      <c r="W66" s="95"/>
-      <c r="X66" s="95"/>
-      <c r="Y66" s="95"/>
-      <c r="Z66" s="95"/>
-      <c r="AA66" s="95"/>
-      <c r="AB66" s="111"/>
+      <c r="V66" s="99"/>
+      <c r="W66" s="99"/>
+      <c r="X66" s="99"/>
+      <c r="Y66" s="99"/>
+      <c r="Z66" s="99"/>
+      <c r="AA66" s="99"/>
+      <c r="AB66" s="100"/>
     </row>
-    <row r="67" spans="1:28" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="17" t="s">
+    <row r="67" spans="1:28" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B67" s="18" t="s">
+      <c r="B67" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="94" t="s">
+      <c r="C67" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="D67" s="95"/>
-      <c r="E67" s="95"/>
-      <c r="F67" s="95"/>
-      <c r="G67" s="95"/>
-      <c r="H67" s="95"/>
-      <c r="I67" s="96"/>
-      <c r="J67" s="94" t="s">
+      <c r="D67" s="99"/>
+      <c r="E67" s="99"/>
+      <c r="F67" s="99"/>
+      <c r="G67" s="99"/>
+      <c r="H67" s="99"/>
+      <c r="I67" s="109"/>
+      <c r="J67" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="K67" s="96"/>
-      <c r="L67" s="97" t="s">
+      <c r="K67" s="109"/>
+      <c r="L67" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="M67" s="98"/>
-      <c r="N67" s="98"/>
-      <c r="O67" s="98"/>
-      <c r="P67" s="98"/>
-      <c r="Q67" s="98"/>
-      <c r="R67" s="99"/>
-      <c r="S67" s="97" t="s">
+      <c r="M67" s="102"/>
+      <c r="N67" s="102"/>
+      <c r="O67" s="102"/>
+      <c r="P67" s="102"/>
+      <c r="Q67" s="102"/>
+      <c r="R67" s="107"/>
+      <c r="S67" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="T67" s="99"/>
-      <c r="U67" s="97" t="s">
+      <c r="T67" s="107"/>
+      <c r="U67" s="101" t="s">
         <v>36</v>
       </c>
-      <c r="V67" s="98"/>
-      <c r="W67" s="98"/>
-      <c r="X67" s="98"/>
-      <c r="Y67" s="98"/>
-      <c r="Z67" s="98"/>
-      <c r="AA67" s="98"/>
-      <c r="AB67" s="100"/>
+      <c r="V67" s="102"/>
+      <c r="W67" s="102"/>
+      <c r="X67" s="102"/>
+      <c r="Y67" s="102"/>
+      <c r="Z67" s="102"/>
+      <c r="AA67" s="102"/>
+      <c r="AB67" s="103"/>
     </row>
-    <row r="68" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="84">
+    <row r="68" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="74">
         <v>21</v>
       </c>
-      <c r="B68" s="85"/>
-      <c r="C68" s="86"/>
-      <c r="D68" s="87"/>
-      <c r="E68" s="90" t="s">
+      <c r="B68" s="75"/>
+      <c r="C68" s="76"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F68" s="87"/>
-      <c r="G68" s="87"/>
-      <c r="H68" s="90" t="s">
+      <c r="F68" s="58"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I68" s="87"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="32" t="s">
+      <c r="I68" s="58"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L68" s="70"/>
-      <c r="M68" s="71"/>
-      <c r="N68" s="74" t="s">
+      <c r="L68" s="62"/>
+      <c r="M68" s="44"/>
+      <c r="N68" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O68" s="71"/>
-      <c r="P68" s="74" t="s">
+      <c r="O68" s="44"/>
+      <c r="P68" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q68" s="71"/>
-      <c r="R68" s="76" t="s">
+      <c r="Q68" s="44"/>
+      <c r="R68" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S68" s="8"/>
-      <c r="T68" s="36" t="s">
+      <c r="S68" s="7"/>
+      <c r="T68" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U68" s="78"/>
-      <c r="V68" s="79"/>
-      <c r="W68" s="79"/>
-      <c r="X68" s="79"/>
-      <c r="Y68" s="79"/>
-      <c r="Z68" s="79"/>
-      <c r="AA68" s="79"/>
-      <c r="AB68" s="80"/>
+      <c r="U68" s="68"/>
+      <c r="V68" s="69"/>
+      <c r="W68" s="69"/>
+      <c r="X68" s="69"/>
+      <c r="Y68" s="69"/>
+      <c r="Z68" s="69"/>
+      <c r="AA68" s="69"/>
+      <c r="AB68" s="70"/>
     </row>
-    <row r="69" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="84"/>
-      <c r="B69" s="85"/>
-      <c r="C69" s="88"/>
-      <c r="D69" s="89"/>
-      <c r="E69" s="91"/>
-      <c r="F69" s="89"/>
-      <c r="G69" s="89"/>
-      <c r="H69" s="91"/>
-      <c r="I69" s="89"/>
-      <c r="J69" s="26"/>
-      <c r="K69" s="33" t="s">
+    <row r="69" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="74"/>
+      <c r="B69" s="75"/>
+      <c r="C69" s="77"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="61"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="59"/>
+      <c r="H69" s="61"/>
+      <c r="I69" s="59"/>
+      <c r="J69" s="25"/>
+      <c r="K69" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L69" s="72"/>
-      <c r="M69" s="73"/>
-      <c r="N69" s="75"/>
-      <c r="O69" s="73"/>
-      <c r="P69" s="75"/>
-      <c r="Q69" s="73"/>
-      <c r="R69" s="77"/>
-      <c r="S69" s="26"/>
-      <c r="T69" s="37" t="s">
+      <c r="L69" s="63"/>
+      <c r="M69" s="45"/>
+      <c r="N69" s="65"/>
+      <c r="O69" s="45"/>
+      <c r="P69" s="65"/>
+      <c r="Q69" s="45"/>
+      <c r="R69" s="67"/>
+      <c r="S69" s="25"/>
+      <c r="T69" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U69" s="81"/>
-      <c r="V69" s="82"/>
-      <c r="W69" s="82"/>
-      <c r="X69" s="82"/>
-      <c r="Y69" s="82"/>
-      <c r="Z69" s="82"/>
-      <c r="AA69" s="82"/>
-      <c r="AB69" s="83"/>
+      <c r="U69" s="71"/>
+      <c r="V69" s="72"/>
+      <c r="W69" s="72"/>
+      <c r="X69" s="72"/>
+      <c r="Y69" s="72"/>
+      <c r="Z69" s="72"/>
+      <c r="AA69" s="72"/>
+      <c r="AB69" s="73"/>
     </row>
-    <row r="70" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="84">
+    <row r="70" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="74">
         <v>22</v>
       </c>
-      <c r="B70" s="85"/>
-      <c r="C70" s="86"/>
-      <c r="D70" s="87"/>
-      <c r="E70" s="90" t="s">
+      <c r="B70" s="75"/>
+      <c r="C70" s="76"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F70" s="87"/>
-      <c r="G70" s="87"/>
-      <c r="H70" s="90" t="s">
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I70" s="87"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="32" t="s">
+      <c r="I70" s="58"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L70" s="70"/>
-      <c r="M70" s="71"/>
-      <c r="N70" s="74" t="s">
+      <c r="L70" s="62"/>
+      <c r="M70" s="44"/>
+      <c r="N70" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O70" s="71"/>
-      <c r="P70" s="74" t="s">
+      <c r="O70" s="44"/>
+      <c r="P70" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q70" s="71"/>
-      <c r="R70" s="76" t="s">
+      <c r="Q70" s="44"/>
+      <c r="R70" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S70" s="8"/>
-      <c r="T70" s="36" t="s">
+      <c r="S70" s="7"/>
+      <c r="T70" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U70" s="78"/>
-      <c r="V70" s="79"/>
-      <c r="W70" s="79"/>
-      <c r="X70" s="79"/>
-      <c r="Y70" s="79"/>
-      <c r="Z70" s="79"/>
-      <c r="AA70" s="79"/>
-      <c r="AB70" s="80"/>
+      <c r="U70" s="68"/>
+      <c r="V70" s="69"/>
+      <c r="W70" s="69"/>
+      <c r="X70" s="69"/>
+      <c r="Y70" s="69"/>
+      <c r="Z70" s="69"/>
+      <c r="AA70" s="69"/>
+      <c r="AB70" s="70"/>
     </row>
-    <row r="71" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="84"/>
-      <c r="B71" s="85"/>
-      <c r="C71" s="88"/>
-      <c r="D71" s="89"/>
-      <c r="E71" s="91"/>
-      <c r="F71" s="89"/>
-      <c r="G71" s="89"/>
-      <c r="H71" s="91"/>
-      <c r="I71" s="89"/>
-      <c r="J71" s="26"/>
-      <c r="K71" s="33" t="s">
+    <row r="71" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="74"/>
+      <c r="B71" s="75"/>
+      <c r="C71" s="77"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="61"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="59"/>
+      <c r="H71" s="61"/>
+      <c r="I71" s="59"/>
+      <c r="J71" s="25"/>
+      <c r="K71" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L71" s="72"/>
-      <c r="M71" s="73"/>
-      <c r="N71" s="75"/>
-      <c r="O71" s="73"/>
-      <c r="P71" s="75"/>
-      <c r="Q71" s="73"/>
-      <c r="R71" s="77"/>
-      <c r="S71" s="26"/>
-      <c r="T71" s="37" t="s">
+      <c r="L71" s="63"/>
+      <c r="M71" s="45"/>
+      <c r="N71" s="65"/>
+      <c r="O71" s="45"/>
+      <c r="P71" s="65"/>
+      <c r="Q71" s="45"/>
+      <c r="R71" s="67"/>
+      <c r="S71" s="25"/>
+      <c r="T71" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U71" s="81"/>
-      <c r="V71" s="82"/>
-      <c r="W71" s="82"/>
-      <c r="X71" s="82"/>
-      <c r="Y71" s="82"/>
-      <c r="Z71" s="82"/>
-      <c r="AA71" s="82"/>
-      <c r="AB71" s="83"/>
+      <c r="U71" s="71"/>
+      <c r="V71" s="72"/>
+      <c r="W71" s="72"/>
+      <c r="X71" s="72"/>
+      <c r="Y71" s="72"/>
+      <c r="Z71" s="72"/>
+      <c r="AA71" s="72"/>
+      <c r="AB71" s="73"/>
     </row>
-    <row r="72" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="84">
+    <row r="72" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="74">
         <v>23</v>
       </c>
-      <c r="B72" s="85"/>
-      <c r="C72" s="86"/>
-      <c r="D72" s="87"/>
-      <c r="E72" s="90" t="s">
+      <c r="B72" s="75"/>
+      <c r="C72" s="76"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F72" s="87"/>
-      <c r="G72" s="87"/>
-      <c r="H72" s="90" t="s">
+      <c r="F72" s="58"/>
+      <c r="G72" s="58"/>
+      <c r="H72" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I72" s="87"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="32" t="s">
+      <c r="I72" s="58"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L72" s="70"/>
-      <c r="M72" s="71"/>
-      <c r="N72" s="74" t="s">
+      <c r="L72" s="62"/>
+      <c r="M72" s="44"/>
+      <c r="N72" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O72" s="71"/>
-      <c r="P72" s="74" t="s">
+      <c r="O72" s="44"/>
+      <c r="P72" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q72" s="71"/>
-      <c r="R72" s="76" t="s">
+      <c r="Q72" s="44"/>
+      <c r="R72" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S72" s="8"/>
-      <c r="T72" s="36" t="s">
+      <c r="S72" s="7"/>
+      <c r="T72" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U72" s="78"/>
-      <c r="V72" s="79"/>
-      <c r="W72" s="79"/>
-      <c r="X72" s="79"/>
-      <c r="Y72" s="79"/>
-      <c r="Z72" s="79"/>
-      <c r="AA72" s="79"/>
-      <c r="AB72" s="80"/>
+      <c r="U72" s="68"/>
+      <c r="V72" s="69"/>
+      <c r="W72" s="69"/>
+      <c r="X72" s="69"/>
+      <c r="Y72" s="69"/>
+      <c r="Z72" s="69"/>
+      <c r="AA72" s="69"/>
+      <c r="AB72" s="70"/>
     </row>
-    <row r="73" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="84"/>
-      <c r="B73" s="85"/>
-      <c r="C73" s="88"/>
-      <c r="D73" s="89"/>
-      <c r="E73" s="91"/>
-      <c r="F73" s="89"/>
-      <c r="G73" s="89"/>
-      <c r="H73" s="91"/>
-      <c r="I73" s="89"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="33" t="s">
+    <row r="73" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="74"/>
+      <c r="B73" s="75"/>
+      <c r="C73" s="77"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="61"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="59"/>
+      <c r="H73" s="61"/>
+      <c r="I73" s="59"/>
+      <c r="J73" s="25"/>
+      <c r="K73" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L73" s="72"/>
-      <c r="M73" s="73"/>
-      <c r="N73" s="75"/>
-      <c r="O73" s="73"/>
-      <c r="P73" s="75"/>
-      <c r="Q73" s="73"/>
-      <c r="R73" s="77"/>
-      <c r="S73" s="26"/>
-      <c r="T73" s="37" t="s">
+      <c r="L73" s="63"/>
+      <c r="M73" s="45"/>
+      <c r="N73" s="65"/>
+      <c r="O73" s="45"/>
+      <c r="P73" s="65"/>
+      <c r="Q73" s="45"/>
+      <c r="R73" s="67"/>
+      <c r="S73" s="25"/>
+      <c r="T73" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U73" s="81"/>
-      <c r="V73" s="82"/>
-      <c r="W73" s="82"/>
-      <c r="X73" s="82"/>
-      <c r="Y73" s="82"/>
-      <c r="Z73" s="82"/>
-      <c r="AA73" s="82"/>
-      <c r="AB73" s="83"/>
+      <c r="U73" s="71"/>
+      <c r="V73" s="72"/>
+      <c r="W73" s="72"/>
+      <c r="X73" s="72"/>
+      <c r="Y73" s="72"/>
+      <c r="Z73" s="72"/>
+      <c r="AA73" s="72"/>
+      <c r="AB73" s="73"/>
     </row>
-    <row r="74" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="84">
+    <row r="74" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="74">
         <v>24</v>
       </c>
-      <c r="B74" s="85"/>
-      <c r="C74" s="86"/>
-      <c r="D74" s="87"/>
-      <c r="E74" s="90" t="s">
+      <c r="B74" s="75"/>
+      <c r="C74" s="76"/>
+      <c r="D74" s="58"/>
+      <c r="E74" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F74" s="87"/>
-      <c r="G74" s="87"/>
-      <c r="H74" s="90" t="s">
+      <c r="F74" s="58"/>
+      <c r="G74" s="58"/>
+      <c r="H74" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I74" s="87"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="32" t="s">
+      <c r="I74" s="58"/>
+      <c r="J74" s="7"/>
+      <c r="K74" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L74" s="70"/>
-      <c r="M74" s="71"/>
-      <c r="N74" s="74" t="s">
+      <c r="L74" s="62"/>
+      <c r="M74" s="44"/>
+      <c r="N74" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O74" s="71"/>
-      <c r="P74" s="74" t="s">
+      <c r="O74" s="44"/>
+      <c r="P74" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q74" s="71"/>
-      <c r="R74" s="76" t="s">
+      <c r="Q74" s="44"/>
+      <c r="R74" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S74" s="8"/>
-      <c r="T74" s="36" t="s">
+      <c r="S74" s="7"/>
+      <c r="T74" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U74" s="78"/>
-      <c r="V74" s="79"/>
-      <c r="W74" s="79"/>
-      <c r="X74" s="79"/>
-      <c r="Y74" s="79"/>
-      <c r="Z74" s="79"/>
-      <c r="AA74" s="79"/>
-      <c r="AB74" s="80"/>
+      <c r="U74" s="68"/>
+      <c r="V74" s="69"/>
+      <c r="W74" s="69"/>
+      <c r="X74" s="69"/>
+      <c r="Y74" s="69"/>
+      <c r="Z74" s="69"/>
+      <c r="AA74" s="69"/>
+      <c r="AB74" s="70"/>
     </row>
-    <row r="75" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="84"/>
-      <c r="B75" s="85"/>
-      <c r="C75" s="88"/>
-      <c r="D75" s="89"/>
-      <c r="E75" s="91"/>
-      <c r="F75" s="89"/>
-      <c r="G75" s="89"/>
-      <c r="H75" s="91"/>
-      <c r="I75" s="89"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="33" t="s">
+    <row r="75" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="74"/>
+      <c r="B75" s="75"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="61"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="61"/>
+      <c r="I75" s="59"/>
+      <c r="J75" s="25"/>
+      <c r="K75" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L75" s="72"/>
-      <c r="M75" s="73"/>
-      <c r="N75" s="75"/>
-      <c r="O75" s="73"/>
-      <c r="P75" s="75"/>
-      <c r="Q75" s="73"/>
-      <c r="R75" s="77"/>
-      <c r="S75" s="26"/>
-      <c r="T75" s="37" t="s">
+      <c r="L75" s="63"/>
+      <c r="M75" s="45"/>
+      <c r="N75" s="65"/>
+      <c r="O75" s="45"/>
+      <c r="P75" s="65"/>
+      <c r="Q75" s="45"/>
+      <c r="R75" s="67"/>
+      <c r="S75" s="25"/>
+      <c r="T75" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U75" s="81"/>
-      <c r="V75" s="82"/>
-      <c r="W75" s="82"/>
-      <c r="X75" s="82"/>
-      <c r="Y75" s="82"/>
-      <c r="Z75" s="82"/>
-      <c r="AA75" s="82"/>
-      <c r="AB75" s="83"/>
+      <c r="U75" s="71"/>
+      <c r="V75" s="72"/>
+      <c r="W75" s="72"/>
+      <c r="X75" s="72"/>
+      <c r="Y75" s="72"/>
+      <c r="Z75" s="72"/>
+      <c r="AA75" s="72"/>
+      <c r="AB75" s="73"/>
     </row>
-    <row r="76" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="84">
+    <row r="76" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="74">
         <v>25</v>
       </c>
-      <c r="B76" s="85"/>
-      <c r="C76" s="86"/>
-      <c r="D76" s="87"/>
-      <c r="E76" s="90" t="s">
+      <c r="B76" s="75"/>
+      <c r="C76" s="76"/>
+      <c r="D76" s="58"/>
+      <c r="E76" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F76" s="87"/>
-      <c r="G76" s="87"/>
-      <c r="H76" s="90" t="s">
+      <c r="F76" s="58"/>
+      <c r="G76" s="58"/>
+      <c r="H76" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I76" s="87"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="32" t="s">
+      <c r="I76" s="58"/>
+      <c r="J76" s="7"/>
+      <c r="K76" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L76" s="70"/>
-      <c r="M76" s="71"/>
-      <c r="N76" s="74" t="s">
+      <c r="L76" s="62"/>
+      <c r="M76" s="44"/>
+      <c r="N76" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O76" s="71"/>
-      <c r="P76" s="74" t="s">
+      <c r="O76" s="44"/>
+      <c r="P76" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q76" s="71"/>
-      <c r="R76" s="76" t="s">
+      <c r="Q76" s="44"/>
+      <c r="R76" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S76" s="8"/>
-      <c r="T76" s="36" t="s">
+      <c r="S76" s="7"/>
+      <c r="T76" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U76" s="78"/>
-      <c r="V76" s="79"/>
-      <c r="W76" s="79"/>
-      <c r="X76" s="79"/>
-      <c r="Y76" s="79"/>
-      <c r="Z76" s="79"/>
-      <c r="AA76" s="79"/>
-      <c r="AB76" s="80"/>
+      <c r="U76" s="68"/>
+      <c r="V76" s="69"/>
+      <c r="W76" s="69"/>
+      <c r="X76" s="69"/>
+      <c r="Y76" s="69"/>
+      <c r="Z76" s="69"/>
+      <c r="AA76" s="69"/>
+      <c r="AB76" s="70"/>
     </row>
-    <row r="77" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="84"/>
-      <c r="B77" s="85"/>
-      <c r="C77" s="88"/>
-      <c r="D77" s="89"/>
-      <c r="E77" s="91"/>
-      <c r="F77" s="89"/>
-      <c r="G77" s="89"/>
-      <c r="H77" s="91"/>
-      <c r="I77" s="89"/>
-      <c r="J77" s="26"/>
-      <c r="K77" s="33" t="s">
+    <row r="77" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="74"/>
+      <c r="B77" s="75"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="61"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="59"/>
+      <c r="H77" s="61"/>
+      <c r="I77" s="59"/>
+      <c r="J77" s="25"/>
+      <c r="K77" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L77" s="72"/>
-      <c r="M77" s="73"/>
-      <c r="N77" s="75"/>
-      <c r="O77" s="73"/>
-      <c r="P77" s="75"/>
-      <c r="Q77" s="73"/>
-      <c r="R77" s="77"/>
-      <c r="S77" s="26"/>
-      <c r="T77" s="37" t="s">
+      <c r="L77" s="63"/>
+      <c r="M77" s="45"/>
+      <c r="N77" s="65"/>
+      <c r="O77" s="45"/>
+      <c r="P77" s="65"/>
+      <c r="Q77" s="45"/>
+      <c r="R77" s="67"/>
+      <c r="S77" s="25"/>
+      <c r="T77" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U77" s="81"/>
-      <c r="V77" s="82"/>
-      <c r="W77" s="82"/>
-      <c r="X77" s="82"/>
-      <c r="Y77" s="82"/>
-      <c r="Z77" s="82"/>
-      <c r="AA77" s="82"/>
-      <c r="AB77" s="83"/>
+      <c r="U77" s="71"/>
+      <c r="V77" s="72"/>
+      <c r="W77" s="72"/>
+      <c r="X77" s="72"/>
+      <c r="Y77" s="72"/>
+      <c r="Z77" s="72"/>
+      <c r="AA77" s="72"/>
+      <c r="AB77" s="73"/>
     </row>
-    <row r="78" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="84">
+    <row r="78" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="74">
         <v>26</v>
       </c>
-      <c r="B78" s="85"/>
-      <c r="C78" s="86"/>
-      <c r="D78" s="87"/>
-      <c r="E78" s="90" t="s">
+      <c r="B78" s="75"/>
+      <c r="C78" s="76"/>
+      <c r="D78" s="58"/>
+      <c r="E78" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F78" s="87"/>
-      <c r="G78" s="87"/>
-      <c r="H78" s="90" t="s">
+      <c r="F78" s="58"/>
+      <c r="G78" s="58"/>
+      <c r="H78" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I78" s="87"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="32" t="s">
+      <c r="I78" s="58"/>
+      <c r="J78" s="7"/>
+      <c r="K78" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L78" s="70"/>
-      <c r="M78" s="71"/>
-      <c r="N78" s="74" t="s">
+      <c r="L78" s="62"/>
+      <c r="M78" s="44"/>
+      <c r="N78" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O78" s="71"/>
-      <c r="P78" s="74" t="s">
+      <c r="O78" s="44"/>
+      <c r="P78" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q78" s="71"/>
-      <c r="R78" s="76" t="s">
+      <c r="Q78" s="44"/>
+      <c r="R78" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S78" s="8"/>
-      <c r="T78" s="36" t="s">
+      <c r="S78" s="7"/>
+      <c r="T78" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U78" s="78"/>
-      <c r="V78" s="79"/>
-      <c r="W78" s="79"/>
-      <c r="X78" s="79"/>
-      <c r="Y78" s="79"/>
-      <c r="Z78" s="79"/>
-      <c r="AA78" s="79"/>
-      <c r="AB78" s="80"/>
+      <c r="U78" s="68"/>
+      <c r="V78" s="69"/>
+      <c r="W78" s="69"/>
+      <c r="X78" s="69"/>
+      <c r="Y78" s="69"/>
+      <c r="Z78" s="69"/>
+      <c r="AA78" s="69"/>
+      <c r="AB78" s="70"/>
     </row>
-    <row r="79" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="84"/>
-      <c r="B79" s="85"/>
-      <c r="C79" s="88"/>
-      <c r="D79" s="89"/>
-      <c r="E79" s="91"/>
-      <c r="F79" s="89"/>
-      <c r="G79" s="89"/>
-      <c r="H79" s="91"/>
-      <c r="I79" s="89"/>
-      <c r="J79" s="26"/>
-      <c r="K79" s="33" t="s">
+    <row r="79" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="74"/>
+      <c r="B79" s="75"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="61"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="59"/>
+      <c r="H79" s="61"/>
+      <c r="I79" s="59"/>
+      <c r="J79" s="25"/>
+      <c r="K79" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L79" s="72"/>
-      <c r="M79" s="73"/>
-      <c r="N79" s="75"/>
-      <c r="O79" s="73"/>
-      <c r="P79" s="75"/>
-      <c r="Q79" s="73"/>
-      <c r="R79" s="77"/>
-      <c r="S79" s="26"/>
-      <c r="T79" s="37" t="s">
+      <c r="L79" s="63"/>
+      <c r="M79" s="45"/>
+      <c r="N79" s="65"/>
+      <c r="O79" s="45"/>
+      <c r="P79" s="65"/>
+      <c r="Q79" s="45"/>
+      <c r="R79" s="67"/>
+      <c r="S79" s="25"/>
+      <c r="T79" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U79" s="81"/>
-      <c r="V79" s="82"/>
-      <c r="W79" s="82"/>
-      <c r="X79" s="82"/>
-      <c r="Y79" s="82"/>
-      <c r="Z79" s="82"/>
-      <c r="AA79" s="82"/>
-      <c r="AB79" s="83"/>
+      <c r="U79" s="71"/>
+      <c r="V79" s="72"/>
+      <c r="W79" s="72"/>
+      <c r="X79" s="72"/>
+      <c r="Y79" s="72"/>
+      <c r="Z79" s="72"/>
+      <c r="AA79" s="72"/>
+      <c r="AB79" s="73"/>
     </row>
-    <row r="80" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="84">
+    <row r="80" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="74">
         <v>27</v>
       </c>
-      <c r="B80" s="85"/>
-      <c r="C80" s="86"/>
-      <c r="D80" s="87"/>
-      <c r="E80" s="90" t="s">
+      <c r="B80" s="75"/>
+      <c r="C80" s="76"/>
+      <c r="D80" s="58"/>
+      <c r="E80" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F80" s="87"/>
-      <c r="G80" s="87"/>
-      <c r="H80" s="90" t="s">
+      <c r="F80" s="58"/>
+      <c r="G80" s="58"/>
+      <c r="H80" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I80" s="87"/>
-      <c r="J80" s="8"/>
-      <c r="K80" s="32" t="s">
+      <c r="I80" s="58"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L80" s="70"/>
-      <c r="M80" s="71"/>
-      <c r="N80" s="74" t="s">
+      <c r="L80" s="62"/>
+      <c r="M80" s="44"/>
+      <c r="N80" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O80" s="71"/>
-      <c r="P80" s="74" t="s">
+      <c r="O80" s="44"/>
+      <c r="P80" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q80" s="71"/>
-      <c r="R80" s="76" t="s">
+      <c r="Q80" s="44"/>
+      <c r="R80" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S80" s="8"/>
-      <c r="T80" s="36" t="s">
+      <c r="S80" s="7"/>
+      <c r="T80" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U80" s="78"/>
-      <c r="V80" s="79"/>
-      <c r="W80" s="79"/>
-      <c r="X80" s="79"/>
-      <c r="Y80" s="79"/>
-      <c r="Z80" s="79"/>
-      <c r="AA80" s="79"/>
-      <c r="AB80" s="80"/>
+      <c r="U80" s="68"/>
+      <c r="V80" s="69"/>
+      <c r="W80" s="69"/>
+      <c r="X80" s="69"/>
+      <c r="Y80" s="69"/>
+      <c r="Z80" s="69"/>
+      <c r="AA80" s="69"/>
+      <c r="AB80" s="70"/>
     </row>
-    <row r="81" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="84"/>
-      <c r="B81" s="85"/>
-      <c r="C81" s="88"/>
-      <c r="D81" s="89"/>
-      <c r="E81" s="91"/>
-      <c r="F81" s="89"/>
-      <c r="G81" s="89"/>
-      <c r="H81" s="91"/>
-      <c r="I81" s="89"/>
-      <c r="J81" s="26"/>
-      <c r="K81" s="33" t="s">
+    <row r="81" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="74"/>
+      <c r="B81" s="75"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="61"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="61"/>
+      <c r="I81" s="59"/>
+      <c r="J81" s="25"/>
+      <c r="K81" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L81" s="72"/>
-      <c r="M81" s="73"/>
-      <c r="N81" s="75"/>
-      <c r="O81" s="73"/>
-      <c r="P81" s="75"/>
-      <c r="Q81" s="73"/>
-      <c r="R81" s="77"/>
-      <c r="S81" s="26"/>
-      <c r="T81" s="37" t="s">
+      <c r="L81" s="63"/>
+      <c r="M81" s="45"/>
+      <c r="N81" s="65"/>
+      <c r="O81" s="45"/>
+      <c r="P81" s="65"/>
+      <c r="Q81" s="45"/>
+      <c r="R81" s="67"/>
+      <c r="S81" s="25"/>
+      <c r="T81" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U81" s="81"/>
-      <c r="V81" s="82"/>
-      <c r="W81" s="82"/>
-      <c r="X81" s="82"/>
-      <c r="Y81" s="82"/>
-      <c r="Z81" s="82"/>
-      <c r="AA81" s="82"/>
-      <c r="AB81" s="83"/>
+      <c r="U81" s="71"/>
+      <c r="V81" s="72"/>
+      <c r="W81" s="72"/>
+      <c r="X81" s="72"/>
+      <c r="Y81" s="72"/>
+      <c r="Z81" s="72"/>
+      <c r="AA81" s="72"/>
+      <c r="AB81" s="73"/>
     </row>
-    <row r="82" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="84">
+    <row r="82" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="74">
         <v>28</v>
       </c>
-      <c r="B82" s="85"/>
-      <c r="C82" s="86"/>
-      <c r="D82" s="87"/>
-      <c r="E82" s="90" t="s">
+      <c r="B82" s="75"/>
+      <c r="C82" s="76"/>
+      <c r="D82" s="58"/>
+      <c r="E82" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F82" s="87"/>
-      <c r="G82" s="87"/>
-      <c r="H82" s="90" t="s">
+      <c r="F82" s="58"/>
+      <c r="G82" s="58"/>
+      <c r="H82" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I82" s="87"/>
-      <c r="J82" s="8"/>
-      <c r="K82" s="32" t="s">
+      <c r="I82" s="58"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L82" s="70"/>
-      <c r="M82" s="71"/>
-      <c r="N82" s="74" t="s">
+      <c r="L82" s="62"/>
+      <c r="M82" s="44"/>
+      <c r="N82" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O82" s="71"/>
-      <c r="P82" s="74" t="s">
+      <c r="O82" s="44"/>
+      <c r="P82" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q82" s="71"/>
-      <c r="R82" s="76" t="s">
+      <c r="Q82" s="44"/>
+      <c r="R82" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S82" s="8"/>
-      <c r="T82" s="36" t="s">
+      <c r="S82" s="7"/>
+      <c r="T82" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U82" s="78"/>
-      <c r="V82" s="79"/>
-      <c r="W82" s="79"/>
-      <c r="X82" s="79"/>
-      <c r="Y82" s="79"/>
-      <c r="Z82" s="79"/>
-      <c r="AA82" s="79"/>
-      <c r="AB82" s="80"/>
+      <c r="U82" s="68"/>
+      <c r="V82" s="69"/>
+      <c r="W82" s="69"/>
+      <c r="X82" s="69"/>
+      <c r="Y82" s="69"/>
+      <c r="Z82" s="69"/>
+      <c r="AA82" s="69"/>
+      <c r="AB82" s="70"/>
     </row>
-    <row r="83" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="84"/>
-      <c r="B83" s="85"/>
-      <c r="C83" s="88"/>
-      <c r="D83" s="89"/>
-      <c r="E83" s="91"/>
-      <c r="F83" s="89"/>
-      <c r="G83" s="89"/>
-      <c r="H83" s="91"/>
-      <c r="I83" s="89"/>
-      <c r="J83" s="26"/>
-      <c r="K83" s="33" t="s">
+    <row r="83" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="74"/>
+      <c r="B83" s="75"/>
+      <c r="C83" s="77"/>
+      <c r="D83" s="59"/>
+      <c r="E83" s="61"/>
+      <c r="F83" s="59"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="61"/>
+      <c r="I83" s="59"/>
+      <c r="J83" s="25"/>
+      <c r="K83" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L83" s="72"/>
-      <c r="M83" s="73"/>
-      <c r="N83" s="75"/>
-      <c r="O83" s="73"/>
-      <c r="P83" s="75"/>
-      <c r="Q83" s="73"/>
-      <c r="R83" s="77"/>
-      <c r="S83" s="26"/>
-      <c r="T83" s="37" t="s">
+      <c r="L83" s="63"/>
+      <c r="M83" s="45"/>
+      <c r="N83" s="65"/>
+      <c r="O83" s="45"/>
+      <c r="P83" s="65"/>
+      <c r="Q83" s="45"/>
+      <c r="R83" s="67"/>
+      <c r="S83" s="25"/>
+      <c r="T83" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U83" s="81"/>
-      <c r="V83" s="82"/>
-      <c r="W83" s="82"/>
-      <c r="X83" s="82"/>
-      <c r="Y83" s="82"/>
-      <c r="Z83" s="82"/>
-      <c r="AA83" s="82"/>
-      <c r="AB83" s="83"/>
+      <c r="U83" s="71"/>
+      <c r="V83" s="72"/>
+      <c r="W83" s="72"/>
+      <c r="X83" s="72"/>
+      <c r="Y83" s="72"/>
+      <c r="Z83" s="72"/>
+      <c r="AA83" s="72"/>
+      <c r="AB83" s="73"/>
     </row>
-    <row r="84" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="84">
+    <row r="84" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="74">
         <v>29</v>
       </c>
-      <c r="B84" s="85"/>
-      <c r="C84" s="86"/>
-      <c r="D84" s="87"/>
-      <c r="E84" s="90" t="s">
+      <c r="B84" s="75"/>
+      <c r="C84" s="76"/>
+      <c r="D84" s="58"/>
+      <c r="E84" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F84" s="87"/>
-      <c r="G84" s="87"/>
-      <c r="H84" s="90" t="s">
+      <c r="F84" s="58"/>
+      <c r="G84" s="58"/>
+      <c r="H84" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I84" s="87"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="32" t="s">
+      <c r="I84" s="58"/>
+      <c r="J84" s="7"/>
+      <c r="K84" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L84" s="70"/>
-      <c r="M84" s="71"/>
-      <c r="N84" s="74" t="s">
+      <c r="L84" s="62"/>
+      <c r="M84" s="44"/>
+      <c r="N84" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O84" s="71"/>
-      <c r="P84" s="74" t="s">
+      <c r="O84" s="44"/>
+      <c r="P84" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q84" s="71"/>
-      <c r="R84" s="76" t="s">
+      <c r="Q84" s="44"/>
+      <c r="R84" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S84" s="8"/>
-      <c r="T84" s="36" t="s">
+      <c r="S84" s="7"/>
+      <c r="T84" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U84" s="78"/>
-      <c r="V84" s="79"/>
-      <c r="W84" s="79"/>
-      <c r="X84" s="79"/>
-      <c r="Y84" s="79"/>
-      <c r="Z84" s="79"/>
-      <c r="AA84" s="79"/>
-      <c r="AB84" s="80"/>
+      <c r="U84" s="68"/>
+      <c r="V84" s="69"/>
+      <c r="W84" s="69"/>
+      <c r="X84" s="69"/>
+      <c r="Y84" s="69"/>
+      <c r="Z84" s="69"/>
+      <c r="AA84" s="69"/>
+      <c r="AB84" s="70"/>
     </row>
-    <row r="85" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="84"/>
-      <c r="B85" s="85"/>
-      <c r="C85" s="88"/>
-      <c r="D85" s="89"/>
-      <c r="E85" s="91"/>
-      <c r="F85" s="89"/>
-      <c r="G85" s="89"/>
-      <c r="H85" s="91"/>
-      <c r="I85" s="89"/>
-      <c r="J85" s="26"/>
-      <c r="K85" s="33" t="s">
+    <row r="85" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="74"/>
+      <c r="B85" s="75"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="59"/>
+      <c r="E85" s="61"/>
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="61"/>
+      <c r="I85" s="59"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L85" s="72"/>
-      <c r="M85" s="73"/>
-      <c r="N85" s="75"/>
-      <c r="O85" s="73"/>
-      <c r="P85" s="75"/>
-      <c r="Q85" s="73"/>
-      <c r="R85" s="77"/>
-      <c r="S85" s="26"/>
-      <c r="T85" s="37" t="s">
+      <c r="L85" s="63"/>
+      <c r="M85" s="45"/>
+      <c r="N85" s="65"/>
+      <c r="O85" s="45"/>
+      <c r="P85" s="65"/>
+      <c r="Q85" s="45"/>
+      <c r="R85" s="67"/>
+      <c r="S85" s="25"/>
+      <c r="T85" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U85" s="81"/>
-      <c r="V85" s="82"/>
-      <c r="W85" s="82"/>
-      <c r="X85" s="82"/>
-      <c r="Y85" s="82"/>
-      <c r="Z85" s="82"/>
-      <c r="AA85" s="82"/>
-      <c r="AB85" s="83"/>
+      <c r="U85" s="71"/>
+      <c r="V85" s="72"/>
+      <c r="W85" s="72"/>
+      <c r="X85" s="72"/>
+      <c r="Y85" s="72"/>
+      <c r="Z85" s="72"/>
+      <c r="AA85" s="72"/>
+      <c r="AB85" s="73"/>
     </row>
-    <row r="86" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="84">
+    <row r="86" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="74">
         <v>30</v>
       </c>
-      <c r="B86" s="85"/>
-      <c r="C86" s="86"/>
-      <c r="D86" s="87"/>
-      <c r="E86" s="90" t="s">
+      <c r="B86" s="75"/>
+      <c r="C86" s="76"/>
+      <c r="D86" s="58"/>
+      <c r="E86" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F86" s="87"/>
-      <c r="G86" s="87"/>
-      <c r="H86" s="90" t="s">
+      <c r="F86" s="58"/>
+      <c r="G86" s="58"/>
+      <c r="H86" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I86" s="87"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="32" t="s">
+      <c r="I86" s="58"/>
+      <c r="J86" s="7"/>
+      <c r="K86" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L86" s="70"/>
-      <c r="M86" s="71"/>
-      <c r="N86" s="74" t="s">
+      <c r="L86" s="62"/>
+      <c r="M86" s="44"/>
+      <c r="N86" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O86" s="71"/>
-      <c r="P86" s="74" t="s">
+      <c r="O86" s="44"/>
+      <c r="P86" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="Q86" s="71"/>
-      <c r="R86" s="76" t="s">
+      <c r="Q86" s="44"/>
+      <c r="R86" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="S86" s="8"/>
-      <c r="T86" s="36" t="s">
+      <c r="S86" s="7"/>
+      <c r="T86" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U86" s="78"/>
-      <c r="V86" s="79"/>
-      <c r="W86" s="79"/>
-      <c r="X86" s="79"/>
-      <c r="Y86" s="79"/>
-      <c r="Z86" s="79"/>
-      <c r="AA86" s="79"/>
-      <c r="AB86" s="80"/>
+      <c r="U86" s="68"/>
+      <c r="V86" s="69"/>
+      <c r="W86" s="69"/>
+      <c r="X86" s="69"/>
+      <c r="Y86" s="69"/>
+      <c r="Z86" s="69"/>
+      <c r="AA86" s="69"/>
+      <c r="AB86" s="70"/>
     </row>
-    <row r="87" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A87" s="84"/>
-      <c r="B87" s="85"/>
-      <c r="C87" s="88"/>
-      <c r="D87" s="89"/>
-      <c r="E87" s="91"/>
-      <c r="F87" s="89"/>
-      <c r="G87" s="89"/>
-      <c r="H87" s="91"/>
-      <c r="I87" s="89"/>
-      <c r="J87" s="26"/>
-      <c r="K87" s="33" t="s">
+    <row r="87" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="74"/>
+      <c r="B87" s="75"/>
+      <c r="C87" s="77"/>
+      <c r="D87" s="59"/>
+      <c r="E87" s="61"/>
+      <c r="F87" s="59"/>
+      <c r="G87" s="59"/>
+      <c r="H87" s="61"/>
+      <c r="I87" s="59"/>
+      <c r="J87" s="25"/>
+      <c r="K87" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L87" s="72"/>
-      <c r="M87" s="73"/>
-      <c r="N87" s="75"/>
-      <c r="O87" s="73"/>
-      <c r="P87" s="75"/>
-      <c r="Q87" s="73"/>
-      <c r="R87" s="77"/>
-      <c r="S87" s="26"/>
-      <c r="T87" s="37" t="s">
+      <c r="L87" s="63"/>
+      <c r="M87" s="45"/>
+      <c r="N87" s="65"/>
+      <c r="O87" s="45"/>
+      <c r="P87" s="65"/>
+      <c r="Q87" s="45"/>
+      <c r="R87" s="67"/>
+      <c r="S87" s="25"/>
+      <c r="T87" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U87" s="81"/>
-      <c r="V87" s="82"/>
-      <c r="W87" s="82"/>
-      <c r="X87" s="82"/>
-      <c r="Y87" s="82"/>
-      <c r="Z87" s="82"/>
-      <c r="AA87" s="82"/>
-      <c r="AB87" s="83"/>
+      <c r="U87" s="71"/>
+      <c r="V87" s="72"/>
+      <c r="W87" s="72"/>
+      <c r="X87" s="72"/>
+      <c r="Y87" s="72"/>
+      <c r="Z87" s="72"/>
+      <c r="AA87" s="72"/>
+      <c r="AB87" s="73"/>
     </row>
-    <row r="88" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="84">
+    <row r="88" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="74">
         <v>31</v>
       </c>
-      <c r="B88" s="85"/>
-      <c r="C88" s="86"/>
-      <c r="D88" s="87"/>
-      <c r="E88" s="90" t="s">
+      <c r="B88" s="75"/>
+      <c r="C88" s="76"/>
+      <c r="D88" s="58"/>
+      <c r="E88" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F88" s="87"/>
-      <c r="G88" s="87"/>
-      <c r="H88" s="90" t="s">
+      <c r="F88" s="58"/>
+      <c r="G88" s="58"/>
+      <c r="H88" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I88" s="87"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="32" t="s">
+      <c r="I88" s="58"/>
+      <c r="J88" s="7"/>
+      <c r="K88" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L88" s="70"/>
-      <c r="M88" s="71"/>
-      <c r="N88" s="74" t="s">
+      <c r="L88" s="62"/>
+      <c r="M88" s="44"/>
+      <c r="N88" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O88" s="71"/>
-      <c r="P88" s="74" t="s">
+      <c r="O88" s="44"/>
+      <c r="P88" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q88" s="71"/>
-      <c r="R88" s="76" t="s">
+      <c r="Q88" s="44"/>
+      <c r="R88" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S88" s="8"/>
-      <c r="T88" s="36" t="s">
+      <c r="S88" s="7"/>
+      <c r="T88" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U88" s="78"/>
-      <c r="V88" s="79"/>
-      <c r="W88" s="79"/>
-      <c r="X88" s="79"/>
-      <c r="Y88" s="79"/>
-      <c r="Z88" s="79"/>
-      <c r="AA88" s="79"/>
-      <c r="AB88" s="80"/>
+      <c r="U88" s="68"/>
+      <c r="V88" s="69"/>
+      <c r="W88" s="69"/>
+      <c r="X88" s="69"/>
+      <c r="Y88" s="69"/>
+      <c r="Z88" s="69"/>
+      <c r="AA88" s="69"/>
+      <c r="AB88" s="70"/>
     </row>
-    <row r="89" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A89" s="84"/>
-      <c r="B89" s="85"/>
-      <c r="C89" s="88"/>
-      <c r="D89" s="89"/>
-      <c r="E89" s="91"/>
-      <c r="F89" s="89"/>
-      <c r="G89" s="89"/>
-      <c r="H89" s="91"/>
-      <c r="I89" s="89"/>
-      <c r="J89" s="26"/>
-      <c r="K89" s="33" t="s">
+    <row r="89" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="74"/>
+      <c r="B89" s="75"/>
+      <c r="C89" s="77"/>
+      <c r="D89" s="59"/>
+      <c r="E89" s="61"/>
+      <c r="F89" s="59"/>
+      <c r="G89" s="59"/>
+      <c r="H89" s="61"/>
+      <c r="I89" s="59"/>
+      <c r="J89" s="25"/>
+      <c r="K89" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L89" s="72"/>
-      <c r="M89" s="73"/>
-      <c r="N89" s="75"/>
-      <c r="O89" s="73"/>
-      <c r="P89" s="75"/>
-      <c r="Q89" s="73"/>
-      <c r="R89" s="77"/>
-      <c r="S89" s="26"/>
-      <c r="T89" s="37" t="s">
+      <c r="L89" s="63"/>
+      <c r="M89" s="45"/>
+      <c r="N89" s="65"/>
+      <c r="O89" s="45"/>
+      <c r="P89" s="65"/>
+      <c r="Q89" s="45"/>
+      <c r="R89" s="67"/>
+      <c r="S89" s="25"/>
+      <c r="T89" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U89" s="81"/>
-      <c r="V89" s="82"/>
-      <c r="W89" s="82"/>
-      <c r="X89" s="82"/>
-      <c r="Y89" s="82"/>
-      <c r="Z89" s="82"/>
-      <c r="AA89" s="82"/>
-      <c r="AB89" s="83"/>
+      <c r="U89" s="71"/>
+      <c r="V89" s="72"/>
+      <c r="W89" s="72"/>
+      <c r="X89" s="72"/>
+      <c r="Y89" s="72"/>
+      <c r="Z89" s="72"/>
+      <c r="AA89" s="72"/>
+      <c r="AB89" s="73"/>
     </row>
-    <row r="90" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A90" s="84">
+    <row r="90" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="74">
         <v>32</v>
       </c>
-      <c r="B90" s="85"/>
-      <c r="C90" s="86"/>
-      <c r="D90" s="87"/>
-      <c r="E90" s="90" t="s">
+      <c r="B90" s="75"/>
+      <c r="C90" s="76"/>
+      <c r="D90" s="58"/>
+      <c r="E90" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F90" s="87"/>
-      <c r="G90" s="87"/>
-      <c r="H90" s="90" t="s">
+      <c r="F90" s="58"/>
+      <c r="G90" s="58"/>
+      <c r="H90" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I90" s="87"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="32" t="s">
+      <c r="I90" s="58"/>
+      <c r="J90" s="7"/>
+      <c r="K90" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L90" s="70"/>
-      <c r="M90" s="71"/>
-      <c r="N90" s="74" t="s">
+      <c r="L90" s="62"/>
+      <c r="M90" s="44"/>
+      <c r="N90" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O90" s="71"/>
-      <c r="P90" s="74" t="s">
+      <c r="O90" s="44"/>
+      <c r="P90" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q90" s="71"/>
-      <c r="R90" s="76" t="s">
+      <c r="Q90" s="44"/>
+      <c r="R90" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S90" s="8"/>
-      <c r="T90" s="36" t="s">
+      <c r="S90" s="7"/>
+      <c r="T90" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U90" s="78"/>
-      <c r="V90" s="79"/>
-      <c r="W90" s="79"/>
-      <c r="X90" s="79"/>
-      <c r="Y90" s="79"/>
-      <c r="Z90" s="79"/>
-      <c r="AA90" s="79"/>
-      <c r="AB90" s="80"/>
+      <c r="U90" s="68"/>
+      <c r="V90" s="69"/>
+      <c r="W90" s="69"/>
+      <c r="X90" s="69"/>
+      <c r="Y90" s="69"/>
+      <c r="Z90" s="69"/>
+      <c r="AA90" s="69"/>
+      <c r="AB90" s="70"/>
     </row>
-    <row r="91" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="84"/>
-      <c r="B91" s="85"/>
-      <c r="C91" s="88"/>
-      <c r="D91" s="89"/>
-      <c r="E91" s="91"/>
-      <c r="F91" s="89"/>
-      <c r="G91" s="89"/>
-      <c r="H91" s="91"/>
-      <c r="I91" s="89"/>
-      <c r="J91" s="26"/>
-      <c r="K91" s="33" t="s">
+    <row r="91" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="74"/>
+      <c r="B91" s="75"/>
+      <c r="C91" s="77"/>
+      <c r="D91" s="59"/>
+      <c r="E91" s="61"/>
+      <c r="F91" s="59"/>
+      <c r="G91" s="59"/>
+      <c r="H91" s="61"/>
+      <c r="I91" s="59"/>
+      <c r="J91" s="25"/>
+      <c r="K91" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L91" s="72"/>
-      <c r="M91" s="73"/>
-      <c r="N91" s="75"/>
-      <c r="O91" s="73"/>
-      <c r="P91" s="75"/>
-      <c r="Q91" s="73"/>
-      <c r="R91" s="77"/>
-      <c r="S91" s="26"/>
-      <c r="T91" s="37" t="s">
+      <c r="L91" s="63"/>
+      <c r="M91" s="45"/>
+      <c r="N91" s="65"/>
+      <c r="O91" s="45"/>
+      <c r="P91" s="65"/>
+      <c r="Q91" s="45"/>
+      <c r="R91" s="67"/>
+      <c r="S91" s="25"/>
+      <c r="T91" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U91" s="81"/>
-      <c r="V91" s="82"/>
-      <c r="W91" s="82"/>
-      <c r="X91" s="82"/>
-      <c r="Y91" s="82"/>
-      <c r="Z91" s="82"/>
-      <c r="AA91" s="82"/>
-      <c r="AB91" s="83"/>
+      <c r="U91" s="71"/>
+      <c r="V91" s="72"/>
+      <c r="W91" s="72"/>
+      <c r="X91" s="72"/>
+      <c r="Y91" s="72"/>
+      <c r="Z91" s="72"/>
+      <c r="AA91" s="72"/>
+      <c r="AB91" s="73"/>
     </row>
-    <row r="92" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A92" s="84">
+    <row r="92" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="74">
         <v>33</v>
       </c>
-      <c r="B92" s="85"/>
-      <c r="C92" s="86"/>
-      <c r="D92" s="87"/>
-      <c r="E92" s="90" t="s">
+      <c r="B92" s="75"/>
+      <c r="C92" s="76"/>
+      <c r="D92" s="58"/>
+      <c r="E92" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F92" s="87"/>
-      <c r="G92" s="87"/>
-      <c r="H92" s="90" t="s">
+      <c r="F92" s="58"/>
+      <c r="G92" s="58"/>
+      <c r="H92" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I92" s="87"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="32" t="s">
+      <c r="I92" s="58"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L92" s="70"/>
-      <c r="M92" s="71"/>
-      <c r="N92" s="74" t="s">
+      <c r="L92" s="62"/>
+      <c r="M92" s="44"/>
+      <c r="N92" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O92" s="71"/>
-      <c r="P92" s="74" t="s">
+      <c r="O92" s="44"/>
+      <c r="P92" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q92" s="71"/>
-      <c r="R92" s="76" t="s">
+      <c r="Q92" s="44"/>
+      <c r="R92" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S92" s="8"/>
-      <c r="T92" s="36" t="s">
+      <c r="S92" s="7"/>
+      <c r="T92" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U92" s="78"/>
-      <c r="V92" s="79"/>
-      <c r="W92" s="79"/>
-      <c r="X92" s="79"/>
-      <c r="Y92" s="79"/>
-      <c r="Z92" s="79"/>
-      <c r="AA92" s="79"/>
-      <c r="AB92" s="80"/>
+      <c r="U92" s="68"/>
+      <c r="V92" s="69"/>
+      <c r="W92" s="69"/>
+      <c r="X92" s="69"/>
+      <c r="Y92" s="69"/>
+      <c r="Z92" s="69"/>
+      <c r="AA92" s="69"/>
+      <c r="AB92" s="70"/>
     </row>
-    <row r="93" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A93" s="84"/>
-      <c r="B93" s="85"/>
-      <c r="C93" s="88"/>
-      <c r="D93" s="89"/>
-      <c r="E93" s="91"/>
-      <c r="F93" s="89"/>
-      <c r="G93" s="89"/>
-      <c r="H93" s="91"/>
-      <c r="I93" s="89"/>
-      <c r="J93" s="26"/>
-      <c r="K93" s="33" t="s">
+    <row r="93" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="74"/>
+      <c r="B93" s="75"/>
+      <c r="C93" s="77"/>
+      <c r="D93" s="59"/>
+      <c r="E93" s="61"/>
+      <c r="F93" s="59"/>
+      <c r="G93" s="59"/>
+      <c r="H93" s="61"/>
+      <c r="I93" s="59"/>
+      <c r="J93" s="25"/>
+      <c r="K93" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L93" s="72"/>
-      <c r="M93" s="73"/>
-      <c r="N93" s="75"/>
-      <c r="O93" s="73"/>
-      <c r="P93" s="75"/>
-      <c r="Q93" s="73"/>
-      <c r="R93" s="77"/>
-      <c r="S93" s="26"/>
-      <c r="T93" s="37" t="s">
+      <c r="L93" s="63"/>
+      <c r="M93" s="45"/>
+      <c r="N93" s="65"/>
+      <c r="O93" s="45"/>
+      <c r="P93" s="65"/>
+      <c r="Q93" s="45"/>
+      <c r="R93" s="67"/>
+      <c r="S93" s="25"/>
+      <c r="T93" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U93" s="81"/>
-      <c r="V93" s="82"/>
-      <c r="W93" s="82"/>
-      <c r="X93" s="82"/>
-      <c r="Y93" s="82"/>
-      <c r="Z93" s="82"/>
-      <c r="AA93" s="82"/>
-      <c r="AB93" s="83"/>
+      <c r="U93" s="71"/>
+      <c r="V93" s="72"/>
+      <c r="W93" s="72"/>
+      <c r="X93" s="72"/>
+      <c r="Y93" s="72"/>
+      <c r="Z93" s="72"/>
+      <c r="AA93" s="72"/>
+      <c r="AB93" s="73"/>
     </row>
-    <row r="94" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A94" s="84">
+    <row r="94" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="74">
         <v>34</v>
       </c>
-      <c r="B94" s="85"/>
-      <c r="C94" s="86"/>
-      <c r="D94" s="87"/>
-      <c r="E94" s="90" t="s">
+      <c r="B94" s="75"/>
+      <c r="C94" s="76"/>
+      <c r="D94" s="58"/>
+      <c r="E94" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F94" s="87"/>
-      <c r="G94" s="87"/>
-      <c r="H94" s="90" t="s">
+      <c r="F94" s="58"/>
+      <c r="G94" s="58"/>
+      <c r="H94" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I94" s="87"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="32" t="s">
+      <c r="I94" s="58"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L94" s="70"/>
-      <c r="M94" s="71"/>
-      <c r="N94" s="74" t="s">
+      <c r="L94" s="62"/>
+      <c r="M94" s="44"/>
+      <c r="N94" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="71"/>
-      <c r="P94" s="74" t="s">
+      <c r="O94" s="44"/>
+      <c r="P94" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q94" s="71"/>
-      <c r="R94" s="76" t="s">
+      <c r="Q94" s="44"/>
+      <c r="R94" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S94" s="8"/>
-      <c r="T94" s="36" t="s">
+      <c r="S94" s="7"/>
+      <c r="T94" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U94" s="78"/>
-      <c r="V94" s="79"/>
-      <c r="W94" s="79"/>
-      <c r="X94" s="79"/>
-      <c r="Y94" s="79"/>
-      <c r="Z94" s="79"/>
-      <c r="AA94" s="79"/>
-      <c r="AB94" s="80"/>
+      <c r="U94" s="68"/>
+      <c r="V94" s="69"/>
+      <c r="W94" s="69"/>
+      <c r="X94" s="69"/>
+      <c r="Y94" s="69"/>
+      <c r="Z94" s="69"/>
+      <c r="AA94" s="69"/>
+      <c r="AB94" s="70"/>
     </row>
-    <row r="95" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="84"/>
-      <c r="B95" s="85"/>
-      <c r="C95" s="88"/>
-      <c r="D95" s="89"/>
-      <c r="E95" s="91"/>
-      <c r="F95" s="89"/>
-      <c r="G95" s="89"/>
-      <c r="H95" s="91"/>
-      <c r="I95" s="89"/>
-      <c r="J95" s="26"/>
-      <c r="K95" s="33" t="s">
+    <row r="95" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="74"/>
+      <c r="B95" s="75"/>
+      <c r="C95" s="77"/>
+      <c r="D95" s="59"/>
+      <c r="E95" s="61"/>
+      <c r="F95" s="59"/>
+      <c r="G95" s="59"/>
+      <c r="H95" s="61"/>
+      <c r="I95" s="59"/>
+      <c r="J95" s="25"/>
+      <c r="K95" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L95" s="72"/>
-      <c r="M95" s="73"/>
-      <c r="N95" s="75"/>
-      <c r="O95" s="73"/>
-      <c r="P95" s="75"/>
-      <c r="Q95" s="73"/>
-      <c r="R95" s="77"/>
-      <c r="S95" s="26"/>
-      <c r="T95" s="37" t="s">
+      <c r="L95" s="63"/>
+      <c r="M95" s="45"/>
+      <c r="N95" s="65"/>
+      <c r="O95" s="45"/>
+      <c r="P95" s="65"/>
+      <c r="Q95" s="45"/>
+      <c r="R95" s="67"/>
+      <c r="S95" s="25"/>
+      <c r="T95" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U95" s="81"/>
-      <c r="V95" s="82"/>
-      <c r="W95" s="82"/>
-      <c r="X95" s="82"/>
-      <c r="Y95" s="82"/>
-      <c r="Z95" s="82"/>
-      <c r="AA95" s="82"/>
-      <c r="AB95" s="83"/>
+      <c r="U95" s="71"/>
+      <c r="V95" s="72"/>
+      <c r="W95" s="72"/>
+      <c r="X95" s="72"/>
+      <c r="Y95" s="72"/>
+      <c r="Z95" s="72"/>
+      <c r="AA95" s="72"/>
+      <c r="AB95" s="73"/>
     </row>
-    <row r="96" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A96" s="84">
+    <row r="96" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="74">
         <v>35</v>
       </c>
-      <c r="B96" s="85"/>
-      <c r="C96" s="86"/>
-      <c r="D96" s="87"/>
-      <c r="E96" s="90" t="s">
+      <c r="B96" s="75"/>
+      <c r="C96" s="76"/>
+      <c r="D96" s="58"/>
+      <c r="E96" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F96" s="87"/>
-      <c r="G96" s="87"/>
-      <c r="H96" s="90" t="s">
+      <c r="F96" s="58"/>
+      <c r="G96" s="58"/>
+      <c r="H96" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I96" s="87"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="32" t="s">
+      <c r="I96" s="58"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L96" s="70"/>
-      <c r="M96" s="71"/>
-      <c r="N96" s="74" t="s">
+      <c r="L96" s="62"/>
+      <c r="M96" s="44"/>
+      <c r="N96" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="71"/>
-      <c r="P96" s="74" t="s">
+      <c r="O96" s="44"/>
+      <c r="P96" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q96" s="71"/>
-      <c r="R96" s="76" t="s">
+      <c r="Q96" s="44"/>
+      <c r="R96" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S96" s="8"/>
-      <c r="T96" s="36" t="s">
+      <c r="S96" s="7"/>
+      <c r="T96" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U96" s="78"/>
-      <c r="V96" s="79"/>
-      <c r="W96" s="79"/>
-      <c r="X96" s="79"/>
-      <c r="Y96" s="79"/>
-      <c r="Z96" s="79"/>
-      <c r="AA96" s="79"/>
-      <c r="AB96" s="80"/>
+      <c r="U96" s="68"/>
+      <c r="V96" s="69"/>
+      <c r="W96" s="69"/>
+      <c r="X96" s="69"/>
+      <c r="Y96" s="69"/>
+      <c r="Z96" s="69"/>
+      <c r="AA96" s="69"/>
+      <c r="AB96" s="70"/>
     </row>
-    <row r="97" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A97" s="84"/>
-      <c r="B97" s="85"/>
-      <c r="C97" s="88"/>
-      <c r="D97" s="89"/>
-      <c r="E97" s="91"/>
-      <c r="F97" s="89"/>
-      <c r="G97" s="89"/>
-      <c r="H97" s="91"/>
-      <c r="I97" s="89"/>
-      <c r="J97" s="26"/>
-      <c r="K97" s="33" t="s">
+    <row r="97" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="74"/>
+      <c r="B97" s="75"/>
+      <c r="C97" s="77"/>
+      <c r="D97" s="59"/>
+      <c r="E97" s="61"/>
+      <c r="F97" s="59"/>
+      <c r="G97" s="59"/>
+      <c r="H97" s="61"/>
+      <c r="I97" s="59"/>
+      <c r="J97" s="25"/>
+      <c r="K97" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L97" s="72"/>
-      <c r="M97" s="73"/>
-      <c r="N97" s="75"/>
-      <c r="O97" s="73"/>
-      <c r="P97" s="75"/>
-      <c r="Q97" s="73"/>
-      <c r="R97" s="77"/>
-      <c r="S97" s="26"/>
-      <c r="T97" s="37" t="s">
+      <c r="L97" s="63"/>
+      <c r="M97" s="45"/>
+      <c r="N97" s="65"/>
+      <c r="O97" s="45"/>
+      <c r="P97" s="65"/>
+      <c r="Q97" s="45"/>
+      <c r="R97" s="67"/>
+      <c r="S97" s="25"/>
+      <c r="T97" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U97" s="81"/>
-      <c r="V97" s="82"/>
-      <c r="W97" s="82"/>
-      <c r="X97" s="82"/>
-      <c r="Y97" s="82"/>
-      <c r="Z97" s="82"/>
-      <c r="AA97" s="82"/>
-      <c r="AB97" s="83"/>
+      <c r="U97" s="71"/>
+      <c r="V97" s="72"/>
+      <c r="W97" s="72"/>
+      <c r="X97" s="72"/>
+      <c r="Y97" s="72"/>
+      <c r="Z97" s="72"/>
+      <c r="AA97" s="72"/>
+      <c r="AB97" s="73"/>
     </row>
-    <row r="98" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="84">
+    <row r="98" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="74">
         <v>36</v>
       </c>
-      <c r="B98" s="85"/>
-      <c r="C98" s="86"/>
-      <c r="D98" s="87"/>
-      <c r="E98" s="90" t="s">
+      <c r="B98" s="75"/>
+      <c r="C98" s="76"/>
+      <c r="D98" s="58"/>
+      <c r="E98" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F98" s="87"/>
-      <c r="G98" s="87"/>
-      <c r="H98" s="90" t="s">
+      <c r="F98" s="58"/>
+      <c r="G98" s="58"/>
+      <c r="H98" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I98" s="87"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="32" t="s">
+      <c r="I98" s="58"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L98" s="70"/>
-      <c r="M98" s="71"/>
-      <c r="N98" s="74" t="s">
+      <c r="L98" s="62"/>
+      <c r="M98" s="44"/>
+      <c r="N98" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O98" s="71"/>
-      <c r="P98" s="74" t="s">
+      <c r="O98" s="44"/>
+      <c r="P98" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q98" s="71"/>
-      <c r="R98" s="76" t="s">
+      <c r="Q98" s="44"/>
+      <c r="R98" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S98" s="8"/>
-      <c r="T98" s="36" t="s">
+      <c r="S98" s="7"/>
+      <c r="T98" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U98" s="78"/>
-      <c r="V98" s="79"/>
-      <c r="W98" s="79"/>
-      <c r="X98" s="79"/>
-      <c r="Y98" s="79"/>
-      <c r="Z98" s="79"/>
-      <c r="AA98" s="79"/>
-      <c r="AB98" s="80"/>
+      <c r="U98" s="68"/>
+      <c r="V98" s="69"/>
+      <c r="W98" s="69"/>
+      <c r="X98" s="69"/>
+      <c r="Y98" s="69"/>
+      <c r="Z98" s="69"/>
+      <c r="AA98" s="69"/>
+      <c r="AB98" s="70"/>
     </row>
-    <row r="99" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="84"/>
-      <c r="B99" s="85"/>
-      <c r="C99" s="88"/>
-      <c r="D99" s="89"/>
-      <c r="E99" s="91"/>
-      <c r="F99" s="89"/>
-      <c r="G99" s="89"/>
-      <c r="H99" s="91"/>
-      <c r="I99" s="89"/>
-      <c r="J99" s="26"/>
-      <c r="K99" s="33" t="s">
+    <row r="99" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="74"/>
+      <c r="B99" s="75"/>
+      <c r="C99" s="77"/>
+      <c r="D99" s="59"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="59"/>
+      <c r="G99" s="59"/>
+      <c r="H99" s="61"/>
+      <c r="I99" s="59"/>
+      <c r="J99" s="25"/>
+      <c r="K99" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L99" s="72"/>
-      <c r="M99" s="73"/>
-      <c r="N99" s="75"/>
-      <c r="O99" s="73"/>
-      <c r="P99" s="75"/>
-      <c r="Q99" s="73"/>
-      <c r="R99" s="77"/>
-      <c r="S99" s="26"/>
-      <c r="T99" s="37" t="s">
+      <c r="L99" s="63"/>
+      <c r="M99" s="45"/>
+      <c r="N99" s="65"/>
+      <c r="O99" s="45"/>
+      <c r="P99" s="65"/>
+      <c r="Q99" s="45"/>
+      <c r="R99" s="67"/>
+      <c r="S99" s="25"/>
+      <c r="T99" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U99" s="81"/>
-      <c r="V99" s="82"/>
-      <c r="W99" s="82"/>
-      <c r="X99" s="82"/>
-      <c r="Y99" s="82"/>
-      <c r="Z99" s="82"/>
-      <c r="AA99" s="82"/>
-      <c r="AB99" s="83"/>
+      <c r="U99" s="71"/>
+      <c r="V99" s="72"/>
+      <c r="W99" s="72"/>
+      <c r="X99" s="72"/>
+      <c r="Y99" s="72"/>
+      <c r="Z99" s="72"/>
+      <c r="AA99" s="72"/>
+      <c r="AB99" s="73"/>
     </row>
-    <row r="100" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="84">
+    <row r="100" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="74">
         <v>37</v>
       </c>
-      <c r="B100" s="85"/>
-      <c r="C100" s="86"/>
-      <c r="D100" s="87"/>
-      <c r="E100" s="90" t="s">
+      <c r="B100" s="75"/>
+      <c r="C100" s="76"/>
+      <c r="D100" s="58"/>
+      <c r="E100" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F100" s="87"/>
-      <c r="G100" s="87"/>
-      <c r="H100" s="90" t="s">
+      <c r="F100" s="58"/>
+      <c r="G100" s="58"/>
+      <c r="H100" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I100" s="87"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="32" t="s">
+      <c r="I100" s="58"/>
+      <c r="J100" s="7"/>
+      <c r="K100" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L100" s="70"/>
-      <c r="M100" s="71"/>
-      <c r="N100" s="74" t="s">
+      <c r="L100" s="62"/>
+      <c r="M100" s="44"/>
+      <c r="N100" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="71"/>
-      <c r="P100" s="74" t="s">
+      <c r="O100" s="44"/>
+      <c r="P100" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q100" s="71"/>
-      <c r="R100" s="76" t="s">
+      <c r="Q100" s="44"/>
+      <c r="R100" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S100" s="8"/>
-      <c r="T100" s="36" t="s">
+      <c r="S100" s="7"/>
+      <c r="T100" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U100" s="78"/>
-      <c r="V100" s="79"/>
-      <c r="W100" s="79"/>
-      <c r="X100" s="79"/>
-      <c r="Y100" s="79"/>
-      <c r="Z100" s="79"/>
-      <c r="AA100" s="79"/>
-      <c r="AB100" s="80"/>
+      <c r="U100" s="68"/>
+      <c r="V100" s="69"/>
+      <c r="W100" s="69"/>
+      <c r="X100" s="69"/>
+      <c r="Y100" s="69"/>
+      <c r="Z100" s="69"/>
+      <c r="AA100" s="69"/>
+      <c r="AB100" s="70"/>
     </row>
-    <row r="101" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="84"/>
-      <c r="B101" s="85"/>
-      <c r="C101" s="88"/>
-      <c r="D101" s="89"/>
-      <c r="E101" s="91"/>
-      <c r="F101" s="89"/>
-      <c r="G101" s="89"/>
-      <c r="H101" s="91"/>
-      <c r="I101" s="89"/>
-      <c r="J101" s="26"/>
-      <c r="K101" s="33" t="s">
+    <row r="101" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="74"/>
+      <c r="B101" s="75"/>
+      <c r="C101" s="77"/>
+      <c r="D101" s="59"/>
+      <c r="E101" s="61"/>
+      <c r="F101" s="59"/>
+      <c r="G101" s="59"/>
+      <c r="H101" s="61"/>
+      <c r="I101" s="59"/>
+      <c r="J101" s="25"/>
+      <c r="K101" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L101" s="72"/>
-      <c r="M101" s="73"/>
-      <c r="N101" s="75"/>
-      <c r="O101" s="73"/>
-      <c r="P101" s="75"/>
-      <c r="Q101" s="73"/>
-      <c r="R101" s="77"/>
-      <c r="S101" s="26"/>
-      <c r="T101" s="37" t="s">
+      <c r="L101" s="63"/>
+      <c r="M101" s="45"/>
+      <c r="N101" s="65"/>
+      <c r="O101" s="45"/>
+      <c r="P101" s="65"/>
+      <c r="Q101" s="45"/>
+      <c r="R101" s="67"/>
+      <c r="S101" s="25"/>
+      <c r="T101" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U101" s="81"/>
-      <c r="V101" s="82"/>
-      <c r="W101" s="82"/>
-      <c r="X101" s="82"/>
-      <c r="Y101" s="82"/>
-      <c r="Z101" s="82"/>
-      <c r="AA101" s="82"/>
-      <c r="AB101" s="83"/>
+      <c r="U101" s="71"/>
+      <c r="V101" s="72"/>
+      <c r="W101" s="72"/>
+      <c r="X101" s="72"/>
+      <c r="Y101" s="72"/>
+      <c r="Z101" s="72"/>
+      <c r="AA101" s="72"/>
+      <c r="AB101" s="73"/>
     </row>
-    <row r="102" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A102" s="84">
+    <row r="102" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="74">
         <v>38</v>
       </c>
-      <c r="B102" s="85"/>
-      <c r="C102" s="86"/>
-      <c r="D102" s="87"/>
-      <c r="E102" s="90" t="s">
+      <c r="B102" s="75"/>
+      <c r="C102" s="76"/>
+      <c r="D102" s="58"/>
+      <c r="E102" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F102" s="87"/>
-      <c r="G102" s="87"/>
-      <c r="H102" s="90" t="s">
+      <c r="F102" s="58"/>
+      <c r="G102" s="58"/>
+      <c r="H102" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I102" s="87"/>
-      <c r="J102" s="8"/>
-      <c r="K102" s="32" t="s">
+      <c r="I102" s="58"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L102" s="70"/>
-      <c r="M102" s="71"/>
-      <c r="N102" s="74" t="s">
+      <c r="L102" s="62"/>
+      <c r="M102" s="44"/>
+      <c r="N102" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O102" s="71"/>
-      <c r="P102" s="74" t="s">
+      <c r="O102" s="44"/>
+      <c r="P102" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q102" s="71"/>
-      <c r="R102" s="76" t="s">
+      <c r="Q102" s="44"/>
+      <c r="R102" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S102" s="8"/>
-      <c r="T102" s="36" t="s">
+      <c r="S102" s="7"/>
+      <c r="T102" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U102" s="78"/>
-      <c r="V102" s="79"/>
-      <c r="W102" s="79"/>
-      <c r="X102" s="79"/>
-      <c r="Y102" s="79"/>
-      <c r="Z102" s="79"/>
-      <c r="AA102" s="79"/>
-      <c r="AB102" s="80"/>
+      <c r="U102" s="68"/>
+      <c r="V102" s="69"/>
+      <c r="W102" s="69"/>
+      <c r="X102" s="69"/>
+      <c r="Y102" s="69"/>
+      <c r="Z102" s="69"/>
+      <c r="AA102" s="69"/>
+      <c r="AB102" s="70"/>
     </row>
-    <row r="103" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A103" s="84"/>
-      <c r="B103" s="85"/>
-      <c r="C103" s="88"/>
-      <c r="D103" s="89"/>
-      <c r="E103" s="91"/>
-      <c r="F103" s="89"/>
-      <c r="G103" s="89"/>
-      <c r="H103" s="91"/>
-      <c r="I103" s="89"/>
-      <c r="J103" s="26"/>
-      <c r="K103" s="33" t="s">
+    <row r="103" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="74"/>
+      <c r="B103" s="75"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="59"/>
+      <c r="E103" s="61"/>
+      <c r="F103" s="59"/>
+      <c r="G103" s="59"/>
+      <c r="H103" s="61"/>
+      <c r="I103" s="59"/>
+      <c r="J103" s="25"/>
+      <c r="K103" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L103" s="72"/>
-      <c r="M103" s="73"/>
-      <c r="N103" s="75"/>
-      <c r="O103" s="73"/>
-      <c r="P103" s="75"/>
-      <c r="Q103" s="73"/>
-      <c r="R103" s="77"/>
-      <c r="S103" s="26"/>
-      <c r="T103" s="37" t="s">
+      <c r="L103" s="63"/>
+      <c r="M103" s="45"/>
+      <c r="N103" s="65"/>
+      <c r="O103" s="45"/>
+      <c r="P103" s="65"/>
+      <c r="Q103" s="45"/>
+      <c r="R103" s="67"/>
+      <c r="S103" s="25"/>
+      <c r="T103" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U103" s="81"/>
-      <c r="V103" s="82"/>
-      <c r="W103" s="82"/>
-      <c r="X103" s="82"/>
-      <c r="Y103" s="82"/>
-      <c r="Z103" s="82"/>
-      <c r="AA103" s="82"/>
-      <c r="AB103" s="83"/>
+      <c r="U103" s="71"/>
+      <c r="V103" s="72"/>
+      <c r="W103" s="72"/>
+      <c r="X103" s="72"/>
+      <c r="Y103" s="72"/>
+      <c r="Z103" s="72"/>
+      <c r="AA103" s="72"/>
+      <c r="AB103" s="73"/>
     </row>
-    <row r="104" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A104" s="84">
+    <row r="104" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="74">
         <v>39</v>
       </c>
-      <c r="B104" s="85"/>
-      <c r="C104" s="86"/>
-      <c r="D104" s="87"/>
-      <c r="E104" s="90" t="s">
+      <c r="B104" s="75"/>
+      <c r="C104" s="76"/>
+      <c r="D104" s="58"/>
+      <c r="E104" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="F104" s="87"/>
-      <c r="G104" s="87"/>
-      <c r="H104" s="90" t="s">
+      <c r="F104" s="58"/>
+      <c r="G104" s="58"/>
+      <c r="H104" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="I104" s="87"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="32" t="s">
+      <c r="I104" s="58"/>
+      <c r="J104" s="7"/>
+      <c r="K104" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L104" s="70"/>
-      <c r="M104" s="71"/>
-      <c r="N104" s="74" t="s">
+      <c r="L104" s="62"/>
+      <c r="M104" s="44"/>
+      <c r="N104" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="O104" s="71"/>
-      <c r="P104" s="74" t="s">
+      <c r="O104" s="44"/>
+      <c r="P104" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="Q104" s="71"/>
-      <c r="R104" s="76" t="s">
+      <c r="Q104" s="44"/>
+      <c r="R104" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="S104" s="8"/>
-      <c r="T104" s="36" t="s">
+      <c r="S104" s="7"/>
+      <c r="T104" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U104" s="78"/>
-      <c r="V104" s="79"/>
-      <c r="W104" s="79"/>
-      <c r="X104" s="79"/>
-      <c r="Y104" s="79"/>
-      <c r="Z104" s="79"/>
-      <c r="AA104" s="79"/>
-      <c r="AB104" s="80"/>
+      <c r="U104" s="68"/>
+      <c r="V104" s="69"/>
+      <c r="W104" s="69"/>
+      <c r="X104" s="69"/>
+      <c r="Y104" s="69"/>
+      <c r="Z104" s="69"/>
+      <c r="AA104" s="69"/>
+      <c r="AB104" s="70"/>
     </row>
-    <row r="105" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="84"/>
-      <c r="B105" s="85"/>
-      <c r="C105" s="88"/>
-      <c r="D105" s="89"/>
-      <c r="E105" s="91"/>
-      <c r="F105" s="89"/>
-      <c r="G105" s="89"/>
-      <c r="H105" s="91"/>
-      <c r="I105" s="89"/>
-      <c r="J105" s="26"/>
-      <c r="K105" s="33" t="s">
+    <row r="105" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="74"/>
+      <c r="B105" s="75"/>
+      <c r="C105" s="77"/>
+      <c r="D105" s="59"/>
+      <c r="E105" s="61"/>
+      <c r="F105" s="59"/>
+      <c r="G105" s="59"/>
+      <c r="H105" s="61"/>
+      <c r="I105" s="59"/>
+      <c r="J105" s="25"/>
+      <c r="K105" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="L105" s="72"/>
-      <c r="M105" s="73"/>
-      <c r="N105" s="75"/>
-      <c r="O105" s="73"/>
-      <c r="P105" s="75"/>
-      <c r="Q105" s="73"/>
-      <c r="R105" s="77"/>
-      <c r="S105" s="26"/>
-      <c r="T105" s="37" t="s">
+      <c r="L105" s="63"/>
+      <c r="M105" s="45"/>
+      <c r="N105" s="65"/>
+      <c r="O105" s="45"/>
+      <c r="P105" s="65"/>
+      <c r="Q105" s="45"/>
+      <c r="R105" s="67"/>
+      <c r="S105" s="25"/>
+      <c r="T105" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="U105" s="81"/>
-      <c r="V105" s="82"/>
-      <c r="W105" s="82"/>
-      <c r="X105" s="82"/>
-      <c r="Y105" s="82"/>
-      <c r="Z105" s="82"/>
-      <c r="AA105" s="82"/>
-      <c r="AB105" s="83"/>
+      <c r="U105" s="71"/>
+      <c r="V105" s="72"/>
+      <c r="W105" s="72"/>
+      <c r="X105" s="72"/>
+      <c r="Y105" s="72"/>
+      <c r="Z105" s="72"/>
+      <c r="AA105" s="72"/>
+      <c r="AB105" s="73"/>
     </row>
-    <row r="106" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="58">
+    <row r="106" spans="1:28" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="78">
         <v>40</v>
       </c>
-      <c r="B106" s="60"/>
-      <c r="C106" s="62"/>
-      <c r="D106" s="63"/>
-      <c r="E106" s="66" t="s">
+      <c r="B106" s="80"/>
+      <c r="C106" s="82"/>
+      <c r="D106" s="83"/>
+      <c r="E106" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F106" s="63"/>
-      <c r="G106" s="63"/>
-      <c r="H106" s="66" t="s">
+      <c r="F106" s="83"/>
+      <c r="G106" s="83"/>
+      <c r="H106" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="I106" s="63"/>
-      <c r="J106" s="27"/>
-      <c r="K106" s="34" t="s">
+      <c r="I106" s="83"/>
+      <c r="J106" s="26"/>
+      <c r="K106" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="L106" s="68"/>
+      <c r="L106" s="88"/>
       <c r="M106" s="46"/>
       <c r="N106" s="48" t="s">
         <v>3</v>
@@ -17456,8 +17428,8 @@
       <c r="R106" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="S106" s="27"/>
-      <c r="T106" s="38" t="s">
+      <c r="S106" s="26"/>
+      <c r="T106" s="36" t="s">
         <v>14</v>
       </c>
       <c r="U106" s="52"/>
@@ -17469,29 +17441,29 @@
       <c r="AA106" s="53"/>
       <c r="AB106" s="54"/>
     </row>
-    <row r="107" spans="1:28" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="59"/>
-      <c r="B107" s="61"/>
-      <c r="C107" s="64"/>
-      <c r="D107" s="65"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="65"/>
-      <c r="G107" s="65"/>
-      <c r="H107" s="67"/>
-      <c r="I107" s="65"/>
-      <c r="J107" s="28"/>
-      <c r="K107" s="35" t="s">
+    <row r="107" spans="1:28" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="79"/>
+      <c r="B107" s="81"/>
+      <c r="C107" s="84"/>
+      <c r="D107" s="85"/>
+      <c r="E107" s="87"/>
+      <c r="F107" s="85"/>
+      <c r="G107" s="85"/>
+      <c r="H107" s="87"/>
+      <c r="I107" s="85"/>
+      <c r="J107" s="27"/>
+      <c r="K107" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="L107" s="69"/>
+      <c r="L107" s="89"/>
       <c r="M107" s="47"/>
       <c r="N107" s="49"/>
       <c r="O107" s="47"/>
       <c r="P107" s="49"/>
       <c r="Q107" s="47"/>
       <c r="R107" s="51"/>
-      <c r="S107" s="28"/>
-      <c r="T107" s="39" t="s">
+      <c r="S107" s="27"/>
+      <c r="T107" s="37" t="s">
         <v>13</v>
       </c>
       <c r="U107" s="55"/>
@@ -17503,13 +17475,583 @@
       <c r="AA107" s="56"/>
       <c r="AB107" s="57"/>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.15">
-      <c r="A108" s="6" t="s">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="594">
+    <mergeCell ref="O106:O107"/>
+    <mergeCell ref="P106:P107"/>
+    <mergeCell ref="Q106:Q107"/>
+    <mergeCell ref="R106:R107"/>
+    <mergeCell ref="U106:AB107"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="C106:D107"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F106:G107"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="I106:I107"/>
+    <mergeCell ref="L106:M107"/>
+    <mergeCell ref="N106:N107"/>
+    <mergeCell ref="L104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="Q104:Q105"/>
+    <mergeCell ref="R104:R105"/>
+    <mergeCell ref="U104:AB105"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:D103"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="F102:G103"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="I102:I103"/>
+    <mergeCell ref="L102:M103"/>
+    <mergeCell ref="N102:N103"/>
+    <mergeCell ref="U102:AB103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="F104:G105"/>
+    <mergeCell ref="H104:H105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="U98:AB99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:D101"/>
+    <mergeCell ref="E100:E101"/>
+    <mergeCell ref="F100:G101"/>
+    <mergeCell ref="H100:H101"/>
+    <mergeCell ref="I100:I101"/>
+    <mergeCell ref="L100:M101"/>
+    <mergeCell ref="N100:N101"/>
+    <mergeCell ref="O100:O101"/>
+    <mergeCell ref="P100:P101"/>
+    <mergeCell ref="Q100:Q101"/>
+    <mergeCell ref="R100:R101"/>
+    <mergeCell ref="U100:AB101"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:D99"/>
+    <mergeCell ref="E98:E99"/>
+    <mergeCell ref="F98:G99"/>
+    <mergeCell ref="H98:H99"/>
+    <mergeCell ref="I98:I99"/>
+    <mergeCell ref="L98:M99"/>
+    <mergeCell ref="N98:N99"/>
+    <mergeCell ref="P94:P95"/>
+    <mergeCell ref="Q94:Q95"/>
+    <mergeCell ref="R94:R95"/>
+    <mergeCell ref="U94:AB95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:D97"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="F96:G97"/>
+    <mergeCell ref="H96:H97"/>
+    <mergeCell ref="I96:I97"/>
+    <mergeCell ref="L96:M97"/>
+    <mergeCell ref="N96:N97"/>
+    <mergeCell ref="O96:O97"/>
+    <mergeCell ref="P96:P97"/>
+    <mergeCell ref="Q96:Q97"/>
+    <mergeCell ref="R96:R97"/>
+    <mergeCell ref="U96:AB97"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:D95"/>
+    <mergeCell ref="E94:E95"/>
+    <mergeCell ref="F94:G95"/>
+    <mergeCell ref="H94:H95"/>
+    <mergeCell ref="I94:I95"/>
+    <mergeCell ref="L94:M95"/>
+    <mergeCell ref="N94:N95"/>
+    <mergeCell ref="H92:H93"/>
+    <mergeCell ref="I92:I93"/>
+    <mergeCell ref="L92:M93"/>
+    <mergeCell ref="N92:N93"/>
+    <mergeCell ref="O92:O93"/>
+    <mergeCell ref="O94:O95"/>
+    <mergeCell ref="P92:P93"/>
+    <mergeCell ref="Q92:Q93"/>
+    <mergeCell ref="R92:R93"/>
+    <mergeCell ref="U92:AB93"/>
+    <mergeCell ref="O88:O89"/>
+    <mergeCell ref="P88:P89"/>
+    <mergeCell ref="Q88:Q89"/>
+    <mergeCell ref="R88:R89"/>
+    <mergeCell ref="U88:AB89"/>
+    <mergeCell ref="O90:O91"/>
+    <mergeCell ref="P90:P91"/>
+    <mergeCell ref="Q90:Q91"/>
+    <mergeCell ref="R90:R91"/>
+    <mergeCell ref="U90:AB91"/>
+    <mergeCell ref="L88:M89"/>
+    <mergeCell ref="N88:N89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:D91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:G91"/>
+    <mergeCell ref="H90:H91"/>
+    <mergeCell ref="I90:I91"/>
+    <mergeCell ref="L90:M91"/>
+    <mergeCell ref="N90:N91"/>
+    <mergeCell ref="U84:AB85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:D87"/>
+    <mergeCell ref="E86:E87"/>
+    <mergeCell ref="F86:G87"/>
+    <mergeCell ref="H86:H87"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="L86:M87"/>
+    <mergeCell ref="N86:N87"/>
+    <mergeCell ref="O86:O87"/>
+    <mergeCell ref="P86:P87"/>
+    <mergeCell ref="Q86:Q87"/>
+    <mergeCell ref="R86:R87"/>
+    <mergeCell ref="U86:AB87"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="C84:D85"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="F84:G85"/>
+    <mergeCell ref="U80:AB81"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="C82:D83"/>
+    <mergeCell ref="E82:E83"/>
+    <mergeCell ref="F82:G83"/>
+    <mergeCell ref="H82:H83"/>
+    <mergeCell ref="I82:I83"/>
+    <mergeCell ref="L82:M83"/>
+    <mergeCell ref="N82:N83"/>
+    <mergeCell ref="O82:O83"/>
+    <mergeCell ref="P82:P83"/>
+    <mergeCell ref="Q82:Q83"/>
+    <mergeCell ref="R82:R83"/>
+    <mergeCell ref="U82:AB83"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:D81"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:G81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="L80:M81"/>
+    <mergeCell ref="N80:N81"/>
+    <mergeCell ref="O78:O79"/>
+    <mergeCell ref="P78:P79"/>
+    <mergeCell ref="Q78:Q79"/>
+    <mergeCell ref="R78:R79"/>
+    <mergeCell ref="U78:AB79"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="C76:D77"/>
+    <mergeCell ref="E76:E77"/>
+    <mergeCell ref="F76:G77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="C78:D79"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:G79"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="I78:I79"/>
+    <mergeCell ref="L78:M79"/>
+    <mergeCell ref="N78:N79"/>
+    <mergeCell ref="H76:H77"/>
+    <mergeCell ref="I76:I77"/>
+    <mergeCell ref="L76:M77"/>
+    <mergeCell ref="N76:N77"/>
+    <mergeCell ref="O76:O77"/>
+    <mergeCell ref="O72:O73"/>
+    <mergeCell ref="P72:P73"/>
+    <mergeCell ref="Q72:Q73"/>
+    <mergeCell ref="R72:R73"/>
+    <mergeCell ref="U72:AB73"/>
+    <mergeCell ref="O74:O75"/>
+    <mergeCell ref="P74:P75"/>
+    <mergeCell ref="Q74:Q75"/>
+    <mergeCell ref="R74:R75"/>
+    <mergeCell ref="U74:AB75"/>
+    <mergeCell ref="P76:P77"/>
+    <mergeCell ref="Q76:Q77"/>
+    <mergeCell ref="R76:R77"/>
+    <mergeCell ref="U76:AB77"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:D75"/>
+    <mergeCell ref="E74:E75"/>
+    <mergeCell ref="F74:G75"/>
+    <mergeCell ref="H74:H75"/>
+    <mergeCell ref="I74:I75"/>
+    <mergeCell ref="L74:M75"/>
+    <mergeCell ref="N74:N75"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:D73"/>
+    <mergeCell ref="E72:E73"/>
+    <mergeCell ref="F72:G73"/>
+    <mergeCell ref="H72:H73"/>
+    <mergeCell ref="I72:I73"/>
+    <mergeCell ref="L72:M73"/>
+    <mergeCell ref="N72:N73"/>
+    <mergeCell ref="O70:O71"/>
+    <mergeCell ref="P70:P71"/>
+    <mergeCell ref="Q70:Q71"/>
+    <mergeCell ref="R70:R71"/>
+    <mergeCell ref="U70:AB71"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C68:D69"/>
+    <mergeCell ref="E68:E69"/>
+    <mergeCell ref="F68:G69"/>
+    <mergeCell ref="H68:H69"/>
+    <mergeCell ref="I68:I69"/>
+    <mergeCell ref="L68:M69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C70:D71"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="F70:G71"/>
+    <mergeCell ref="H70:H71"/>
+    <mergeCell ref="I70:I71"/>
+    <mergeCell ref="L70:M71"/>
+    <mergeCell ref="N70:N71"/>
+    <mergeCell ref="N68:N69"/>
+    <mergeCell ref="O68:O69"/>
+    <mergeCell ref="B54:AB54"/>
+    <mergeCell ref="B55:AB55"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="L67:R67"/>
+    <mergeCell ref="S67:T67"/>
+    <mergeCell ref="U67:AB67"/>
+    <mergeCell ref="C63:AB63"/>
+    <mergeCell ref="C64:AB64"/>
+    <mergeCell ref="B65:AB65"/>
+    <mergeCell ref="L66:R66"/>
+    <mergeCell ref="S66:T66"/>
+    <mergeCell ref="U66:AB66"/>
+    <mergeCell ref="B58:U58"/>
+    <mergeCell ref="Z60:AA60"/>
+    <mergeCell ref="A61:AB61"/>
+    <mergeCell ref="P68:P69"/>
+    <mergeCell ref="Q68:Q69"/>
+    <mergeCell ref="R68:R69"/>
+    <mergeCell ref="U68:AB69"/>
+    <mergeCell ref="W60:X60"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="N29:N30"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="L25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:G18"/>
+    <mergeCell ref="B56:U56"/>
+    <mergeCell ref="O80:O81"/>
+    <mergeCell ref="P80:P81"/>
+    <mergeCell ref="Q80:Q81"/>
+    <mergeCell ref="R80:R81"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:D93"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="F92:G93"/>
+    <mergeCell ref="H84:H85"/>
+    <mergeCell ref="I84:I85"/>
+    <mergeCell ref="L84:M85"/>
+    <mergeCell ref="N84:N85"/>
+    <mergeCell ref="O84:O85"/>
+    <mergeCell ref="P84:P85"/>
+    <mergeCell ref="Q84:Q85"/>
+    <mergeCell ref="R84:R85"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:D89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:G89"/>
+    <mergeCell ref="H88:H89"/>
+    <mergeCell ref="I88:I89"/>
+    <mergeCell ref="O98:O99"/>
+    <mergeCell ref="P98:P99"/>
+    <mergeCell ref="Q98:Q99"/>
+    <mergeCell ref="R98:R99"/>
+    <mergeCell ref="O102:O103"/>
+    <mergeCell ref="P102:P103"/>
+    <mergeCell ref="Q102:Q103"/>
+    <mergeCell ref="R102:R103"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="U15:AB16"/>
+    <mergeCell ref="P21:P22"/>
+    <mergeCell ref="R25:R26"/>
+    <mergeCell ref="U25:AB26"/>
+    <mergeCell ref="O27:O28"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="Q27:Q28"/>
+    <mergeCell ref="R27:R28"/>
+    <mergeCell ref="U27:AB28"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="Z3:AA3"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="A5:AB5"/>
+    <mergeCell ref="U11:AB11"/>
+    <mergeCell ref="U12:AB12"/>
+    <mergeCell ref="U13:AB14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="L13:M14"/>
+    <mergeCell ref="B10:AB10"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L11:R11"/>
+    <mergeCell ref="L12:R12"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:G14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="L17:M18"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="L15:M16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="Q21:Q22"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="U17:AB18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="L19:M20"/>
+    <mergeCell ref="N19:N20"/>
+    <mergeCell ref="O19:O20"/>
+    <mergeCell ref="P19:P20"/>
+    <mergeCell ref="Q19:Q20"/>
+    <mergeCell ref="R19:R20"/>
+    <mergeCell ref="U19:AB20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:D22"/>
+    <mergeCell ref="R21:R22"/>
+    <mergeCell ref="U21:AB22"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:D24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="L23:M24"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="O23:O24"/>
+    <mergeCell ref="P23:P24"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:R24"/>
+    <mergeCell ref="U23:AB24"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:G22"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="I21:I22"/>
+    <mergeCell ref="L21:M22"/>
+    <mergeCell ref="N21:N22"/>
+    <mergeCell ref="O21:O22"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:G28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="I27:I28"/>
+    <mergeCell ref="L27:M28"/>
+    <mergeCell ref="N27:N28"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="R29:R30"/>
+    <mergeCell ref="U29:AB30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:D32"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:G32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="L31:M32"/>
+    <mergeCell ref="N31:N32"/>
+    <mergeCell ref="O31:O32"/>
+    <mergeCell ref="P31:P32"/>
+    <mergeCell ref="Q31:Q32"/>
+    <mergeCell ref="R31:R32"/>
+    <mergeCell ref="U31:AB32"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="C29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:G30"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="I29:I30"/>
+    <mergeCell ref="L29:M30"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="L35:M36"/>
+    <mergeCell ref="N35:N36"/>
+    <mergeCell ref="C8:AB8"/>
+    <mergeCell ref="C9:AB9"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:D34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:G34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="L33:M34"/>
+    <mergeCell ref="N33:N34"/>
+    <mergeCell ref="O33:O34"/>
+    <mergeCell ref="P33:P34"/>
+    <mergeCell ref="Q33:Q34"/>
+    <mergeCell ref="R33:R34"/>
+    <mergeCell ref="U33:AB34"/>
+    <mergeCell ref="O29:O30"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="Q29:Q30"/>
+    <mergeCell ref="O35:O36"/>
+    <mergeCell ref="P35:P36"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="U35:AB36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:G38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="L37:M38"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="R37:R38"/>
+    <mergeCell ref="U37:AB38"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:G36"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:G40"/>
+    <mergeCell ref="H39:H40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="L39:M40"/>
+    <mergeCell ref="N39:N40"/>
+    <mergeCell ref="Q43:Q44"/>
+    <mergeCell ref="R43:R44"/>
+    <mergeCell ref="U43:AB44"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:D42"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F41:G42"/>
+    <mergeCell ref="H41:H42"/>
+    <mergeCell ref="I41:I42"/>
+    <mergeCell ref="L41:M42"/>
+    <mergeCell ref="N41:N42"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="P39:P40"/>
+    <mergeCell ref="Q39:Q40"/>
+    <mergeCell ref="R39:R40"/>
+    <mergeCell ref="U39:AB40"/>
+    <mergeCell ref="O41:O42"/>
+    <mergeCell ref="P41:P42"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="R41:R42"/>
+    <mergeCell ref="U41:AB42"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="Q45:Q46"/>
+    <mergeCell ref="R45:R46"/>
+    <mergeCell ref="U45:AB46"/>
+    <mergeCell ref="A43:A44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:D44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:G44"/>
+    <mergeCell ref="A45:A46"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:D46"/>
+    <mergeCell ref="E45:E46"/>
+    <mergeCell ref="F45:G46"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="I45:I46"/>
+    <mergeCell ref="L45:M46"/>
+    <mergeCell ref="N45:N46"/>
+    <mergeCell ref="H43:H44"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="L43:M44"/>
+    <mergeCell ref="N43:N44"/>
+    <mergeCell ref="O43:O44"/>
+    <mergeCell ref="P43:P44"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="C51:D52"/>
+    <mergeCell ref="E51:E52"/>
+    <mergeCell ref="F51:G52"/>
+    <mergeCell ref="H51:H52"/>
+    <mergeCell ref="I51:I52"/>
+    <mergeCell ref="L51:M52"/>
+    <mergeCell ref="N51:N52"/>
+    <mergeCell ref="U47:AB48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:D50"/>
+    <mergeCell ref="E49:E50"/>
+    <mergeCell ref="U49:AB50"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:D48"/>
+    <mergeCell ref="E47:E48"/>
     <mergeCell ref="O45:O46"/>
     <mergeCell ref="O51:O52"/>
     <mergeCell ref="P51:P52"/>
@@ -17534,581 +18076,11 @@
     <mergeCell ref="P47:P48"/>
     <mergeCell ref="Q47:Q48"/>
     <mergeCell ref="R47:R48"/>
-    <mergeCell ref="U47:AB48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="C49:D50"/>
-    <mergeCell ref="E49:E50"/>
-    <mergeCell ref="U49:AB50"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:D52"/>
-    <mergeCell ref="E51:E52"/>
-    <mergeCell ref="F51:G52"/>
-    <mergeCell ref="H51:H52"/>
-    <mergeCell ref="I51:I52"/>
-    <mergeCell ref="L51:M52"/>
-    <mergeCell ref="N51:N52"/>
-    <mergeCell ref="P45:P46"/>
-    <mergeCell ref="Q45:Q46"/>
-    <mergeCell ref="R45:R46"/>
-    <mergeCell ref="U45:AB46"/>
-    <mergeCell ref="A43:A44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:D44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:G44"/>
-    <mergeCell ref="A45:A46"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:D46"/>
-    <mergeCell ref="E45:E46"/>
-    <mergeCell ref="F45:G46"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="I45:I46"/>
-    <mergeCell ref="L45:M46"/>
-    <mergeCell ref="N45:N46"/>
-    <mergeCell ref="H43:H44"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="L43:M44"/>
-    <mergeCell ref="N43:N44"/>
-    <mergeCell ref="O43:O44"/>
-    <mergeCell ref="P43:P44"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="P39:P40"/>
-    <mergeCell ref="Q39:Q40"/>
-    <mergeCell ref="R39:R40"/>
-    <mergeCell ref="U39:AB40"/>
-    <mergeCell ref="O41:O42"/>
-    <mergeCell ref="P41:P42"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="R41:R42"/>
-    <mergeCell ref="U41:AB42"/>
-    <mergeCell ref="Q43:Q44"/>
-    <mergeCell ref="R43:R44"/>
-    <mergeCell ref="U43:AB44"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:D42"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F41:G42"/>
-    <mergeCell ref="H41:H42"/>
-    <mergeCell ref="I41:I42"/>
-    <mergeCell ref="L41:M42"/>
-    <mergeCell ref="N41:N42"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:D40"/>
-    <mergeCell ref="E39:E40"/>
-    <mergeCell ref="F39:G40"/>
-    <mergeCell ref="H39:H40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="L39:M40"/>
-    <mergeCell ref="N39:N40"/>
-    <mergeCell ref="O35:O36"/>
-    <mergeCell ref="P35:P36"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="U35:AB36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:G38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="L37:M38"/>
-    <mergeCell ref="N37:N38"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="U37:AB38"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:D36"/>
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:G36"/>
-    <mergeCell ref="L29:M30"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="L35:M36"/>
-    <mergeCell ref="N35:N36"/>
-    <mergeCell ref="C8:AB8"/>
-    <mergeCell ref="C9:AB9"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="C33:D34"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:G34"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="L33:M34"/>
-    <mergeCell ref="N33:N34"/>
-    <mergeCell ref="O33:O34"/>
-    <mergeCell ref="P33:P34"/>
-    <mergeCell ref="Q33:Q34"/>
-    <mergeCell ref="R33:R34"/>
-    <mergeCell ref="U33:AB34"/>
-    <mergeCell ref="O29:O30"/>
-    <mergeCell ref="P29:P30"/>
-    <mergeCell ref="Q29:Q30"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="R29:R30"/>
-    <mergeCell ref="U29:AB30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:D32"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="L31:M32"/>
-    <mergeCell ref="N31:N32"/>
-    <mergeCell ref="O31:O32"/>
-    <mergeCell ref="P31:P32"/>
-    <mergeCell ref="Q31:Q32"/>
-    <mergeCell ref="R31:R32"/>
-    <mergeCell ref="U31:AB32"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="F29:G30"/>
-    <mergeCell ref="H29:H30"/>
-    <mergeCell ref="I29:I30"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:G28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="I27:I28"/>
-    <mergeCell ref="L27:M28"/>
-    <mergeCell ref="N27:N28"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="R21:R22"/>
-    <mergeCell ref="U21:AB22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:D24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="L23:M24"/>
-    <mergeCell ref="N23:N24"/>
-    <mergeCell ref="O23:O24"/>
-    <mergeCell ref="P23:P24"/>
-    <mergeCell ref="Q23:Q24"/>
-    <mergeCell ref="R23:R24"/>
-    <mergeCell ref="U23:AB24"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:G22"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="I21:I22"/>
-    <mergeCell ref="L21:M22"/>
-    <mergeCell ref="N21:N22"/>
-    <mergeCell ref="O21:O22"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="Q21:Q22"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="U17:AB18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="L19:M20"/>
-    <mergeCell ref="N19:N20"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="P19:P20"/>
-    <mergeCell ref="Q19:Q20"/>
-    <mergeCell ref="R19:R20"/>
-    <mergeCell ref="U19:AB20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="L17:M18"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:G16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="L15:M16"/>
-    <mergeCell ref="Z3:AA3"/>
-    <mergeCell ref="U1:AB1"/>
-    <mergeCell ref="A5:AB5"/>
-    <mergeCell ref="U11:AB11"/>
-    <mergeCell ref="U12:AB12"/>
-    <mergeCell ref="U13:AB14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="L13:M14"/>
-    <mergeCell ref="B10:AB10"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L11:R11"/>
-    <mergeCell ref="L12:R12"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:G14"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="O98:O99"/>
-    <mergeCell ref="P98:P99"/>
-    <mergeCell ref="Q98:Q99"/>
-    <mergeCell ref="R98:R99"/>
-    <mergeCell ref="O102:O103"/>
-    <mergeCell ref="P102:P103"/>
-    <mergeCell ref="Q102:Q103"/>
-    <mergeCell ref="R102:R103"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="U15:AB16"/>
-    <mergeCell ref="P21:P22"/>
-    <mergeCell ref="R25:R26"/>
-    <mergeCell ref="U25:AB26"/>
-    <mergeCell ref="O27:O28"/>
-    <mergeCell ref="P27:P28"/>
-    <mergeCell ref="Q27:Q28"/>
-    <mergeCell ref="R27:R28"/>
-    <mergeCell ref="U27:AB28"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="O80:O81"/>
-    <mergeCell ref="P80:P81"/>
-    <mergeCell ref="Q80:Q81"/>
-    <mergeCell ref="R80:R81"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:D93"/>
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="F92:G93"/>
-    <mergeCell ref="H84:H85"/>
-    <mergeCell ref="I84:I85"/>
-    <mergeCell ref="L84:M85"/>
-    <mergeCell ref="N84:N85"/>
-    <mergeCell ref="O84:O85"/>
-    <mergeCell ref="P84:P85"/>
-    <mergeCell ref="Q84:Q85"/>
-    <mergeCell ref="R84:R85"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="C88:D89"/>
-    <mergeCell ref="E88:E89"/>
-    <mergeCell ref="F88:G89"/>
-    <mergeCell ref="H88:H89"/>
-    <mergeCell ref="I88:I89"/>
-    <mergeCell ref="P68:P69"/>
-    <mergeCell ref="Q68:Q69"/>
-    <mergeCell ref="R68:R69"/>
-    <mergeCell ref="U68:AB69"/>
-    <mergeCell ref="W60:X60"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="N29:N30"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="L25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="F17:G18"/>
-    <mergeCell ref="B56:U56"/>
-    <mergeCell ref="B54:AB54"/>
-    <mergeCell ref="B55:AB55"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="L67:R67"/>
-    <mergeCell ref="S67:T67"/>
-    <mergeCell ref="U67:AB67"/>
-    <mergeCell ref="C63:AB63"/>
-    <mergeCell ref="C64:AB64"/>
-    <mergeCell ref="B65:AB65"/>
-    <mergeCell ref="L66:R66"/>
-    <mergeCell ref="S66:T66"/>
-    <mergeCell ref="U66:AB66"/>
-    <mergeCell ref="B58:U58"/>
-    <mergeCell ref="Z60:AA60"/>
-    <mergeCell ref="A61:AB61"/>
-    <mergeCell ref="O70:O71"/>
-    <mergeCell ref="P70:P71"/>
-    <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="R70:R71"/>
-    <mergeCell ref="U70:AB71"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C68:D69"/>
-    <mergeCell ref="E68:E69"/>
-    <mergeCell ref="F68:G69"/>
-    <mergeCell ref="H68:H69"/>
-    <mergeCell ref="I68:I69"/>
-    <mergeCell ref="L68:M69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C70:D71"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="F70:G71"/>
-    <mergeCell ref="H70:H71"/>
-    <mergeCell ref="I70:I71"/>
-    <mergeCell ref="L70:M71"/>
-    <mergeCell ref="N70:N71"/>
-    <mergeCell ref="N68:N69"/>
-    <mergeCell ref="O68:O69"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:D73"/>
-    <mergeCell ref="E72:E73"/>
-    <mergeCell ref="F72:G73"/>
-    <mergeCell ref="H72:H73"/>
-    <mergeCell ref="I72:I73"/>
-    <mergeCell ref="L72:M73"/>
-    <mergeCell ref="N72:N73"/>
-    <mergeCell ref="P76:P77"/>
-    <mergeCell ref="Q76:Q77"/>
-    <mergeCell ref="R76:R77"/>
-    <mergeCell ref="U76:AB77"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:D75"/>
-    <mergeCell ref="E74:E75"/>
-    <mergeCell ref="F74:G75"/>
-    <mergeCell ref="H74:H75"/>
-    <mergeCell ref="I74:I75"/>
-    <mergeCell ref="L74:M75"/>
-    <mergeCell ref="N74:N75"/>
-    <mergeCell ref="O72:O73"/>
-    <mergeCell ref="P72:P73"/>
-    <mergeCell ref="Q72:Q73"/>
-    <mergeCell ref="R72:R73"/>
-    <mergeCell ref="U72:AB73"/>
-    <mergeCell ref="O74:O75"/>
-    <mergeCell ref="P74:P75"/>
-    <mergeCell ref="Q74:Q75"/>
-    <mergeCell ref="R74:R75"/>
-    <mergeCell ref="U74:AB75"/>
-    <mergeCell ref="O78:O79"/>
-    <mergeCell ref="P78:P79"/>
-    <mergeCell ref="Q78:Q79"/>
-    <mergeCell ref="R78:R79"/>
-    <mergeCell ref="U78:AB79"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="C76:D77"/>
-    <mergeCell ref="E76:E77"/>
-    <mergeCell ref="F76:G77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="C78:D79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:G79"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="I78:I79"/>
-    <mergeCell ref="L78:M79"/>
-    <mergeCell ref="N78:N79"/>
-    <mergeCell ref="H76:H77"/>
-    <mergeCell ref="I76:I77"/>
-    <mergeCell ref="L76:M77"/>
-    <mergeCell ref="N76:N77"/>
-    <mergeCell ref="O76:O77"/>
-    <mergeCell ref="U80:AB81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="B82:B83"/>
-    <mergeCell ref="C82:D83"/>
-    <mergeCell ref="E82:E83"/>
-    <mergeCell ref="F82:G83"/>
-    <mergeCell ref="H82:H83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="L82:M83"/>
-    <mergeCell ref="N82:N83"/>
-    <mergeCell ref="O82:O83"/>
-    <mergeCell ref="P82:P83"/>
-    <mergeCell ref="Q82:Q83"/>
-    <mergeCell ref="R82:R83"/>
-    <mergeCell ref="U82:AB83"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:D81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:G81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="L80:M81"/>
-    <mergeCell ref="N80:N81"/>
-    <mergeCell ref="U84:AB85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:D87"/>
-    <mergeCell ref="E86:E87"/>
-    <mergeCell ref="F86:G87"/>
-    <mergeCell ref="H86:H87"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="L86:M87"/>
-    <mergeCell ref="N86:N87"/>
-    <mergeCell ref="O86:O87"/>
-    <mergeCell ref="P86:P87"/>
-    <mergeCell ref="Q86:Q87"/>
-    <mergeCell ref="R86:R87"/>
-    <mergeCell ref="U86:AB87"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="C84:D85"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="F84:G85"/>
-    <mergeCell ref="L88:M89"/>
-    <mergeCell ref="N88:N89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="C90:D91"/>
-    <mergeCell ref="E90:E91"/>
-    <mergeCell ref="F90:G91"/>
-    <mergeCell ref="H90:H91"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="L90:M91"/>
-    <mergeCell ref="N90:N91"/>
-    <mergeCell ref="P92:P93"/>
-    <mergeCell ref="Q92:Q93"/>
-    <mergeCell ref="R92:R93"/>
-    <mergeCell ref="U92:AB93"/>
-    <mergeCell ref="O88:O89"/>
-    <mergeCell ref="P88:P89"/>
-    <mergeCell ref="Q88:Q89"/>
-    <mergeCell ref="R88:R89"/>
-    <mergeCell ref="U88:AB89"/>
-    <mergeCell ref="O90:O91"/>
-    <mergeCell ref="P90:P91"/>
-    <mergeCell ref="Q90:Q91"/>
-    <mergeCell ref="R90:R91"/>
-    <mergeCell ref="U90:AB91"/>
-    <mergeCell ref="I94:I95"/>
-    <mergeCell ref="L94:M95"/>
-    <mergeCell ref="N94:N95"/>
-    <mergeCell ref="H92:H93"/>
-    <mergeCell ref="I92:I93"/>
-    <mergeCell ref="L92:M93"/>
-    <mergeCell ref="N92:N93"/>
-    <mergeCell ref="O92:O93"/>
-    <mergeCell ref="O94:O95"/>
-    <mergeCell ref="P94:P95"/>
-    <mergeCell ref="Q94:Q95"/>
-    <mergeCell ref="R94:R95"/>
-    <mergeCell ref="U94:AB95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:D97"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="F96:G97"/>
-    <mergeCell ref="H96:H97"/>
-    <mergeCell ref="I96:I97"/>
-    <mergeCell ref="L96:M97"/>
-    <mergeCell ref="N96:N97"/>
-    <mergeCell ref="O96:O97"/>
-    <mergeCell ref="P96:P97"/>
-    <mergeCell ref="Q96:Q97"/>
-    <mergeCell ref="R96:R97"/>
-    <mergeCell ref="U96:AB97"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:D95"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="F94:G95"/>
-    <mergeCell ref="H94:H95"/>
-    <mergeCell ref="U98:AB99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:D101"/>
-    <mergeCell ref="E100:E101"/>
-    <mergeCell ref="F100:G101"/>
-    <mergeCell ref="H100:H101"/>
-    <mergeCell ref="I100:I101"/>
-    <mergeCell ref="L100:M101"/>
-    <mergeCell ref="N100:N101"/>
-    <mergeCell ref="O100:O101"/>
-    <mergeCell ref="P100:P101"/>
-    <mergeCell ref="Q100:Q101"/>
-    <mergeCell ref="R100:R101"/>
-    <mergeCell ref="U100:AB101"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:D99"/>
-    <mergeCell ref="E98:E99"/>
-    <mergeCell ref="F98:G99"/>
-    <mergeCell ref="H98:H99"/>
-    <mergeCell ref="I98:I99"/>
-    <mergeCell ref="L98:M99"/>
-    <mergeCell ref="N98:N99"/>
-    <mergeCell ref="L104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="Q104:Q105"/>
-    <mergeCell ref="R104:R105"/>
-    <mergeCell ref="U104:AB105"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:D103"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="F102:G103"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="I102:I103"/>
-    <mergeCell ref="L102:M103"/>
-    <mergeCell ref="N102:N103"/>
-    <mergeCell ref="U102:AB103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="C104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="F104:G105"/>
-    <mergeCell ref="H104:H105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="O106:O107"/>
-    <mergeCell ref="P106:P107"/>
-    <mergeCell ref="Q106:Q107"/>
-    <mergeCell ref="R106:R107"/>
-    <mergeCell ref="U106:AB107"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="C106:D107"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F106:G107"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="I106:I107"/>
-    <mergeCell ref="L106:M107"/>
-    <mergeCell ref="N106:N107"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="53" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="58" max="27" man="1"/>
   </rowBreaks>
